--- a/AAII_Financials/Quarterly/NTES_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NTES_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
   <si>
     <t>NTES</t>
   </si>
@@ -656,416 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3765500</v>
+        <v>3773000</v>
       </c>
       <c r="E8" s="3">
-        <v>3315500</v>
+        <v>3791100</v>
       </c>
       <c r="F8" s="3">
-        <v>3458400</v>
+        <v>3338100</v>
       </c>
       <c r="G8" s="3">
-        <v>3500900</v>
+        <v>3481900</v>
       </c>
       <c r="H8" s="3">
-        <v>3372900</v>
+        <v>3524700</v>
       </c>
       <c r="I8" s="3">
-        <v>3197800</v>
+        <v>3395800</v>
       </c>
       <c r="J8" s="3">
+        <v>3219600</v>
+      </c>
+      <c r="K8" s="3">
         <v>3252600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3358200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3154400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2917600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2856000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2750800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2749500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2679700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2691800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2422800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2253600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2207400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2203400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1098200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1841900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2336400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2033500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2167900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1851800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1985100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2024400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1759600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1339600</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1422800</v>
+        <v>1434000</v>
       </c>
       <c r="E9" s="3">
-        <v>1330500</v>
+        <v>1432500</v>
       </c>
       <c r="F9" s="3">
-        <v>1401500</v>
+        <v>1339600</v>
       </c>
       <c r="G9" s="3">
-        <v>1672100</v>
+        <v>1411000</v>
       </c>
       <c r="H9" s="3">
-        <v>1475100</v>
+        <v>1683500</v>
       </c>
       <c r="I9" s="3">
-        <v>1410800</v>
+        <v>1485100</v>
       </c>
       <c r="J9" s="3">
+        <v>1420400</v>
+      </c>
+      <c r="K9" s="3">
         <v>1480100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1578400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1475500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1327000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1317500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1368900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1292700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1236700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1212300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1131300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1041700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1025400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1021300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>92700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>830800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1296900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1179300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1315400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>969100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>985300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>913700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>819600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>564000</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2342700</v>
+        <v>2339000</v>
       </c>
       <c r="E10" s="3">
-        <v>1985000</v>
+        <v>2358700</v>
       </c>
       <c r="F10" s="3">
-        <v>2056900</v>
+        <v>1998500</v>
       </c>
       <c r="G10" s="3">
-        <v>1828800</v>
+        <v>2070900</v>
       </c>
       <c r="H10" s="3">
-        <v>1897800</v>
+        <v>1841200</v>
       </c>
       <c r="I10" s="3">
-        <v>1787000</v>
+        <v>1910700</v>
       </c>
       <c r="J10" s="3">
+        <v>1799100</v>
+      </c>
+      <c r="K10" s="3">
         <v>1772400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1779800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1678900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1590600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1538500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1381900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1456800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1443000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1479400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1291500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1211900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1182000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1182200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1005500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1011100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1039500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>854200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>852600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>882700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>999800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1110600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>940000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>775700</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,100 +1110,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>600200</v>
+        <v>622700</v>
       </c>
       <c r="E12" s="3">
-        <v>539700</v>
+        <v>604300</v>
       </c>
       <c r="F12" s="3">
-        <v>517800</v>
+        <v>543400</v>
       </c>
       <c r="G12" s="3">
-        <v>564800</v>
+        <v>521300</v>
       </c>
       <c r="H12" s="3">
-        <v>548100</v>
+        <v>568600</v>
       </c>
       <c r="I12" s="3">
-        <v>494600</v>
+        <v>551800</v>
       </c>
       <c r="J12" s="3">
+        <v>497900</v>
+      </c>
+      <c r="K12" s="3">
         <v>469200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>530100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>534700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>484300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>426000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>421700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>411000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>354900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>338000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>349100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>332900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>297300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>311300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>269400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>300500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>275100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>209300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>184400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>171100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>156000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>137200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>127600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>119300</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1282,8 +1298,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1374,8 +1393,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1466,8 +1488,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>2721900</v>
+        <v>2818200</v>
       </c>
       <c r="E17" s="3">
-        <v>2478300</v>
+        <v>2740400</v>
       </c>
       <c r="F17" s="3">
-        <v>2461400</v>
+        <v>2495200</v>
       </c>
       <c r="G17" s="3">
-        <v>2888700</v>
+        <v>2478200</v>
       </c>
       <c r="H17" s="3">
-        <v>2718100</v>
+        <v>2908400</v>
       </c>
       <c r="I17" s="3">
-        <v>2514800</v>
+        <v>2736600</v>
       </c>
       <c r="J17" s="3">
+        <v>2531900</v>
+      </c>
+      <c r="K17" s="3">
         <v>2492200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2723300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2617800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2383300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2260800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2331600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2326500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2065200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1984000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1964500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1740100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1638400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1629700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>531600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1487000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2001600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1860400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1956200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1473400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1479700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1316200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1197200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>925700</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>1043600</v>
+        <v>954900</v>
       </c>
       <c r="E18" s="3">
-        <v>837100</v>
+        <v>1050700</v>
       </c>
       <c r="F18" s="3">
-        <v>997000</v>
+        <v>842800</v>
       </c>
       <c r="G18" s="3">
-        <v>612200</v>
+        <v>1003700</v>
       </c>
       <c r="H18" s="3">
-        <v>654700</v>
+        <v>616300</v>
       </c>
       <c r="I18" s="3">
-        <v>683000</v>
+        <v>659200</v>
       </c>
       <c r="J18" s="3">
+        <v>687600</v>
+      </c>
+      <c r="K18" s="3">
         <v>760400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>634900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>536600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>534200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>595200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>419300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>422900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>614500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>707800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>458300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>513500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>569000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>573700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>566600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>354900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>334800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>173200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>211700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>378400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>505400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>708200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>562300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>414000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1715,192 +1747,199 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>213100</v>
+        <v>121800</v>
       </c>
       <c r="E20" s="3">
-        <v>387900</v>
+        <v>214600</v>
       </c>
       <c r="F20" s="3">
-        <v>154500</v>
+        <v>390500</v>
       </c>
       <c r="G20" s="3">
-        <v>47300</v>
+        <v>155500</v>
       </c>
       <c r="H20" s="3">
-        <v>478600</v>
+        <v>47700</v>
       </c>
       <c r="I20" s="3">
-        <v>108400</v>
+        <v>481800</v>
       </c>
       <c r="J20" s="3">
+        <v>109100</v>
+      </c>
+      <c r="K20" s="3">
         <v>3900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>274000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>50600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>118200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>210400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-212200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>39200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>227800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>86200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>152700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>140900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>55000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>49800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>68900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>55200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>50200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-17100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>24600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>32300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>43400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>27100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>105700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>54700</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>1346700</v>
+        <v>1168400</v>
       </c>
       <c r="E21" s="3">
-        <v>1316300</v>
+        <v>1355900</v>
       </c>
       <c r="F21" s="3">
-        <v>1300900</v>
+        <v>1325300</v>
       </c>
       <c r="G21" s="3">
-        <v>765700</v>
+        <v>1309700</v>
       </c>
       <c r="H21" s="3">
-        <v>1231900</v>
+        <v>770900</v>
       </c>
       <c r="I21" s="3">
-        <v>875500</v>
+        <v>1240300</v>
       </c>
       <c r="J21" s="3">
+        <v>881400</v>
+      </c>
+      <c r="K21" s="3">
         <v>870100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1024100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>701700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>768200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>919700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>341000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>596700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>973700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>902800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>718200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>762700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>720800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>712200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>734400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>489200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>452600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>208600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>277000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>441900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>574100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>756900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>682100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>481700</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1991,192 +2030,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>1256700</v>
+        <v>1076700</v>
       </c>
       <c r="E23" s="3">
-        <v>1225000</v>
+        <v>1265300</v>
       </c>
       <c r="F23" s="3">
-        <v>1151400</v>
+        <v>1233300</v>
       </c>
       <c r="G23" s="3">
-        <v>659500</v>
+        <v>1159300</v>
       </c>
       <c r="H23" s="3">
-        <v>1133300</v>
+        <v>664000</v>
       </c>
       <c r="I23" s="3">
-        <v>791400</v>
+        <v>1141000</v>
       </c>
       <c r="J23" s="3">
+        <v>796800</v>
+      </c>
+      <c r="K23" s="3">
         <v>764300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>908900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>587200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>652400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>805600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>207100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>462100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>842300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>794000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>611000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>654400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>624000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>623500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>635400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>410100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>385000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>156000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>236300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>410700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>548800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>735300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>668100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>468700</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>178200</v>
+        <v>148600</v>
       </c>
       <c r="E24" s="3">
-        <v>98300</v>
+        <v>179400</v>
       </c>
       <c r="F24" s="3">
-        <v>224900</v>
+        <v>99000</v>
       </c>
       <c r="G24" s="3">
-        <v>133500</v>
+        <v>226400</v>
       </c>
       <c r="H24" s="3">
-        <v>219100</v>
+        <v>134400</v>
       </c>
       <c r="I24" s="3">
-        <v>173900</v>
+        <v>220600</v>
       </c>
       <c r="J24" s="3">
+        <v>175100</v>
+      </c>
+      <c r="K24" s="3">
         <v>168400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>128700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>114800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>158200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>177300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>76900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>50500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>156900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>170700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>134900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>13500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>104500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>193500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>132800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>118000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>60300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>40600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>43100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>33500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>104400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>140000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>128300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>62100</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>1078500</v>
+        <v>928100</v>
       </c>
       <c r="E26" s="3">
-        <v>1126700</v>
+        <v>1085900</v>
       </c>
       <c r="F26" s="3">
-        <v>926600</v>
+        <v>1134300</v>
       </c>
       <c r="G26" s="3">
-        <v>526000</v>
+        <v>932900</v>
       </c>
       <c r="H26" s="3">
-        <v>914200</v>
+        <v>529600</v>
       </c>
       <c r="I26" s="3">
-        <v>617500</v>
+        <v>920500</v>
       </c>
       <c r="J26" s="3">
+        <v>621700</v>
+      </c>
+      <c r="K26" s="3">
         <v>595900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>780200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>472400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>494200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>628300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>130100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>411600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>685400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>623300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>476100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>640900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>519600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>429900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>502600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>292100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>324700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>115500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>193200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>377200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>444400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>595300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>539800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>406500</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>1082100</v>
+        <v>915100</v>
       </c>
       <c r="E27" s="3">
-        <v>1138200</v>
+        <v>1089500</v>
       </c>
       <c r="F27" s="3">
-        <v>932700</v>
+        <v>1145900</v>
       </c>
       <c r="G27" s="3">
-        <v>545800</v>
+        <v>939000</v>
       </c>
       <c r="H27" s="3">
-        <v>925000</v>
+        <v>549500</v>
       </c>
       <c r="I27" s="3">
-        <v>644400</v>
+        <v>931300</v>
       </c>
       <c r="J27" s="3">
+        <v>648800</v>
+      </c>
+      <c r="K27" s="3">
         <v>606700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>784500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>452300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>503500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>617900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>135800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>441800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>668700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>560200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>470200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>636600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>512500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>417500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>489400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>288700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>302200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>107900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>190800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>375100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>441100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>582200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>535600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2554,26 +2614,26 @@
       <c r="E29" s="3">
         <v>0</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>86300</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>0</v>
+        <v>86900</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>37</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>37</v>
@@ -2581,14 +2641,14 @@
       <c r="N29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3" t="s">
+      <c r="O29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -2597,28 +2657,28 @@
         <v>0</v>
       </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>1323600</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-43200</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-53600</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-242900</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-65300</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="AA29" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="AB29" s="3">
         <v>0</v>
@@ -2635,8 +2695,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2819,192 +2885,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-213100</v>
+        <v>-121800</v>
       </c>
       <c r="E32" s="3">
-        <v>-387900</v>
+        <v>-214600</v>
       </c>
       <c r="F32" s="3">
-        <v>-154500</v>
+        <v>-390500</v>
       </c>
       <c r="G32" s="3">
-        <v>-47300</v>
+        <v>-155500</v>
       </c>
       <c r="H32" s="3">
-        <v>-478600</v>
+        <v>-47700</v>
       </c>
       <c r="I32" s="3">
-        <v>-108400</v>
+        <v>-481800</v>
       </c>
       <c r="J32" s="3">
+        <v>-109100</v>
+      </c>
+      <c r="K32" s="3">
         <v>-3900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-274000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-50600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-118200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-210400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>212200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-39200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-227800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-86200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-152700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-140900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-55000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-49800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-68900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-55200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-50200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>17100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-24600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-32300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-43400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-27100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-105700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-54700</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>1082100</v>
+        <v>915100</v>
       </c>
       <c r="E33" s="3">
-        <v>1138200</v>
+        <v>1089500</v>
       </c>
       <c r="F33" s="3">
-        <v>932700</v>
+        <v>1145900</v>
       </c>
       <c r="G33" s="3">
-        <v>545800</v>
+        <v>939000</v>
       </c>
       <c r="H33" s="3">
-        <v>925000</v>
+        <v>549500</v>
       </c>
       <c r="I33" s="3">
-        <v>730600</v>
+        <v>931300</v>
       </c>
       <c r="J33" s="3">
+        <v>735600</v>
+      </c>
+      <c r="K33" s="3">
         <v>606700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>784500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>452300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>503500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>617900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>135800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>441800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>668700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>560200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>470200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1960200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>469200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>363900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>246600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>223400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>302200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>107900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>190800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>375100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>441100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>582200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>535600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>1082100</v>
+        <v>915100</v>
       </c>
       <c r="E35" s="3">
-        <v>1138200</v>
+        <v>1089500</v>
       </c>
       <c r="F35" s="3">
-        <v>932700</v>
+        <v>1145900</v>
       </c>
       <c r="G35" s="3">
-        <v>545800</v>
+        <v>939000</v>
       </c>
       <c r="H35" s="3">
-        <v>925000</v>
+        <v>549500</v>
       </c>
       <c r="I35" s="3">
-        <v>730600</v>
+        <v>931300</v>
       </c>
       <c r="J35" s="3">
+        <v>735600</v>
+      </c>
+      <c r="K35" s="3">
         <v>606700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>784500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>452300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>503500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>617900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>135800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>441800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>668700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>560200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>470200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1960200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>469200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>363900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>246600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>223400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>302200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>107900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>190800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>375100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>441100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>582200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>535600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3352,361 +3437,371 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>2087300</v>
+        <v>2979000</v>
       </c>
       <c r="E41" s="3">
-        <v>1762800</v>
+        <v>2101500</v>
       </c>
       <c r="F41" s="3">
-        <v>1891800</v>
+        <v>1774800</v>
       </c>
       <c r="G41" s="3">
-        <v>3436700</v>
+        <v>1904700</v>
       </c>
       <c r="H41" s="3">
-        <v>2485300</v>
+        <v>3460100</v>
       </c>
       <c r="I41" s="3">
-        <v>2273100</v>
+        <v>2502200</v>
       </c>
       <c r="J41" s="3">
+        <v>2288500</v>
+      </c>
+      <c r="K41" s="3">
         <v>1360400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1997600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3165200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1412400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1223700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1269100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>952900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1565400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>882300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>499900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>422100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>738300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>631300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>724500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>668700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>441800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>534800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>410200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>382200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>447100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>587600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>791100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>651800</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>13215700</v>
+        <v>14637700</v>
       </c>
       <c r="E42" s="3">
-        <v>13399500</v>
+        <v>13305700</v>
       </c>
       <c r="F42" s="3">
-        <v>14739200</v>
+        <v>13490800</v>
       </c>
       <c r="G42" s="3">
-        <v>12782100</v>
+        <v>14839600</v>
       </c>
       <c r="H42" s="3">
-        <v>13564400</v>
+        <v>12869100</v>
       </c>
       <c r="I42" s="3">
-        <v>13129100</v>
+        <v>13656800</v>
       </c>
       <c r="J42" s="3">
+        <v>13218500</v>
+      </c>
+      <c r="K42" s="3">
         <v>12793000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>11440800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>9817800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>12928100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>12628000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>11741800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>13547400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>12606300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>11025600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>10593800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>9029400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>7748900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>7283200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>6473600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>5270700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>5889700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>5683300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>5987800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>5655100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>5658600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>5370000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>4500100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>3836200</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>896400</v>
+        <v>892800</v>
       </c>
       <c r="E43" s="3">
-        <v>737800</v>
+        <v>902500</v>
       </c>
       <c r="F43" s="3">
-        <v>841100</v>
+        <v>742800</v>
       </c>
       <c r="G43" s="3">
-        <v>690800</v>
+        <v>846900</v>
       </c>
       <c r="H43" s="3">
-        <v>719100</v>
+        <v>695500</v>
       </c>
       <c r="I43" s="3">
-        <v>719800</v>
+        <v>724000</v>
       </c>
       <c r="J43" s="3">
+        <v>724700</v>
+      </c>
+      <c r="K43" s="3">
         <v>728700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>758900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>770800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>632900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>703900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>637000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>729300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>739500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>719300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>642000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>724700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>686700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>774700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>598200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>639500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>554400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>637900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>537200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>483700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>505200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>546600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>618300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>387100</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>99700</v>
+        <v>96700</v>
       </c>
       <c r="E44" s="3">
-        <v>111400</v>
+        <v>100400</v>
       </c>
       <c r="F44" s="3">
-        <v>121000</v>
+        <v>112200</v>
       </c>
       <c r="G44" s="3">
-        <v>137200</v>
+        <v>121800</v>
       </c>
       <c r="H44" s="3">
-        <v>128800</v>
+        <v>138100</v>
       </c>
       <c r="I44" s="3">
-        <v>116500</v>
+        <v>129700</v>
       </c>
       <c r="J44" s="3">
+        <v>117300</v>
+      </c>
+      <c r="K44" s="3">
         <v>118900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>132900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>147600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>125700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>121800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>86500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>77300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>82300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>88700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>100200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>105700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>606000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>653500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>154800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>880500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>814400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>734800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>812500</v>
-      </c>
-      <c r="AB44" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="AC44" s="3" t="s">
         <v>37</v>
@@ -3714,382 +3809,397 @@
       <c r="AD44" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AE44" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF44" s="3">
         <v>229500</v>
       </c>
-      <c r="AF44" s="3" t="s">
+      <c r="AG44" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1315100</v>
+        <v>1230900</v>
       </c>
       <c r="E45" s="3">
-        <v>1141300</v>
+        <v>1324100</v>
       </c>
       <c r="F45" s="3">
-        <v>1123200</v>
+        <v>1149100</v>
       </c>
       <c r="G45" s="3">
-        <v>1125000</v>
+        <v>1130900</v>
       </c>
       <c r="H45" s="3">
-        <v>1272500</v>
+        <v>1132600</v>
       </c>
       <c r="I45" s="3">
-        <v>1437000</v>
+        <v>1281200</v>
       </c>
       <c r="J45" s="3">
+        <v>1446800</v>
+      </c>
+      <c r="K45" s="3">
         <v>1440700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1255600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1584900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1384500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1404200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1275600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1457600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1380100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1517400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1268600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2428400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1379700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1603500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2028600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1351100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1249200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1503400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1445900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2209500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1940600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1537400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1120900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>922600</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>17614200</v>
+        <v>19837100</v>
       </c>
       <c r="E46" s="3">
-        <v>17152800</v>
+        <v>17734100</v>
       </c>
       <c r="F46" s="3">
-        <v>18716400</v>
+        <v>17269600</v>
       </c>
       <c r="G46" s="3">
-        <v>18171800</v>
+        <v>18843800</v>
       </c>
       <c r="H46" s="3">
-        <v>18170200</v>
+        <v>18295500</v>
       </c>
       <c r="I46" s="3">
-        <v>17675500</v>
+        <v>18293900</v>
       </c>
       <c r="J46" s="3">
+        <v>17795800</v>
+      </c>
+      <c r="K46" s="3">
         <v>16441700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15585700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15486300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>16483600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>16081600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15010100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>16764400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>16373600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>14233300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>13104500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12710400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>11159600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>10946200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>9979600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>8810600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>8949500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>9094200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>9193700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>8730600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>8551400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>8041600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>7181800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5797700</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>306700</v>
+        <v>146000</v>
       </c>
       <c r="E47" s="3">
-        <v>370300</v>
+        <v>308700</v>
       </c>
       <c r="F47" s="3">
-        <v>377200</v>
+        <v>372800</v>
       </c>
       <c r="G47" s="3">
-        <v>2971200</v>
+        <v>379800</v>
       </c>
       <c r="H47" s="3">
+        <v>2991500</v>
+      </c>
+      <c r="I47" s="3">
+        <v>622000</v>
+      </c>
+      <c r="J47" s="3">
+        <v>622000</v>
+      </c>
+      <c r="K47" s="3">
         <v>617700</v>
       </c>
-      <c r="I47" s="3">
-        <v>617700</v>
-      </c>
-      <c r="J47" s="3">
-        <v>617700</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3393300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>988400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1009300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>938200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2553100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>626300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1005500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>607400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1794500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7700</v>
-      </c>
-      <c r="U47" s="3">
-        <v>7600</v>
       </c>
       <c r="V47" s="3">
         <v>7600</v>
       </c>
       <c r="W47" s="3">
+        <v>7600</v>
+      </c>
+      <c r="X47" s="3">
         <v>776400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>21000</v>
-      </c>
-      <c r="Y47" s="3">
-        <v>21500</v>
       </c>
       <c r="Z47" s="3">
         <v>21500</v>
       </c>
       <c r="AA47" s="3">
+        <v>21500</v>
+      </c>
+      <c r="AB47" s="3">
         <v>413300</v>
-      </c>
-      <c r="AB47" s="3">
-        <v>7400</v>
       </c>
       <c r="AC47" s="3">
         <v>7400</v>
       </c>
       <c r="AD47" s="3">
+        <v>7400</v>
+      </c>
+      <c r="AE47" s="3">
         <v>74200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>366500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1047000</v>
+        <v>1122600</v>
       </c>
       <c r="E48" s="3">
-        <v>1014500</v>
+        <v>1054100</v>
       </c>
       <c r="F48" s="3">
-        <v>913800</v>
+        <v>1021400</v>
       </c>
       <c r="G48" s="3">
-        <v>998400</v>
+        <v>920000</v>
       </c>
       <c r="H48" s="3">
-        <v>851300</v>
+        <v>1005200</v>
       </c>
       <c r="I48" s="3">
-        <v>831600</v>
+        <v>857100</v>
       </c>
       <c r="J48" s="3">
+        <v>837200</v>
+      </c>
+      <c r="K48" s="3">
         <v>806700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>892500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>704600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>667300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>647500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>741700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>654200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>650800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1302800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1353900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1301600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>945300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>944100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>678700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>742600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>699200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>611500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>559400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>498100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>442500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>398600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>351900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>314500</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4150,38 +4260,41 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-      <c r="W49" s="3" t="s">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+      <c r="X49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>492700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>84200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>84700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>88000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>88500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>86500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>86900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>85600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>86100</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4480,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4723200</v>
+        <v>4741600</v>
       </c>
       <c r="E52" s="3">
-        <v>4646800</v>
+        <v>4755400</v>
       </c>
       <c r="F52" s="3">
-        <v>4604200</v>
+        <v>4678400</v>
       </c>
       <c r="G52" s="3">
-        <v>1713500</v>
+        <v>4635500</v>
       </c>
       <c r="H52" s="3">
-        <v>4208200</v>
+        <v>1725100</v>
       </c>
       <c r="I52" s="3">
-        <v>4097400</v>
+        <v>4236900</v>
       </c>
       <c r="J52" s="3">
+        <v>4125300</v>
+      </c>
+      <c r="K52" s="3">
         <v>4122900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1297500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3828800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3852800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3282900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1444000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3282800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3215000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2575400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1012100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2275000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2065600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2072100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1957600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1128300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1064000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>773500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>287400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>544500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>588900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>726800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>453800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>847100</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>23691100</v>
+        <v>25847300</v>
       </c>
       <c r="E54" s="3">
-        <v>23184400</v>
+        <v>23852400</v>
       </c>
       <c r="F54" s="3">
-        <v>24611600</v>
+        <v>23342300</v>
       </c>
       <c r="G54" s="3">
-        <v>23854800</v>
+        <v>24779100</v>
       </c>
       <c r="H54" s="3">
-        <v>23847500</v>
+        <v>24017200</v>
       </c>
       <c r="I54" s="3">
-        <v>23222200</v>
+        <v>24009800</v>
       </c>
       <c r="J54" s="3">
+        <v>23380300</v>
+      </c>
+      <c r="K54" s="3">
         <v>21989000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21169100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21008100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>22012900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>20950100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>19748900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>21327700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>21244900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>18718800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>17264900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>16294800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>14178000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>13970100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>12630400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>11195300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>10818400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>10585300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>10541800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>9869200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>9676800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>9328300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>8439600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>7221400</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,406 +4837,419 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>119200</v>
+        <v>122500</v>
       </c>
       <c r="E57" s="3">
-        <v>102300</v>
+        <v>120000</v>
       </c>
       <c r="F57" s="3">
-        <v>114800</v>
+        <v>103000</v>
       </c>
       <c r="G57" s="3">
-        <v>208100</v>
+        <v>115500</v>
       </c>
       <c r="H57" s="3">
-        <v>119800</v>
+        <v>209500</v>
       </c>
       <c r="I57" s="3">
-        <v>130100</v>
+        <v>120600</v>
       </c>
       <c r="J57" s="3">
+        <v>131000</v>
+      </c>
+      <c r="K57" s="3">
         <v>127700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>135700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>156200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>126500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>149100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>157900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>146900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>125800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>188800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>186700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>187800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>398700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>450600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>174500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>360300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>331200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>339400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>362500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>307000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>281800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>234400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>203000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>110800</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1549400</v>
+        <v>2674800</v>
       </c>
       <c r="E58" s="3">
-        <v>1640600</v>
+        <v>1560000</v>
       </c>
       <c r="F58" s="3">
-        <v>3782400</v>
+        <v>1651800</v>
       </c>
       <c r="G58" s="3">
-        <v>3296800</v>
+        <v>3808100</v>
       </c>
       <c r="H58" s="3">
-        <v>3513500</v>
+        <v>3319200</v>
       </c>
       <c r="I58" s="3">
-        <v>3870000</v>
+        <v>3537400</v>
       </c>
       <c r="J58" s="3">
+        <v>3896300</v>
+      </c>
+      <c r="K58" s="3">
         <v>3131600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2666400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2788200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3864800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3038300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2715100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3278400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3232000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3096000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2591200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2385900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2070800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2159500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1983600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1909900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1825900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1365400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>983000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>850800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>798100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>665400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>554900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>437000</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4388800</v>
+        <v>4687900</v>
       </c>
       <c r="E59" s="3">
-        <v>4103300</v>
+        <v>4418600</v>
       </c>
       <c r="F59" s="3">
-        <v>4136400</v>
+        <v>4131200</v>
       </c>
       <c r="G59" s="3">
-        <v>4342100</v>
+        <v>4164600</v>
       </c>
       <c r="H59" s="3">
-        <v>4241200</v>
+        <v>4371600</v>
       </c>
       <c r="I59" s="3">
-        <v>3931900</v>
+        <v>4270100</v>
       </c>
       <c r="J59" s="3">
+        <v>3958700</v>
+      </c>
+      <c r="K59" s="3">
         <v>3888400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4156000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4022200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3733400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3862800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3633700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3490100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3302200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3563100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3110800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2755700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2714800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2925100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2940700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2365900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2092900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2295300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2179300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1824600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1916500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2096200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2083000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1540700</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>6057400</v>
+        <v>7485200</v>
       </c>
       <c r="E60" s="3">
-        <v>5846200</v>
+        <v>6098600</v>
       </c>
       <c r="F60" s="3">
-        <v>8033600</v>
+        <v>5886000</v>
       </c>
       <c r="G60" s="3">
-        <v>7846900</v>
+        <v>8088300</v>
       </c>
       <c r="H60" s="3">
-        <v>7874500</v>
+        <v>7900300</v>
       </c>
       <c r="I60" s="3">
-        <v>7932000</v>
+        <v>7928100</v>
       </c>
       <c r="J60" s="3">
+        <v>7986000</v>
+      </c>
+      <c r="K60" s="3">
         <v>7147600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6958100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6966500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7724700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7050200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6506700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6915400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6660000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6848000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5888700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5329300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5184200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5535100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5098900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4636100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4250000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4000100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3524800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2982400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2996300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2995900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2788800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2088600</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>59100</v>
+        <v>59500</v>
       </c>
       <c r="E61" s="3">
-        <v>545900</v>
+        <v>59500</v>
       </c>
       <c r="F61" s="3">
-        <v>515000</v>
+        <v>549600</v>
       </c>
       <c r="G61" s="3">
-        <v>504700</v>
+        <v>518600</v>
       </c>
       <c r="H61" s="3">
-        <v>490200</v>
+        <v>508100</v>
       </c>
       <c r="I61" s="3">
-        <v>463400</v>
+        <v>493500</v>
       </c>
       <c r="J61" s="3">
+        <v>466500</v>
+      </c>
+      <c r="K61" s="3">
         <v>438300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>175700</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -5168,100 +5310,106 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>460200</v>
+        <v>496400</v>
       </c>
       <c r="E62" s="3">
-        <v>462200</v>
+        <v>463400</v>
       </c>
       <c r="F62" s="3">
-        <v>505000</v>
+        <v>465300</v>
       </c>
       <c r="G62" s="3">
-        <v>470000</v>
+        <v>508400</v>
       </c>
       <c r="H62" s="3">
-        <v>342400</v>
+        <v>473200</v>
       </c>
       <c r="I62" s="3">
-        <v>341400</v>
+        <v>344800</v>
       </c>
       <c r="J62" s="3">
+        <v>343700</v>
+      </c>
+      <c r="K62" s="3">
         <v>350100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>336700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>331200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>284400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>241500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>186100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>154400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>214700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>166100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>129300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>185900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>210400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>168600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>65000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>87600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>84800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>60500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>34400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>17800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>41800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>27800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>57100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>7124400</v>
+        <v>8569100</v>
       </c>
       <c r="E66" s="3">
-        <v>7406700</v>
+        <v>7172900</v>
       </c>
       <c r="F66" s="3">
-        <v>9610300</v>
+        <v>7457200</v>
       </c>
       <c r="G66" s="3">
-        <v>9393500</v>
+        <v>9675700</v>
       </c>
       <c r="H66" s="3">
-        <v>9298700</v>
+        <v>9457500</v>
       </c>
       <c r="I66" s="3">
-        <v>9299500</v>
+        <v>9362000</v>
       </c>
       <c r="J66" s="3">
+        <v>9362800</v>
+      </c>
+      <c r="K66" s="3">
         <v>8502500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8034800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9098800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9768700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9019800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8316900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8765700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8600700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8843500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7802300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>6535300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>6393700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6672100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6061400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5124400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4561000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4202100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3754700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3188400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3215300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3151400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2885400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2130900</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,8 +6200,11 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6044,11 +6217,11 @@
       <c r="F72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G72" s="3">
-        <v>12752100</v>
-      </c>
-      <c r="H72" s="3" t="s">
+      <c r="G72" s="3" t="s">
         <v>37</v>
+      </c>
+      <c r="H72" s="3">
+        <v>12839000</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>37</v>
@@ -6056,11 +6229,11 @@
       <c r="J72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L72" s="3">
         <v>10848700</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>37</v>
@@ -6068,11 +6241,11 @@
       <c r="N72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="P72" s="3">
         <v>9102400</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>37</v>
@@ -6080,11 +6253,11 @@
       <c r="R72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="T72" s="3">
         <v>8870600</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>37</v>
@@ -6092,11 +6265,11 @@
       <c r="V72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="W72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="X72" s="3">
         <v>6566100</v>
-      </c>
-      <c r="X72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="Y72" s="3" t="s">
         <v>37</v>
@@ -6116,14 +6289,17 @@
       <c r="AD72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF72" s="3">
         <v>5306600</v>
       </c>
-      <c r="AF72" s="3" t="s">
+      <c r="AG72" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>16566700</v>
+        <v>17278200</v>
       </c>
       <c r="E76" s="3">
-        <v>15777700</v>
+        <v>16679400</v>
       </c>
       <c r="F76" s="3">
-        <v>15001300</v>
+        <v>15885100</v>
       </c>
       <c r="G76" s="3">
-        <v>14461300</v>
+        <v>15103400</v>
       </c>
       <c r="H76" s="3">
-        <v>14548800</v>
+        <v>14559700</v>
       </c>
       <c r="I76" s="3">
-        <v>13922700</v>
+        <v>14647800</v>
       </c>
       <c r="J76" s="3">
+        <v>14017500</v>
+      </c>
+      <c r="K76" s="3">
         <v>13486500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13134300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11909300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12244200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11930300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11432100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12562000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12644200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9875400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9462600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9759400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7784300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7298000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>6569000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>6070900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>6257400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6383200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6787100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6680800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6461500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6176800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5554100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5090500</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>1082100</v>
+        <v>915100</v>
       </c>
       <c r="E81" s="3">
-        <v>1138200</v>
+        <v>1089500</v>
       </c>
       <c r="F81" s="3">
-        <v>932700</v>
+        <v>1145900</v>
       </c>
       <c r="G81" s="3">
-        <v>545800</v>
+        <v>939000</v>
       </c>
       <c r="H81" s="3">
-        <v>925000</v>
+        <v>549500</v>
       </c>
       <c r="I81" s="3">
-        <v>730600</v>
+        <v>931300</v>
       </c>
       <c r="J81" s="3">
+        <v>735600</v>
+      </c>
+      <c r="K81" s="3">
         <v>606700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>784500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>452300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>503500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>617900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>135800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>441800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>668700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>560200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>470200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1960200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>469200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>363900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>246600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>223400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>302200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>107900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>190800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>375100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>441100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>582200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>535600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7002,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>90000</v>
+        <v>91700</v>
       </c>
       <c r="E83" s="3">
-        <v>91300</v>
+        <v>90600</v>
       </c>
       <c r="F83" s="3">
-        <v>149400</v>
+        <v>91900</v>
       </c>
       <c r="G83" s="3">
-        <v>106200</v>
+        <v>150500</v>
       </c>
       <c r="H83" s="3">
-        <v>98600</v>
+        <v>106900</v>
       </c>
       <c r="I83" s="3">
-        <v>84100</v>
+        <v>99200</v>
       </c>
       <c r="J83" s="3">
+        <v>84700</v>
+      </c>
+      <c r="K83" s="3">
         <v>105800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>115200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>114500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>115800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>114100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>134000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>134500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>131500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>108900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>107100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>106000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>98100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>89700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>98200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>79800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>67600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>52600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>40700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>31300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>25300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>21700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>14100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1359200</v>
+        <v>1641600</v>
       </c>
       <c r="E89" s="3">
-        <v>1060200</v>
+        <v>1368500</v>
       </c>
       <c r="F89" s="3">
-        <v>828600</v>
+        <v>1067500</v>
       </c>
       <c r="G89" s="3">
-        <v>1244000</v>
+        <v>834200</v>
       </c>
       <c r="H89" s="3">
-        <v>1033700</v>
+        <v>1252500</v>
       </c>
       <c r="I89" s="3">
-        <v>915600</v>
+        <v>1040700</v>
       </c>
       <c r="J89" s="3">
+        <v>921900</v>
+      </c>
+      <c r="K89" s="3">
         <v>632800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1153000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>894500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>671300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>771500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1143400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>795900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>703200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1025500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>848500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>593400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>682300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>517400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>862000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>506300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>280900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>273300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>576000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>245700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>344500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>598300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>782200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>542400</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7702,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-606700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1385700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-803900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1479600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-510800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-709300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-530200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-893200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-739700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-625900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-988600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-45900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-42200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-51700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-34900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-25900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-36300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-50800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-41900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-56500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-73400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-80900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-111200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-96200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-84900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-76000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-64300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-48300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-67700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-24400</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-71200</v>
+        <v>-1490900</v>
       </c>
       <c r="E94" s="3">
-        <v>1600300</v>
+        <v>-71700</v>
       </c>
       <c r="F94" s="3">
-        <v>-2401500</v>
+        <v>1611200</v>
       </c>
       <c r="G94" s="3">
-        <v>533600</v>
+        <v>-2417900</v>
       </c>
       <c r="H94" s="3">
-        <v>136300</v>
+        <v>537200</v>
       </c>
       <c r="I94" s="3">
-        <v>-163400</v>
+        <v>137200</v>
       </c>
       <c r="J94" s="3">
+        <v>-164500</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1524100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2144900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>3007600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-788000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-991800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>145500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1105500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2985100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-391000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1069600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1090100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-514900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-724400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1195600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-55800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-555300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-153300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-592900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-140100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-343300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-831600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-670000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-658900</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,100 +8117,104 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-334600</v>
+        <v>-314000</v>
       </c>
       <c r="E96" s="3">
-        <v>-292600</v>
+        <v>-336900</v>
       </c>
       <c r="F96" s="3">
-        <v>-167400</v>
+        <v>-294600</v>
       </c>
       <c r="G96" s="3">
-        <v>-278800</v>
+        <v>-168500</v>
       </c>
       <c r="H96" s="3">
-        <v>-223400</v>
+        <v>-280700</v>
       </c>
       <c r="I96" s="3">
-        <v>-193800</v>
+        <v>-224900</v>
       </c>
       <c r="J96" s="3">
+        <v>-195100</v>
+      </c>
+      <c r="K96" s="3">
         <v>-232500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-129600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-146100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-181800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-36300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-119900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-203000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-164300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-146200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1061000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-142200</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-93700</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-63200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-58000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-74700</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-27500</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-45300</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-92700</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-109200</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-145500</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-136100</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-100700</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-99400</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8495,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-946300</v>
+        <v>714500</v>
       </c>
       <c r="E100" s="3">
-        <v>-2806500</v>
+        <v>-952800</v>
       </c>
       <c r="F100" s="3">
-        <v>79000</v>
+        <v>-2825600</v>
       </c>
       <c r="G100" s="3">
-        <v>-853700</v>
+        <v>79600</v>
       </c>
       <c r="H100" s="3">
-        <v>-992100</v>
+        <v>-859500</v>
       </c>
       <c r="I100" s="3">
-        <v>116100</v>
+        <v>-998800</v>
       </c>
       <c r="J100" s="3">
+        <v>116900</v>
+      </c>
+      <c r="K100" s="3">
         <v>316100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-147900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2117200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>281100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>195600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-887500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-367800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2973500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-219900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>180400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>112800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-188300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>62800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>406100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-127900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-41900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-6900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-171000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-31700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>16300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>17200</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-24200</v>
+      </c>
+      <c r="E101" s="3">
         <v>600</v>
       </c>
-      <c r="E101" s="3">
-        <v>-6600</v>
-      </c>
       <c r="F101" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="G101" s="3">
+        <v>2200</v>
+      </c>
+      <c r="H101" s="3">
+        <v>7400</v>
+      </c>
+      <c r="I101" s="3">
+        <v>500</v>
+      </c>
+      <c r="J101" s="3">
+        <v>10400</v>
+      </c>
+      <c r="K101" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="M101" s="3">
         <v>2100</v>
       </c>
-      <c r="G101" s="3">
-        <v>7400</v>
-      </c>
-      <c r="H101" s="3">
-        <v>500</v>
-      </c>
-      <c r="I101" s="3">
-        <v>10300</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-11100</v>
-      </c>
-      <c r="L101" s="3">
-        <v>2100</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>5000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-9400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>26500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>11700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-4100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>5900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>5400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>7600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>11200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>4000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>9900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>342300</v>
+        <v>840900</v>
       </c>
       <c r="E102" s="3">
-        <v>-152600</v>
+        <v>344600</v>
       </c>
       <c r="F102" s="3">
-        <v>-1491800</v>
+        <v>-153600</v>
       </c>
       <c r="G102" s="3">
-        <v>931200</v>
+        <v>-1501900</v>
       </c>
       <c r="H102" s="3">
-        <v>178400</v>
+        <v>937500</v>
       </c>
       <c r="I102" s="3">
-        <v>878700</v>
+        <v>179600</v>
       </c>
       <c r="J102" s="3">
+        <v>884700</v>
+      </c>
+      <c r="K102" s="3">
         <v>-578200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1150900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1786900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>160900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-19700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>392000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-681100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>718200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>426300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-44800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-378000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-15500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-146900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>70400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>330100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-305100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>114500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-25400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-61500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-34000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-217600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>139300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-112800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NTES_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NTES_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
   <si>
     <t>NTES</t>
   </si>
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3773000</v>
+        <v>3709800</v>
       </c>
       <c r="E8" s="3">
-        <v>3791100</v>
+        <v>3749700</v>
       </c>
       <c r="F8" s="3">
-        <v>3338100</v>
+        <v>3767700</v>
       </c>
       <c r="G8" s="3">
-        <v>3481900</v>
+        <v>3317400</v>
       </c>
       <c r="H8" s="3">
-        <v>3524700</v>
+        <v>3460400</v>
       </c>
       <c r="I8" s="3">
-        <v>3395800</v>
+        <v>3502900</v>
       </c>
       <c r="J8" s="3">
+        <v>3374800</v>
+      </c>
+      <c r="K8" s="3">
         <v>3219600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3252600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3358200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3154400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2917600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2856000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2750800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2749500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2679700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2691800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2422800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2253600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2207400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2203400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1098200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1841900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2336400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2033500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2167900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1851800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1985100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2024400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1759600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1339600</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1434000</v>
+        <v>1358900</v>
       </c>
       <c r="E9" s="3">
-        <v>1432500</v>
+        <v>1425100</v>
       </c>
       <c r="F9" s="3">
-        <v>1339600</v>
+        <v>1423600</v>
       </c>
       <c r="G9" s="3">
-        <v>1411000</v>
+        <v>1331300</v>
       </c>
       <c r="H9" s="3">
-        <v>1683500</v>
+        <v>1402300</v>
       </c>
       <c r="I9" s="3">
-        <v>1485100</v>
+        <v>1673100</v>
       </c>
       <c r="J9" s="3">
+        <v>1475900</v>
+      </c>
+      <c r="K9" s="3">
         <v>1420400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1480100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1578400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1475500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1327000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1317500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1368900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1292700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1236700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1212300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1131300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1041700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1025400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1021300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>92700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>830800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1296900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1179300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1315400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>969100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>985300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>913700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>819600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>564000</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2339000</v>
+        <v>2350900</v>
       </c>
       <c r="E10" s="3">
-        <v>2358700</v>
+        <v>2324600</v>
       </c>
       <c r="F10" s="3">
-        <v>1998500</v>
+        <v>2344100</v>
       </c>
       <c r="G10" s="3">
-        <v>2070900</v>
+        <v>1986100</v>
       </c>
       <c r="H10" s="3">
-        <v>1841200</v>
+        <v>2058100</v>
       </c>
       <c r="I10" s="3">
-        <v>1910700</v>
+        <v>1829800</v>
       </c>
       <c r="J10" s="3">
+        <v>1898900</v>
+      </c>
+      <c r="K10" s="3">
         <v>1799100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1772400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1779800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1678900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1590600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1538500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1381900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1456800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1443000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1479400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1291500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1211900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1182000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1182200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1005500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1011100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1039500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>854200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>852600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>882700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>999800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1110600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>940000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>775700</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,103 +1124,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>622700</v>
+        <v>576800</v>
       </c>
       <c r="E12" s="3">
-        <v>604300</v>
+        <v>618800</v>
       </c>
       <c r="F12" s="3">
-        <v>543400</v>
+        <v>600600</v>
       </c>
       <c r="G12" s="3">
-        <v>521300</v>
+        <v>540100</v>
       </c>
       <c r="H12" s="3">
-        <v>568600</v>
+        <v>518100</v>
       </c>
       <c r="I12" s="3">
-        <v>551800</v>
+        <v>565100</v>
       </c>
       <c r="J12" s="3">
+        <v>548400</v>
+      </c>
+      <c r="K12" s="3">
         <v>497900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>469200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>530100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>534700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>484300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>426000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>421700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>411000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>354900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>338000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>349100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>332900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>297300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>311300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>269400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>300500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>275100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>209300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>184400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>171100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>156000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>137200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>127600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>119300</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1301,8 +1318,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1396,8 +1416,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1491,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>2818200</v>
+        <v>2656700</v>
       </c>
       <c r="E17" s="3">
-        <v>2740400</v>
+        <v>2800700</v>
       </c>
       <c r="F17" s="3">
-        <v>2495200</v>
+        <v>2723500</v>
       </c>
       <c r="G17" s="3">
-        <v>2478200</v>
+        <v>2479800</v>
       </c>
       <c r="H17" s="3">
-        <v>2908400</v>
+        <v>2462900</v>
       </c>
       <c r="I17" s="3">
-        <v>2736600</v>
+        <v>2890400</v>
       </c>
       <c r="J17" s="3">
+        <v>2719700</v>
+      </c>
+      <c r="K17" s="3">
         <v>2531900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2492200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2723300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2617800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2383300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2260800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2331600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2326500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2065200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1984000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1964500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1740100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1638400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1629700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>531600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1487000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2001600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1860400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1956200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1473400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1479700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1316200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1197200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>925700</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>954900</v>
+        <v>1053100</v>
       </c>
       <c r="E18" s="3">
-        <v>1050700</v>
+        <v>949000</v>
       </c>
       <c r="F18" s="3">
-        <v>842800</v>
+        <v>1044200</v>
       </c>
       <c r="G18" s="3">
-        <v>1003700</v>
+        <v>837600</v>
       </c>
       <c r="H18" s="3">
-        <v>616300</v>
+        <v>997500</v>
       </c>
       <c r="I18" s="3">
-        <v>659200</v>
+        <v>612500</v>
       </c>
       <c r="J18" s="3">
+        <v>655100</v>
+      </c>
+      <c r="K18" s="3">
         <v>687600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>760400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>634900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>536600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>534200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>595200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>419300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>422900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>614500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>707800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>458300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>513500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>569000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>573700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>566600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>354900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>334800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>173200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>211700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>378400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>505400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>708200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>562300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>414000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1748,198 +1781,205 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>121800</v>
+        <v>230200</v>
       </c>
       <c r="E20" s="3">
-        <v>214600</v>
+        <v>121100</v>
       </c>
       <c r="F20" s="3">
-        <v>390500</v>
+        <v>213200</v>
       </c>
       <c r="G20" s="3">
-        <v>155500</v>
+        <v>388100</v>
       </c>
       <c r="H20" s="3">
-        <v>47700</v>
+        <v>154600</v>
       </c>
       <c r="I20" s="3">
-        <v>481800</v>
+        <v>47400</v>
       </c>
       <c r="J20" s="3">
+        <v>478800</v>
+      </c>
+      <c r="K20" s="3">
         <v>109100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>274000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>50600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>118200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>210400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-212200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>39200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>227800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>86200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>152700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>140900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>55000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>49800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>68900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>55200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>50200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-17100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>24600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>32300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>43400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>27100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>105700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>54700</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>1168400</v>
+        <v>1361700</v>
       </c>
       <c r="E21" s="3">
-        <v>1355900</v>
+        <v>1161200</v>
       </c>
       <c r="F21" s="3">
-        <v>1325300</v>
+        <v>1347500</v>
       </c>
       <c r="G21" s="3">
-        <v>1309700</v>
+        <v>1317100</v>
       </c>
       <c r="H21" s="3">
-        <v>770900</v>
+        <v>1301600</v>
       </c>
       <c r="I21" s="3">
-        <v>1240300</v>
+        <v>766200</v>
       </c>
       <c r="J21" s="3">
+        <v>1232600</v>
+      </c>
+      <c r="K21" s="3">
         <v>881400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>870100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1024100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>701700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>768200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>919700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>341000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>596700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>973700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>902800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>718200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>762700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>720800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>712200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>734400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>489200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>452600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>208600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>277000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>441900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>574100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>756900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>682100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>481700</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -2033,198 +2073,207 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>1076700</v>
+        <v>1283300</v>
       </c>
       <c r="E23" s="3">
-        <v>1265300</v>
+        <v>1070000</v>
       </c>
       <c r="F23" s="3">
-        <v>1233300</v>
+        <v>1257400</v>
       </c>
       <c r="G23" s="3">
-        <v>1159300</v>
+        <v>1225700</v>
       </c>
       <c r="H23" s="3">
-        <v>664000</v>
+        <v>1152100</v>
       </c>
       <c r="I23" s="3">
-        <v>1141000</v>
+        <v>659900</v>
       </c>
       <c r="J23" s="3">
+        <v>1134000</v>
+      </c>
+      <c r="K23" s="3">
         <v>796800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>764300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>908900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>587200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>652400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>805600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>207100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>462100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>842300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>794000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>611000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>654400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>624000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>623500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>635400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>410100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>385000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>156000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>236300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>410700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>548800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>735300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>668100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>468700</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>148600</v>
+        <v>205300</v>
       </c>
       <c r="E24" s="3">
-        <v>179400</v>
+        <v>147600</v>
       </c>
       <c r="F24" s="3">
-        <v>99000</v>
+        <v>178300</v>
       </c>
       <c r="G24" s="3">
-        <v>226400</v>
+        <v>98400</v>
       </c>
       <c r="H24" s="3">
-        <v>134400</v>
+        <v>225000</v>
       </c>
       <c r="I24" s="3">
-        <v>220600</v>
+        <v>133500</v>
       </c>
       <c r="J24" s="3">
+        <v>219200</v>
+      </c>
+      <c r="K24" s="3">
         <v>175100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>168400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>128700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>114800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>158200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>177300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>76900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>50500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>156900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>170700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>134900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>13500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>104500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>193500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>132800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>118000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>60300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>40600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>43100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>33500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>104400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>140000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>128300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>62100</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>928100</v>
+        <v>1078000</v>
       </c>
       <c r="E26" s="3">
-        <v>1085900</v>
+        <v>922400</v>
       </c>
       <c r="F26" s="3">
-        <v>1134300</v>
+        <v>1079200</v>
       </c>
       <c r="G26" s="3">
-        <v>932900</v>
+        <v>1127300</v>
       </c>
       <c r="H26" s="3">
-        <v>529600</v>
+        <v>927100</v>
       </c>
       <c r="I26" s="3">
-        <v>920500</v>
+        <v>526300</v>
       </c>
       <c r="J26" s="3">
+        <v>914800</v>
+      </c>
+      <c r="K26" s="3">
         <v>621700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>595900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>780200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>472400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>494200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>628300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>130100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>411600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>685400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>623300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>476100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>640900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>519600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>429900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>502600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>292100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>324700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>115500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>193200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>377200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>444400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>595300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>539800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>406500</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>915100</v>
+        <v>1054700</v>
       </c>
       <c r="E27" s="3">
-        <v>1089500</v>
+        <v>909400</v>
       </c>
       <c r="F27" s="3">
-        <v>1145900</v>
+        <v>1082700</v>
       </c>
       <c r="G27" s="3">
-        <v>939000</v>
+        <v>1138800</v>
       </c>
       <c r="H27" s="3">
-        <v>549500</v>
+        <v>933200</v>
       </c>
       <c r="I27" s="3">
-        <v>931300</v>
+        <v>546100</v>
       </c>
       <c r="J27" s="3">
+        <v>925600</v>
+      </c>
+      <c r="K27" s="3">
         <v>648800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>606700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>784500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>452300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>503500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>617900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>135800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>441800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>668700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>560200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>470200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>636600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>512500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>417500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>489400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>288700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>302200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>107900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>190800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>375100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>441100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>582200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>535600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2603,13 +2661,16 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -2617,26 +2678,26 @@
       <c r="F29" s="3">
         <v>0</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
       <c r="I29" s="3">
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>86900</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>37</v>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>37</v>
@@ -2644,14 +2705,14 @@
       <c r="O29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3" t="s">
+      <c r="P29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -2660,28 +2721,28 @@
         <v>0</v>
       </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>1323600</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-43200</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-53600</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-242900</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-65300</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
+      <c r="AB29" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="AC29" s="3">
         <v>0</v>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2888,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-121800</v>
+        <v>-230200</v>
       </c>
       <c r="E32" s="3">
-        <v>-214600</v>
+        <v>-121100</v>
       </c>
       <c r="F32" s="3">
-        <v>-390500</v>
+        <v>-213200</v>
       </c>
       <c r="G32" s="3">
-        <v>-155500</v>
+        <v>-388100</v>
       </c>
       <c r="H32" s="3">
-        <v>-47700</v>
+        <v>-154600</v>
       </c>
       <c r="I32" s="3">
-        <v>-481800</v>
+        <v>-47400</v>
       </c>
       <c r="J32" s="3">
+        <v>-478800</v>
+      </c>
+      <c r="K32" s="3">
         <v>-109100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-274000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-50600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-118200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-210400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>212200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-39200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-227800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-86200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-152700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-140900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-55000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-49800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-68900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-55200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-50200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>17100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-24600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-32300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-43400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-27100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-105700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-54700</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>915100</v>
+        <v>1054700</v>
       </c>
       <c r="E33" s="3">
-        <v>1089500</v>
+        <v>909400</v>
       </c>
       <c r="F33" s="3">
-        <v>1145900</v>
+        <v>1082700</v>
       </c>
       <c r="G33" s="3">
-        <v>939000</v>
+        <v>1138800</v>
       </c>
       <c r="H33" s="3">
-        <v>549500</v>
+        <v>933200</v>
       </c>
       <c r="I33" s="3">
-        <v>931300</v>
+        <v>546100</v>
       </c>
       <c r="J33" s="3">
+        <v>925600</v>
+      </c>
+      <c r="K33" s="3">
         <v>735600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>606700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>784500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>452300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>503500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>617900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>135800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>441800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>668700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>560200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>470200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1960200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>469200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>363900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>246600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>223400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>302200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>107900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>190800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>375100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>441100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>582200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>535600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>915100</v>
+        <v>1054700</v>
       </c>
       <c r="E35" s="3">
-        <v>1089500</v>
+        <v>909400</v>
       </c>
       <c r="F35" s="3">
-        <v>1145900</v>
+        <v>1082700</v>
       </c>
       <c r="G35" s="3">
-        <v>939000</v>
+        <v>1138800</v>
       </c>
       <c r="H35" s="3">
-        <v>549500</v>
+        <v>933200</v>
       </c>
       <c r="I35" s="3">
-        <v>931300</v>
+        <v>546100</v>
       </c>
       <c r="J35" s="3">
+        <v>925600</v>
+      </c>
+      <c r="K35" s="3">
         <v>735600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>606700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>784500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>452300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>503500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>617900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>135800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>441800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>668700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>560200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>470200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1960200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>469200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>363900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>246600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>223400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>302200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>107900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>190800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>375100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>441100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>582200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>535600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3438,373 +3524,383 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>2979000</v>
+        <v>5944600</v>
       </c>
       <c r="E41" s="3">
-        <v>2101500</v>
+        <v>2960600</v>
       </c>
       <c r="F41" s="3">
-        <v>1774800</v>
+        <v>2088500</v>
       </c>
       <c r="G41" s="3">
-        <v>1904700</v>
+        <v>1763800</v>
       </c>
       <c r="H41" s="3">
-        <v>3460100</v>
+        <v>1892900</v>
       </c>
       <c r="I41" s="3">
-        <v>2502200</v>
+        <v>3438700</v>
       </c>
       <c r="J41" s="3">
+        <v>2486800</v>
+      </c>
+      <c r="K41" s="3">
         <v>2288500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1360400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1997600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3165200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1412400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1223700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1269100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>952900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1565400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>882300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>499900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>422100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>738300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>631300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>724500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>668700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>441800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>534800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>410200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>382200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>447100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>587600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>791100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>651800</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>14637700</v>
+        <v>12651100</v>
       </c>
       <c r="E42" s="3">
-        <v>13305700</v>
+        <v>14547200</v>
       </c>
       <c r="F42" s="3">
-        <v>13490800</v>
+        <v>13223400</v>
       </c>
       <c r="G42" s="3">
-        <v>14839600</v>
+        <v>13407300</v>
       </c>
       <c r="H42" s="3">
-        <v>12869100</v>
+        <v>14747800</v>
       </c>
       <c r="I42" s="3">
-        <v>13656800</v>
+        <v>12789500</v>
       </c>
       <c r="J42" s="3">
+        <v>13572300</v>
+      </c>
+      <c r="K42" s="3">
         <v>13218500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>12793000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>11440800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>9817800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>12928100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>12628000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>11741800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>13547400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>12606300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>11025600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>10593800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>9029400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>7748900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>7283200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>6473600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>5270700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>5889700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>5683300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>5987800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>5655100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>5658600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>5370000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>4500100</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>3836200</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>892800</v>
+        <v>1073200</v>
       </c>
       <c r="E43" s="3">
-        <v>902500</v>
+        <v>887300</v>
       </c>
       <c r="F43" s="3">
-        <v>742800</v>
+        <v>897000</v>
       </c>
       <c r="G43" s="3">
-        <v>846900</v>
+        <v>738200</v>
       </c>
       <c r="H43" s="3">
-        <v>695500</v>
+        <v>841600</v>
       </c>
       <c r="I43" s="3">
-        <v>724000</v>
+        <v>691200</v>
       </c>
       <c r="J43" s="3">
+        <v>719500</v>
+      </c>
+      <c r="K43" s="3">
         <v>724700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>728700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>758900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>770800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>632900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>703900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>637000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>729300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>739500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>719300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>642000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>724700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>686700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>774700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>598200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>639500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>554400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>637900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>537200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>483700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>505200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>546600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>618300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>387100</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>96700</v>
+        <v>83400</v>
       </c>
       <c r="E44" s="3">
-        <v>100400</v>
+        <v>96100</v>
       </c>
       <c r="F44" s="3">
-        <v>112200</v>
+        <v>99700</v>
       </c>
       <c r="G44" s="3">
+        <v>111500</v>
+      </c>
+      <c r="H44" s="3">
+        <v>121100</v>
+      </c>
+      <c r="I44" s="3">
+        <v>137300</v>
+      </c>
+      <c r="J44" s="3">
+        <v>128900</v>
+      </c>
+      <c r="K44" s="3">
+        <v>117300</v>
+      </c>
+      <c r="L44" s="3">
+        <v>118900</v>
+      </c>
+      <c r="M44" s="3">
+        <v>132900</v>
+      </c>
+      <c r="N44" s="3">
+        <v>147600</v>
+      </c>
+      <c r="O44" s="3">
+        <v>125700</v>
+      </c>
+      <c r="P44" s="3">
         <v>121800</v>
       </c>
-      <c r="H44" s="3">
-        <v>138100</v>
-      </c>
-      <c r="I44" s="3">
-        <v>129700</v>
-      </c>
-      <c r="J44" s="3">
-        <v>117300</v>
-      </c>
-      <c r="K44" s="3">
-        <v>118900</v>
-      </c>
-      <c r="L44" s="3">
-        <v>132900</v>
-      </c>
-      <c r="M44" s="3">
-        <v>147600</v>
-      </c>
-      <c r="N44" s="3">
-        <v>125700</v>
-      </c>
-      <c r="O44" s="3">
-        <v>121800</v>
-      </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>86500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>77300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>82300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>88700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>100200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>105700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>606000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>653500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>154800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>880500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>814400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>734800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>812500</v>
-      </c>
-      <c r="AC44" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="AD44" s="3" t="s">
         <v>37</v>
@@ -3812,394 +3908,409 @@
       <c r="AE44" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AF44" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AG44" s="3">
         <v>229500</v>
       </c>
-      <c r="AG44" s="3" t="s">
+      <c r="AH44" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1230900</v>
+        <v>1219300</v>
       </c>
       <c r="E45" s="3">
-        <v>1324100</v>
+        <v>1223200</v>
       </c>
       <c r="F45" s="3">
-        <v>1149100</v>
+        <v>1315900</v>
       </c>
       <c r="G45" s="3">
-        <v>1130900</v>
+        <v>1142000</v>
       </c>
       <c r="H45" s="3">
-        <v>1132600</v>
+        <v>1123900</v>
       </c>
       <c r="I45" s="3">
-        <v>1281200</v>
+        <v>1125600</v>
       </c>
       <c r="J45" s="3">
+        <v>1273300</v>
+      </c>
+      <c r="K45" s="3">
         <v>1446800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1440700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1255600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1584900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1384500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1404200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1275600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1457600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1380100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1517400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1268600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2428400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1379700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1603500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2028600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1351100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1249200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1503400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1445900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2209500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1940600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1537400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1120900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>922600</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>19837100</v>
+        <v>20971600</v>
       </c>
       <c r="E46" s="3">
-        <v>17734100</v>
+        <v>19714400</v>
       </c>
       <c r="F46" s="3">
-        <v>17269600</v>
+        <v>17624400</v>
       </c>
       <c r="G46" s="3">
-        <v>18843800</v>
+        <v>17162800</v>
       </c>
       <c r="H46" s="3">
-        <v>18295500</v>
+        <v>18727200</v>
       </c>
       <c r="I46" s="3">
-        <v>18293900</v>
+        <v>18182300</v>
       </c>
       <c r="J46" s="3">
+        <v>18180800</v>
+      </c>
+      <c r="K46" s="3">
         <v>17795800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>16441700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15585700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>15486300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>16483600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>16081600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15010100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>16764400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>16373600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>14233300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>13104500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>12710400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>11159600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>10946200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>9979600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>8810600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>8949500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>9094200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>9193700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>8730600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>8551400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>8041600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>7181800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5797700</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>146000</v>
+        <v>145100</v>
       </c>
       <c r="E47" s="3">
-        <v>308700</v>
+        <v>3154600</v>
       </c>
       <c r="F47" s="3">
-        <v>372800</v>
+        <v>306800</v>
       </c>
       <c r="G47" s="3">
-        <v>379800</v>
+        <v>370500</v>
       </c>
       <c r="H47" s="3">
-        <v>2991500</v>
+        <v>377400</v>
       </c>
       <c r="I47" s="3">
+        <v>2973000</v>
+      </c>
+      <c r="J47" s="3">
+        <v>618100</v>
+      </c>
+      <c r="K47" s="3">
         <v>622000</v>
       </c>
-      <c r="J47" s="3">
-        <v>622000</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>617700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3393300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>988400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1009300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>938200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2553100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>626300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1005500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>607400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1794500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7700</v>
-      </c>
-      <c r="V47" s="3">
-        <v>7600</v>
       </c>
       <c r="W47" s="3">
         <v>7600</v>
       </c>
       <c r="X47" s="3">
+        <v>7600</v>
+      </c>
+      <c r="Y47" s="3">
         <v>776400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>21000</v>
-      </c>
-      <c r="Z47" s="3">
-        <v>21500</v>
       </c>
       <c r="AA47" s="3">
         <v>21500</v>
       </c>
       <c r="AB47" s="3">
+        <v>21500</v>
+      </c>
+      <c r="AC47" s="3">
         <v>413300</v>
-      </c>
-      <c r="AC47" s="3">
-        <v>7400</v>
       </c>
       <c r="AD47" s="3">
         <v>7400</v>
       </c>
       <c r="AE47" s="3">
+        <v>7400</v>
+      </c>
+      <c r="AF47" s="3">
         <v>74200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>366500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1122600</v>
+        <v>1113100</v>
       </c>
       <c r="E48" s="3">
-        <v>1054100</v>
+        <v>1219200</v>
       </c>
       <c r="F48" s="3">
-        <v>1021400</v>
+        <v>1047600</v>
       </c>
       <c r="G48" s="3">
-        <v>920000</v>
+        <v>1015100</v>
       </c>
       <c r="H48" s="3">
-        <v>1005200</v>
+        <v>914300</v>
       </c>
       <c r="I48" s="3">
-        <v>857100</v>
+        <v>998900</v>
       </c>
       <c r="J48" s="3">
+        <v>851800</v>
+      </c>
+      <c r="K48" s="3">
         <v>837200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>806700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>892500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>704600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>667300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>647500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>741700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>654200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>650800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1302800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1353900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1301600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>945300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>944100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>678700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>742600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>699200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>611500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>559400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>498100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>442500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>398600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>351900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>314500</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4263,38 +4374,41 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-      <c r="X49" s="3" t="s">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>492700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>84200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>84700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>88000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>88500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>86500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>86900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>85600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>86100</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,103 +4600,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4741600</v>
+        <v>4720400</v>
       </c>
       <c r="E52" s="3">
-        <v>4755400</v>
+        <v>1599200</v>
       </c>
       <c r="F52" s="3">
-        <v>4678400</v>
+        <v>4726000</v>
       </c>
       <c r="G52" s="3">
-        <v>4635500</v>
+        <v>4649500</v>
       </c>
       <c r="H52" s="3">
-        <v>1725100</v>
+        <v>4606900</v>
       </c>
       <c r="I52" s="3">
-        <v>4236900</v>
+        <v>1714500</v>
       </c>
       <c r="J52" s="3">
+        <v>4210700</v>
+      </c>
+      <c r="K52" s="3">
         <v>4125300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4122900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1297500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3828800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3852800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3282900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1444000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3282800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3215000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2575400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1012100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2275000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2065600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2072100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1957600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1128300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1064000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>773500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>287400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>544500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>588900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>726800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>453800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>847100</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>25847300</v>
+        <v>26950200</v>
       </c>
       <c r="E54" s="3">
-        <v>23852400</v>
+        <v>25687400</v>
       </c>
       <c r="F54" s="3">
-        <v>23342300</v>
+        <v>23704800</v>
       </c>
       <c r="G54" s="3">
-        <v>24779100</v>
+        <v>23197900</v>
       </c>
       <c r="H54" s="3">
-        <v>24017200</v>
+        <v>24625800</v>
       </c>
       <c r="I54" s="3">
-        <v>24009800</v>
+        <v>23868700</v>
       </c>
       <c r="J54" s="3">
+        <v>23861300</v>
+      </c>
+      <c r="K54" s="3">
         <v>23380300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21989000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21169100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21008100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>22012900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>20950100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>19748900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>21327700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>21244900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>18718800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>17264900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>16294800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>14178000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>13970100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>12630400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>11195300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>10818400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>10585300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>10541800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>9869200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>9676800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>9328300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>8439600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>7221400</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,421 +4968,434 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>122500</v>
+        <v>120400</v>
       </c>
       <c r="E57" s="3">
-        <v>120000</v>
+        <v>121700</v>
       </c>
       <c r="F57" s="3">
-        <v>103000</v>
+        <v>119300</v>
       </c>
       <c r="G57" s="3">
-        <v>115500</v>
+        <v>102300</v>
       </c>
       <c r="H57" s="3">
-        <v>209500</v>
+        <v>114800</v>
       </c>
       <c r="I57" s="3">
-        <v>120600</v>
+        <v>208200</v>
       </c>
       <c r="J57" s="3">
+        <v>119800</v>
+      </c>
+      <c r="K57" s="3">
         <v>131000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>127700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>135700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>156200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>126500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>149100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>157900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>146900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>125800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>188800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>186700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>187800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>398700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>450600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>174500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>360300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>331200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>339400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>362500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>307000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>281800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>234400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>203000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>110800</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2674800</v>
+        <v>3432400</v>
       </c>
       <c r="E58" s="3">
-        <v>1560000</v>
+        <v>2658200</v>
       </c>
       <c r="F58" s="3">
-        <v>1651800</v>
+        <v>1550300</v>
       </c>
       <c r="G58" s="3">
-        <v>3808100</v>
+        <v>1641600</v>
       </c>
       <c r="H58" s="3">
-        <v>3319200</v>
+        <v>3784600</v>
       </c>
       <c r="I58" s="3">
-        <v>3537400</v>
+        <v>3298700</v>
       </c>
       <c r="J58" s="3">
+        <v>3515600</v>
+      </c>
+      <c r="K58" s="3">
         <v>3896300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3131600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2666400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2788200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3864800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3038300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2715100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3278400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3232000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3096000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2591200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2385900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2070800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2159500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1983600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1909900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1825900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1365400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>983000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>850800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>798100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>665400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>554900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>437000</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4687900</v>
+        <v>4743700</v>
       </c>
       <c r="E59" s="3">
-        <v>4418600</v>
+        <v>4658900</v>
       </c>
       <c r="F59" s="3">
-        <v>4131200</v>
+        <v>4391300</v>
       </c>
       <c r="G59" s="3">
-        <v>4164600</v>
+        <v>4105700</v>
       </c>
       <c r="H59" s="3">
-        <v>4371600</v>
+        <v>4138800</v>
       </c>
       <c r="I59" s="3">
-        <v>4270100</v>
+        <v>4344600</v>
       </c>
       <c r="J59" s="3">
+        <v>4243700</v>
+      </c>
+      <c r="K59" s="3">
         <v>3958700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3888400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4156000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4022200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3733400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3862800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3633700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3490100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3302200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3563100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3110800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2755700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2714800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2925100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2940700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2365900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2092900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2295300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2179300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1824600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1916500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2096200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2083000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1540700</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>7485200</v>
+        <v>8296400</v>
       </c>
       <c r="E60" s="3">
-        <v>6098600</v>
+        <v>7438900</v>
       </c>
       <c r="F60" s="3">
-        <v>5886000</v>
+        <v>6060900</v>
       </c>
       <c r="G60" s="3">
-        <v>8088300</v>
+        <v>5849600</v>
       </c>
       <c r="H60" s="3">
-        <v>7900300</v>
+        <v>8038200</v>
       </c>
       <c r="I60" s="3">
-        <v>7928100</v>
+        <v>7851500</v>
       </c>
       <c r="J60" s="3">
+        <v>7879100</v>
+      </c>
+      <c r="K60" s="3">
         <v>7986000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7147600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6958100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6966500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7724700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7050200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6506700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6915400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6660000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6848000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5888700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5329300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5184200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5535100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5098900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4636100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4250000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4000100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3524800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2982400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2996300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2995900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2788800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2088600</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>59500</v>
+        <v>59100</v>
       </c>
       <c r="E61" s="3">
-        <v>59500</v>
+        <v>59100</v>
       </c>
       <c r="F61" s="3">
-        <v>549600</v>
+        <v>59100</v>
       </c>
       <c r="G61" s="3">
-        <v>518600</v>
+        <v>546200</v>
       </c>
       <c r="H61" s="3">
-        <v>508100</v>
+        <v>515300</v>
       </c>
       <c r="I61" s="3">
-        <v>493500</v>
+        <v>505000</v>
       </c>
       <c r="J61" s="3">
+        <v>490500</v>
+      </c>
+      <c r="K61" s="3">
         <v>466500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>438300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>175700</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -5313,103 +5456,109 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>496400</v>
+        <v>545600</v>
       </c>
       <c r="E62" s="3">
-        <v>463400</v>
+        <v>493300</v>
       </c>
       <c r="F62" s="3">
-        <v>465300</v>
+        <v>460500</v>
       </c>
       <c r="G62" s="3">
-        <v>508400</v>
+        <v>462500</v>
       </c>
       <c r="H62" s="3">
-        <v>473200</v>
+        <v>505300</v>
       </c>
       <c r="I62" s="3">
-        <v>344800</v>
+        <v>470300</v>
       </c>
       <c r="J62" s="3">
+        <v>342600</v>
+      </c>
+      <c r="K62" s="3">
         <v>343700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>350100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>336700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>331200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>284400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>241500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>186100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>154400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>214700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>166100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>129300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>185900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>210400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>168600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>65000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>87600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>84800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>60500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>34400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>17800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>41800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>27800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>57100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>8569100</v>
+        <v>9365700</v>
       </c>
       <c r="E66" s="3">
-        <v>7172900</v>
+        <v>8516100</v>
       </c>
       <c r="F66" s="3">
-        <v>7457200</v>
+        <v>7128500</v>
       </c>
       <c r="G66" s="3">
-        <v>9675700</v>
+        <v>7411000</v>
       </c>
       <c r="H66" s="3">
-        <v>9457500</v>
+        <v>9615800</v>
       </c>
       <c r="I66" s="3">
-        <v>9362000</v>
+        <v>9399000</v>
       </c>
       <c r="J66" s="3">
+        <v>9304100</v>
+      </c>
+      <c r="K66" s="3">
         <v>9362800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8502500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>8034800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9098800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9768700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9019800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8316900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8765700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8600700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8843500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7802300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>6535300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6393700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6672100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>6061400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5124400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4561000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4202100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3754700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3188400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3215300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3151400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2885400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2130900</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,16 +6374,19 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>37</v>
+      <c r="E72" s="3">
+        <v>15716500</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>37</v>
@@ -6220,11 +6394,11 @@
       <c r="G72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H72" s="3">
-        <v>12839000</v>
-      </c>
-      <c r="I72" s="3" t="s">
+      <c r="H72" s="3" t="s">
         <v>37</v>
+      </c>
+      <c r="I72" s="3">
+        <v>12759500</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>37</v>
@@ -6232,11 +6406,11 @@
       <c r="K72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M72" s="3">
         <v>10848700</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>37</v>
@@ -6244,11 +6418,11 @@
       <c r="O72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="P72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q72" s="3">
         <v>9102400</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="R72" s="3" t="s">
         <v>37</v>
@@ -6256,11 +6430,11 @@
       <c r="S72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="T72" s="3">
+      <c r="T72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="U72" s="3">
         <v>8870600</v>
-      </c>
-      <c r="U72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>37</v>
@@ -6268,11 +6442,11 @@
       <c r="W72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="X72" s="3">
+      <c r="X72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y72" s="3">
         <v>6566100</v>
-      </c>
-      <c r="Y72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="Z72" s="3" t="s">
         <v>37</v>
@@ -6292,14 +6466,17 @@
       <c r="AE72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AF72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AG72" s="3">
         <v>5306600</v>
       </c>
-      <c r="AG72" s="3" t="s">
+      <c r="AH72" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>17278200</v>
+        <v>17584400</v>
       </c>
       <c r="E76" s="3">
-        <v>16679400</v>
+        <v>17171300</v>
       </c>
       <c r="F76" s="3">
-        <v>15885100</v>
+        <v>16576300</v>
       </c>
       <c r="G76" s="3">
-        <v>15103400</v>
+        <v>15786800</v>
       </c>
       <c r="H76" s="3">
-        <v>14559700</v>
+        <v>15010000</v>
       </c>
       <c r="I76" s="3">
-        <v>14647800</v>
+        <v>14469700</v>
       </c>
       <c r="J76" s="3">
+        <v>14557200</v>
+      </c>
+      <c r="K76" s="3">
         <v>14017500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13486500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13134300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11909300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12244200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11930300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11432100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12562000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12644200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9875400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9462600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9759400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7784300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7298000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>6569000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>6070900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6257400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6383200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6787100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6680800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6461500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6176800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5554100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5090500</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>915100</v>
+        <v>1054700</v>
       </c>
       <c r="E81" s="3">
-        <v>1089500</v>
+        <v>909400</v>
       </c>
       <c r="F81" s="3">
-        <v>1145900</v>
+        <v>1082700</v>
       </c>
       <c r="G81" s="3">
-        <v>939000</v>
+        <v>1138800</v>
       </c>
       <c r="H81" s="3">
-        <v>549500</v>
+        <v>933200</v>
       </c>
       <c r="I81" s="3">
-        <v>931300</v>
+        <v>546100</v>
       </c>
       <c r="J81" s="3">
+        <v>925600</v>
+      </c>
+      <c r="K81" s="3">
         <v>735600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>606700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>784500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>452300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>503500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>617900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>135800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>441800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>668700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>560200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>470200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1960200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>469200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>363900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>246600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>223400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>302200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>107900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>190800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>375100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>441100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>582200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>535600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,103 +7201,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>91700</v>
+        <v>78500</v>
       </c>
       <c r="E83" s="3">
-        <v>90600</v>
+        <v>91200</v>
       </c>
       <c r="F83" s="3">
-        <v>91900</v>
+        <v>90100</v>
       </c>
       <c r="G83" s="3">
-        <v>150500</v>
+        <v>91400</v>
       </c>
       <c r="H83" s="3">
-        <v>106900</v>
+        <v>149500</v>
       </c>
       <c r="I83" s="3">
-        <v>99200</v>
+        <v>106300</v>
       </c>
       <c r="J83" s="3">
+        <v>98600</v>
+      </c>
+      <c r="K83" s="3">
         <v>84700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>105800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>115200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>114500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>115800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>114100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>134000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>134500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>131500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>108900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>107100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>106000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>98100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>89700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>98200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>79800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>67600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>52600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>40700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>31300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>25300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>21700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>14100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1641600</v>
+        <v>1320400</v>
       </c>
       <c r="E89" s="3">
-        <v>1368500</v>
+        <v>1631400</v>
       </c>
       <c r="F89" s="3">
-        <v>1067500</v>
+        <v>1360000</v>
       </c>
       <c r="G89" s="3">
-        <v>834200</v>
+        <v>1060800</v>
       </c>
       <c r="H89" s="3">
-        <v>1252500</v>
+        <v>829100</v>
       </c>
       <c r="I89" s="3">
-        <v>1040700</v>
+        <v>1244700</v>
       </c>
       <c r="J89" s="3">
+        <v>1034300</v>
+      </c>
+      <c r="K89" s="3">
         <v>921900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>632800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1153000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>894500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>671300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>771500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1143400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>795900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>703200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1025500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>848500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>593400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>682300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>517400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>862000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>506300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>280900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>273300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>576000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>245700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>344500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>598300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>782200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>542400</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,103 +7923,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-603800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-606700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1385700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-803900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1479600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-510800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-709300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-530200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-893200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-739700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-625900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-988600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-45900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-42200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-51700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-34900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-25900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-36300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-50800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-41900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-56500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-73400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-80900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-111200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-96200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-84900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-76000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-64300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-48300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-67700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-24400</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1490900</v>
+        <v>1776700</v>
       </c>
       <c r="E94" s="3">
-        <v>-71700</v>
+        <v>-1481700</v>
       </c>
       <c r="F94" s="3">
-        <v>1611200</v>
+        <v>-71300</v>
       </c>
       <c r="G94" s="3">
-        <v>-2417900</v>
+        <v>1601200</v>
       </c>
       <c r="H94" s="3">
-        <v>537200</v>
+        <v>-2402900</v>
       </c>
       <c r="I94" s="3">
-        <v>137200</v>
+        <v>533900</v>
       </c>
       <c r="J94" s="3">
+        <v>136400</v>
+      </c>
+      <c r="K94" s="3">
         <v>-164500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1524100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2144900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>3007600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-788000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-991800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>145500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1105500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2985100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-391000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1069600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1090100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-514900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-724400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1195600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-55800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-555300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-153300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-592900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-140100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-343300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-831600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-670000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-658900</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,103 +8351,107 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-314000</v>
+        <v>-683200</v>
       </c>
       <c r="E96" s="3">
-        <v>-336900</v>
+        <v>-312100</v>
       </c>
       <c r="F96" s="3">
-        <v>-294600</v>
+        <v>-334800</v>
       </c>
       <c r="G96" s="3">
-        <v>-168500</v>
+        <v>-292800</v>
       </c>
       <c r="H96" s="3">
-        <v>-280700</v>
+        <v>-167500</v>
       </c>
       <c r="I96" s="3">
-        <v>-224900</v>
+        <v>-278900</v>
       </c>
       <c r="J96" s="3">
+        <v>-223500</v>
+      </c>
+      <c r="K96" s="3">
         <v>-195100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-232500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-129600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-146100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-181800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-36300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-119900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-203000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-164300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-146200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-1061000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-142200</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-93700</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-63200</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-58000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-74700</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-27500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-45300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-92700</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-109200</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-145500</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-136100</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-100700</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-99400</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,289 +8741,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>714500</v>
+        <v>-68400</v>
       </c>
       <c r="E100" s="3">
-        <v>-952800</v>
+        <v>710000</v>
       </c>
       <c r="F100" s="3">
-        <v>-2825600</v>
+        <v>-946900</v>
       </c>
       <c r="G100" s="3">
-        <v>79600</v>
+        <v>-2808100</v>
       </c>
       <c r="H100" s="3">
-        <v>-859500</v>
+        <v>79100</v>
       </c>
       <c r="I100" s="3">
-        <v>-998800</v>
+        <v>-854200</v>
       </c>
       <c r="J100" s="3">
+        <v>-992700</v>
+      </c>
+      <c r="K100" s="3">
         <v>116900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>316100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-147900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2117200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>281100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>195600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-887500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-367800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2973500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-219900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>180400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>112800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-188300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>62800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>406100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-127900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-41900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-6900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-171000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-31700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>16300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>17200</v>
       </c>
-      <c r="AG100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-24200</v>
+        <v>-6000</v>
       </c>
       <c r="E101" s="3">
+        <v>-24100</v>
+      </c>
+      <c r="F101" s="3">
         <v>600</v>
       </c>
-      <c r="F101" s="3">
-        <v>-6700</v>
-      </c>
       <c r="G101" s="3">
-        <v>2200</v>
+        <v>-6600</v>
       </c>
       <c r="H101" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I101" s="3">
         <v>7400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>10400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-11100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>5000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-3700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>26500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>11700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-4100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>5900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>5400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>7600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>11200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>4000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>9900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>840900</v>
+        <v>3022800</v>
       </c>
       <c r="E102" s="3">
-        <v>344600</v>
+        <v>835700</v>
       </c>
       <c r="F102" s="3">
-        <v>-153600</v>
+        <v>342500</v>
       </c>
       <c r="G102" s="3">
-        <v>-1501900</v>
+        <v>-152700</v>
       </c>
       <c r="H102" s="3">
-        <v>937500</v>
+        <v>-1492600</v>
       </c>
       <c r="I102" s="3">
-        <v>179600</v>
+        <v>931700</v>
       </c>
       <c r="J102" s="3">
+        <v>178500</v>
+      </c>
+      <c r="K102" s="3">
         <v>884700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-578200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1150900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1786900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>160900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-19700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>392000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-681100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>718200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>426300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-44800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-378000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-15500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-146900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>70400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>330100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-305100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>114500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-25400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-61500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-34000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-217600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>139300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-112800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NTES_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NTES_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
   <si>
     <t>NTES</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3709800</v>
+        <v>3593000</v>
       </c>
       <c r="E8" s="3">
-        <v>3749700</v>
+        <v>3785600</v>
       </c>
       <c r="F8" s="3">
-        <v>3767700</v>
+        <v>3826200</v>
       </c>
       <c r="G8" s="3">
-        <v>3317400</v>
+        <v>3844600</v>
       </c>
       <c r="H8" s="3">
-        <v>3460400</v>
+        <v>3385100</v>
       </c>
       <c r="I8" s="3">
-        <v>3502900</v>
+        <v>3531000</v>
       </c>
       <c r="J8" s="3">
+        <v>3574400</v>
+      </c>
+      <c r="K8" s="3">
         <v>3374800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3219600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3252600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3358200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3154400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2917600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2856000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2750800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2749500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2679700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2691800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2422800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2253600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2207400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2203400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1098200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1841900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2336400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2033500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2167900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1851800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1985100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2024400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1759600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1339600</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1358900</v>
+        <v>1331400</v>
       </c>
       <c r="E9" s="3">
-        <v>1425100</v>
+        <v>1386700</v>
       </c>
       <c r="F9" s="3">
-        <v>1423600</v>
+        <v>1454200</v>
       </c>
       <c r="G9" s="3">
-        <v>1331300</v>
+        <v>1452700</v>
       </c>
       <c r="H9" s="3">
-        <v>1402300</v>
+        <v>1358500</v>
       </c>
       <c r="I9" s="3">
-        <v>1673100</v>
+        <v>1430900</v>
       </c>
       <c r="J9" s="3">
+        <v>1707200</v>
+      </c>
+      <c r="K9" s="3">
         <v>1475900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1420400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1480100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1578400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1475500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1327000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1317500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1368900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1292700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1236700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1212300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1131300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1041700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1025400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1021300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>92700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>830800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1296900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1179300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1315400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>969100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>985300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>913700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>819600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>564000</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2350900</v>
+        <v>2261600</v>
       </c>
       <c r="E10" s="3">
-        <v>2324600</v>
+        <v>2398900</v>
       </c>
       <c r="F10" s="3">
-        <v>2344100</v>
+        <v>2372000</v>
       </c>
       <c r="G10" s="3">
-        <v>1986100</v>
+        <v>2391900</v>
       </c>
       <c r="H10" s="3">
-        <v>2058100</v>
+        <v>2026600</v>
       </c>
       <c r="I10" s="3">
-        <v>1829800</v>
+        <v>2100100</v>
       </c>
       <c r="J10" s="3">
+        <v>1867200</v>
+      </c>
+      <c r="K10" s="3">
         <v>1898900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1799100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1772400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1779800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1678900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1590600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1538500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1381900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1456800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1443000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1479400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1291500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1211900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1182000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1182200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1005500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1011100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1039500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>854200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>852600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>882700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>999800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1110600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>940000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>775700</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,106 +1138,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>576800</v>
+        <v>628200</v>
       </c>
       <c r="E12" s="3">
-        <v>618800</v>
+        <v>588600</v>
       </c>
       <c r="F12" s="3">
-        <v>600600</v>
+        <v>631500</v>
       </c>
       <c r="G12" s="3">
-        <v>540100</v>
+        <v>612800</v>
       </c>
       <c r="H12" s="3">
-        <v>518100</v>
+        <v>551100</v>
       </c>
       <c r="I12" s="3">
-        <v>565100</v>
+        <v>528600</v>
       </c>
       <c r="J12" s="3">
+        <v>576600</v>
+      </c>
+      <c r="K12" s="3">
         <v>548400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>497900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>469200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>530100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>534700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>484300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>426000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>421700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>411000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>354900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>338000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>349100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>332900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>297300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>311300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>269400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>300500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>275100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>209300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>184400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>171100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>156000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>137200</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>127600</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>119300</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1321,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1419,8 +1439,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>2656700</v>
+        <v>2607100</v>
       </c>
       <c r="E17" s="3">
-        <v>2800700</v>
+        <v>2710900</v>
       </c>
       <c r="F17" s="3">
-        <v>2723500</v>
+        <v>2857900</v>
       </c>
       <c r="G17" s="3">
-        <v>2479800</v>
+        <v>2779100</v>
       </c>
       <c r="H17" s="3">
-        <v>2462900</v>
+        <v>2530400</v>
       </c>
       <c r="I17" s="3">
-        <v>2890400</v>
+        <v>2513100</v>
       </c>
       <c r="J17" s="3">
+        <v>2949400</v>
+      </c>
+      <c r="K17" s="3">
         <v>2719700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2531900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2492200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2723300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2617800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2383300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2260800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2331600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2326500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2065200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1984000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1964500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1740100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1638400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1629700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>531600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1487000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2001600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1860400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1956200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1473400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1479700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1316200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1197200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>925700</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>1053100</v>
+        <v>985900</v>
       </c>
       <c r="E18" s="3">
-        <v>949000</v>
+        <v>1074600</v>
       </c>
       <c r="F18" s="3">
-        <v>1044200</v>
+        <v>968300</v>
       </c>
       <c r="G18" s="3">
-        <v>837600</v>
+        <v>1065500</v>
       </c>
       <c r="H18" s="3">
-        <v>997500</v>
+        <v>854700</v>
       </c>
       <c r="I18" s="3">
-        <v>612500</v>
+        <v>1017900</v>
       </c>
       <c r="J18" s="3">
+        <v>625000</v>
+      </c>
+      <c r="K18" s="3">
         <v>655100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>687600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>760400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>634900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>536600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>534200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>595200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>419300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>422900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>614500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>707800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>458300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>513500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>569000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>573700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>566600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>354900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>334800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>173200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>211700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>378400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>505400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>708200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>562300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>414000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1782,204 +1815,211 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>230200</v>
+        <v>160200</v>
       </c>
       <c r="E20" s="3">
-        <v>121100</v>
+        <v>234800</v>
       </c>
       <c r="F20" s="3">
-        <v>213200</v>
+        <v>123600</v>
       </c>
       <c r="G20" s="3">
-        <v>388100</v>
+        <v>217600</v>
       </c>
       <c r="H20" s="3">
-        <v>154600</v>
+        <v>396000</v>
       </c>
       <c r="I20" s="3">
-        <v>47400</v>
+        <v>157700</v>
       </c>
       <c r="J20" s="3">
+        <v>48300</v>
+      </c>
+      <c r="K20" s="3">
         <v>478800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>109100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>274000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>50600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>118200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>210400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-212200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>39200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>227800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>86200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>152700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>140900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>55000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>49800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>68900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>55200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>50200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-17100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>24600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>32300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>43400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>27100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>105700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>54700</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>1361700</v>
+        <v>1235200</v>
       </c>
       <c r="E21" s="3">
-        <v>1161200</v>
+        <v>1389500</v>
       </c>
       <c r="F21" s="3">
-        <v>1347500</v>
+        <v>1184900</v>
       </c>
       <c r="G21" s="3">
-        <v>1317100</v>
+        <v>1375000</v>
       </c>
       <c r="H21" s="3">
-        <v>1301600</v>
+        <v>1344000</v>
       </c>
       <c r="I21" s="3">
-        <v>766200</v>
+        <v>1328200</v>
       </c>
       <c r="J21" s="3">
+        <v>781800</v>
+      </c>
+      <c r="K21" s="3">
         <v>1232600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>881400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>870100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1024100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>701700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>768200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>919700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>341000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>596700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>973700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>902800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>718200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>762700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>720800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>712200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>734400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>489200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>452600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>208600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>277000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>441900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>574100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>756900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>682100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>481700</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -2076,204 +2116,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>1283300</v>
+        <v>1146100</v>
       </c>
       <c r="E23" s="3">
-        <v>1070000</v>
+        <v>1309500</v>
       </c>
       <c r="F23" s="3">
-        <v>1257400</v>
+        <v>1091900</v>
       </c>
       <c r="G23" s="3">
-        <v>1225700</v>
+        <v>1283100</v>
       </c>
       <c r="H23" s="3">
-        <v>1152100</v>
+        <v>1250700</v>
       </c>
       <c r="I23" s="3">
-        <v>659900</v>
+        <v>1175600</v>
       </c>
       <c r="J23" s="3">
+        <v>673400</v>
+      </c>
+      <c r="K23" s="3">
         <v>1134000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>796800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>764300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>908900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>587200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>652400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>805600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>207100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>462100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>842300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>794000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>611000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>654400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>624000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>623500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>635400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>410100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>385000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>156000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>236300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>410700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>548800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>735300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>668100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>468700</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>205300</v>
+        <v>183400</v>
       </c>
       <c r="E24" s="3">
-        <v>147600</v>
+        <v>209500</v>
       </c>
       <c r="F24" s="3">
-        <v>178300</v>
+        <v>150700</v>
       </c>
       <c r="G24" s="3">
-        <v>98400</v>
+        <v>181900</v>
       </c>
       <c r="H24" s="3">
-        <v>225000</v>
+        <v>100400</v>
       </c>
       <c r="I24" s="3">
-        <v>133500</v>
+        <v>229600</v>
       </c>
       <c r="J24" s="3">
+        <v>136300</v>
+      </c>
+      <c r="K24" s="3">
         <v>219200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>175100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>168400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>128700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>114800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>158200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>177300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>76900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>50500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>156900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>170700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>134900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>13500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>104500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>193500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>132800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>118000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>60300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>40600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>43100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>33500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>104400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>140000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>128300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>62100</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>1078000</v>
+        <v>962700</v>
       </c>
       <c r="E26" s="3">
-        <v>922400</v>
+        <v>1100000</v>
       </c>
       <c r="F26" s="3">
-        <v>1079200</v>
+        <v>941200</v>
       </c>
       <c r="G26" s="3">
-        <v>1127300</v>
+        <v>1101200</v>
       </c>
       <c r="H26" s="3">
-        <v>927100</v>
+        <v>1150300</v>
       </c>
       <c r="I26" s="3">
-        <v>526300</v>
+        <v>946000</v>
       </c>
       <c r="J26" s="3">
+        <v>537100</v>
+      </c>
+      <c r="K26" s="3">
         <v>914800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>621700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>595900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>780200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>472400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>494200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>628300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>130100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>411600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>685400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>623300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>476100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>640900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>519600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>429900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>502600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>292100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>324700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>115500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>193200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>377200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>444400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>595300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>539800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>406500</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>1054700</v>
+        <v>952800</v>
       </c>
       <c r="E27" s="3">
-        <v>909400</v>
+        <v>1076200</v>
       </c>
       <c r="F27" s="3">
-        <v>1082700</v>
+        <v>928000</v>
       </c>
       <c r="G27" s="3">
-        <v>1138800</v>
+        <v>1104800</v>
       </c>
       <c r="H27" s="3">
-        <v>933200</v>
+        <v>1162100</v>
       </c>
       <c r="I27" s="3">
-        <v>546100</v>
+        <v>952300</v>
       </c>
       <c r="J27" s="3">
+        <v>557300</v>
+      </c>
+      <c r="K27" s="3">
         <v>925600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>648800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>606700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>784500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>452300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>503500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>617900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>135800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>441800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>668700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>560200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>470200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>636600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>512500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>417500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>489400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>288700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>302200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>107900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>190800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>375100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>441100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>582200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>535600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2664,16 +2722,19 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
+      <c r="E29" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -2681,26 +2742,26 @@
       <c r="G29" s="3">
         <v>0</v>
       </c>
-      <c r="H29" s="3" t="s">
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>86900</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>37</v>
+      <c r="N29" s="3">
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>37</v>
@@ -2708,14 +2769,14 @@
       <c r="P29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3" t="s">
+      <c r="Q29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="T29" s="3">
         <v>0</v>
@@ -2724,28 +2785,28 @@
         <v>0</v>
       </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>1323600</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-43200</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-53600</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-242900</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-65300</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-230200</v>
+        <v>-160200</v>
       </c>
       <c r="E32" s="3">
-        <v>-121100</v>
+        <v>-234800</v>
       </c>
       <c r="F32" s="3">
-        <v>-213200</v>
+        <v>-123600</v>
       </c>
       <c r="G32" s="3">
-        <v>-388100</v>
+        <v>-217600</v>
       </c>
       <c r="H32" s="3">
-        <v>-154600</v>
+        <v>-396000</v>
       </c>
       <c r="I32" s="3">
-        <v>-47400</v>
+        <v>-157700</v>
       </c>
       <c r="J32" s="3">
+        <v>-48300</v>
+      </c>
+      <c r="K32" s="3">
         <v>-478800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-109100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-274000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-50600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-118200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-210400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>212200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-39200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-227800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-86200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-152700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-140900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-55000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-49800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-68900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-55200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-50200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>17100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-24600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-32300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-43400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-27100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-105700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-54700</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>1054700</v>
+        <v>952800</v>
       </c>
       <c r="E33" s="3">
-        <v>909400</v>
+        <v>1076200</v>
       </c>
       <c r="F33" s="3">
-        <v>1082700</v>
+        <v>928000</v>
       </c>
       <c r="G33" s="3">
-        <v>1138800</v>
+        <v>1104800</v>
       </c>
       <c r="H33" s="3">
-        <v>933200</v>
+        <v>1162100</v>
       </c>
       <c r="I33" s="3">
-        <v>546100</v>
+        <v>952300</v>
       </c>
       <c r="J33" s="3">
+        <v>557300</v>
+      </c>
+      <c r="K33" s="3">
         <v>925600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>735600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>606700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>784500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>452300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>503500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>617900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>135800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>441800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>668700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>560200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>470200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1960200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>469200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>363900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>246600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>223400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>302200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>107900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>190800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>375100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>441100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>582200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>535600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>1054700</v>
+        <v>952800</v>
       </c>
       <c r="E35" s="3">
-        <v>909400</v>
+        <v>1076200</v>
       </c>
       <c r="F35" s="3">
-        <v>1082700</v>
+        <v>928000</v>
       </c>
       <c r="G35" s="3">
-        <v>1138800</v>
+        <v>1104800</v>
       </c>
       <c r="H35" s="3">
-        <v>933200</v>
+        <v>1162100</v>
       </c>
       <c r="I35" s="3">
-        <v>546100</v>
+        <v>952300</v>
       </c>
       <c r="J35" s="3">
+        <v>557300</v>
+      </c>
+      <c r="K35" s="3">
         <v>925600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>735600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>606700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>784500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>452300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>503500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>617900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>135800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>441800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>668700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>560200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>470200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1960200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>469200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>363900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>246600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>223400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>302200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>107900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>190800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>375100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>441100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>582200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>535600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3525,385 +3611,395 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>5944600</v>
+        <v>2676100</v>
       </c>
       <c r="E41" s="3">
-        <v>2960600</v>
+        <v>6065900</v>
       </c>
       <c r="F41" s="3">
-        <v>2088500</v>
+        <v>3021000</v>
       </c>
       <c r="G41" s="3">
-        <v>1763800</v>
+        <v>2131100</v>
       </c>
       <c r="H41" s="3">
-        <v>1892900</v>
+        <v>1799800</v>
       </c>
       <c r="I41" s="3">
-        <v>3438700</v>
+        <v>1931500</v>
       </c>
       <c r="J41" s="3">
+        <v>3508900</v>
+      </c>
+      <c r="K41" s="3">
         <v>2486800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2288500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1360400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1997600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3165200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1412400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1223700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1269100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>952900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1565400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>882300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>499900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>422100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>738300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>631300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>724500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>668700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>441800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>534800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>410200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>382200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>447100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>587600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>791100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>651800</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>12651100</v>
+        <v>14644200</v>
       </c>
       <c r="E42" s="3">
-        <v>14547200</v>
+        <v>12909400</v>
       </c>
       <c r="F42" s="3">
-        <v>13223400</v>
+        <v>14844100</v>
       </c>
       <c r="G42" s="3">
-        <v>13407300</v>
+        <v>13493300</v>
       </c>
       <c r="H42" s="3">
-        <v>14747800</v>
+        <v>13681000</v>
       </c>
       <c r="I42" s="3">
-        <v>12789500</v>
+        <v>15048800</v>
       </c>
       <c r="J42" s="3">
+        <v>13050600</v>
+      </c>
+      <c r="K42" s="3">
         <v>13572300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>13218500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>12793000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>11440800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>9817800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>12928100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>12628000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>11741800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>13547400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>12606300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>11025600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>10593800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>9029400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>7748900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>7283200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>6473600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>5270700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>5889700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>5683300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>5987800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>5655100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>5658600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>5370000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>4500100</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>3836200</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>1073200</v>
+        <v>897300</v>
       </c>
       <c r="E43" s="3">
-        <v>887300</v>
+        <v>1095100</v>
       </c>
       <c r="F43" s="3">
-        <v>897000</v>
+        <v>905400</v>
       </c>
       <c r="G43" s="3">
-        <v>738200</v>
+        <v>915300</v>
       </c>
       <c r="H43" s="3">
-        <v>841600</v>
+        <v>753300</v>
       </c>
       <c r="I43" s="3">
-        <v>691200</v>
+        <v>858800</v>
       </c>
       <c r="J43" s="3">
+        <v>705300</v>
+      </c>
+      <c r="K43" s="3">
         <v>719500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>724700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>728700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>758900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>770800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>632900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>703900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>637000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>729300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>739500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>719300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>642000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>724700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>686700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>774700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>598200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>639500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>554400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>637900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>537200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>483700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>505200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>546600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>618300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>387100</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>83400</v>
+        <v>81000</v>
       </c>
       <c r="E44" s="3">
-        <v>96100</v>
+        <v>85100</v>
       </c>
       <c r="F44" s="3">
-        <v>99700</v>
+        <v>98000</v>
       </c>
       <c r="G44" s="3">
-        <v>111500</v>
+        <v>101800</v>
       </c>
       <c r="H44" s="3">
-        <v>121100</v>
+        <v>113800</v>
       </c>
       <c r="I44" s="3">
-        <v>137300</v>
+        <v>123500</v>
       </c>
       <c r="J44" s="3">
+        <v>140100</v>
+      </c>
+      <c r="K44" s="3">
         <v>128900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>117300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>118900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>132900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>147600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>125700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>121800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>86500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>77300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>82300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>88700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>100200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>105700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>606000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>653500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>154800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>880500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>814400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>734800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>812500</v>
-      </c>
-      <c r="AD44" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="AE44" s="3" t="s">
         <v>37</v>
@@ -3911,406 +4007,421 @@
       <c r="AF44" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AG44" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH44" s="3">
         <v>229500</v>
       </c>
-      <c r="AH44" s="3" t="s">
+      <c r="AI44" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1219300</v>
+        <v>1178300</v>
       </c>
       <c r="E45" s="3">
-        <v>1223200</v>
+        <v>1244100</v>
       </c>
       <c r="F45" s="3">
-        <v>1315900</v>
+        <v>1248200</v>
       </c>
       <c r="G45" s="3">
-        <v>1142000</v>
+        <v>1342700</v>
       </c>
       <c r="H45" s="3">
-        <v>1123900</v>
+        <v>1165300</v>
       </c>
       <c r="I45" s="3">
-        <v>1125600</v>
+        <v>1146800</v>
       </c>
       <c r="J45" s="3">
+        <v>1148600</v>
+      </c>
+      <c r="K45" s="3">
         <v>1273300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1446800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1440700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1255600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1584900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1384500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1404200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1275600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1457600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1380100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1517400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1268600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2428400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1379700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1603500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2028600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1351100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1249200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1503400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1445900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2209500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1940600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1537400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1120900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>922600</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>20971600</v>
+        <v>19476800</v>
       </c>
       <c r="E46" s="3">
-        <v>19714400</v>
+        <v>21399700</v>
       </c>
       <c r="F46" s="3">
-        <v>17624400</v>
+        <v>20116800</v>
       </c>
       <c r="G46" s="3">
-        <v>17162800</v>
+        <v>17984200</v>
       </c>
       <c r="H46" s="3">
-        <v>18727200</v>
+        <v>17513100</v>
       </c>
       <c r="I46" s="3">
-        <v>18182300</v>
+        <v>19109500</v>
       </c>
       <c r="J46" s="3">
+        <v>18553400</v>
+      </c>
+      <c r="K46" s="3">
         <v>18180800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>17795800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>16441700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>15585700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>15486300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>16483600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>16081600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>15010100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>16764400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>16373600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>14233300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>13104500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>12710400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>11159600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>10946200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>9979600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>8810600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>8949500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>9094200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>9193700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>8730600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>8551400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>8041600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>7181800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>5797700</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>145100</v>
+        <v>555500</v>
       </c>
       <c r="E47" s="3">
-        <v>3154600</v>
+        <v>148000</v>
       </c>
       <c r="F47" s="3">
-        <v>306800</v>
+        <v>3219000</v>
       </c>
       <c r="G47" s="3">
-        <v>370500</v>
+        <v>313100</v>
       </c>
       <c r="H47" s="3">
-        <v>377400</v>
+        <v>378100</v>
       </c>
       <c r="I47" s="3">
-        <v>2973000</v>
+        <v>385100</v>
       </c>
       <c r="J47" s="3">
+        <v>3033600</v>
+      </c>
+      <c r="K47" s="3">
         <v>618100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>622000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>617700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3393300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>988400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1009300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>938200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2553100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>626300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1005500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>607400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1794500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7700</v>
-      </c>
-      <c r="W47" s="3">
-        <v>7600</v>
       </c>
       <c r="X47" s="3">
         <v>7600</v>
       </c>
       <c r="Y47" s="3">
+        <v>7600</v>
+      </c>
+      <c r="Z47" s="3">
         <v>776400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>21000</v>
-      </c>
-      <c r="AA47" s="3">
-        <v>21500</v>
       </c>
       <c r="AB47" s="3">
         <v>21500</v>
       </c>
       <c r="AC47" s="3">
+        <v>21500</v>
+      </c>
+      <c r="AD47" s="3">
         <v>413300</v>
-      </c>
-      <c r="AD47" s="3">
-        <v>7400</v>
       </c>
       <c r="AE47" s="3">
         <v>7400</v>
       </c>
       <c r="AF47" s="3">
+        <v>7400</v>
+      </c>
+      <c r="AG47" s="3">
         <v>74200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>366500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1113100</v>
+        <v>1140800</v>
       </c>
       <c r="E48" s="3">
-        <v>1219200</v>
+        <v>1135800</v>
       </c>
       <c r="F48" s="3">
-        <v>1047600</v>
+        <v>1244100</v>
       </c>
       <c r="G48" s="3">
-        <v>1015100</v>
+        <v>1069000</v>
       </c>
       <c r="H48" s="3">
-        <v>914300</v>
+        <v>1035800</v>
       </c>
       <c r="I48" s="3">
-        <v>998900</v>
+        <v>933000</v>
       </c>
       <c r="J48" s="3">
+        <v>1019300</v>
+      </c>
+      <c r="K48" s="3">
         <v>851800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>837200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>806700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>892500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>704600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>667300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>647500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>741700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>654200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>650800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1302800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1353900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1301600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>945300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>944100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>678700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>742600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>699200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>611500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>559400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>498100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>442500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>398600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>351900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>314500</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4377,38 +4488,41 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-      <c r="Y49" s="3" t="s">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>492700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>84200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>84700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>88000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>88500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>86500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>86900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>85600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>86100</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4720400</v>
+        <v>4674500</v>
       </c>
       <c r="E52" s="3">
-        <v>1599200</v>
+        <v>4816700</v>
       </c>
       <c r="F52" s="3">
-        <v>4726000</v>
+        <v>1631800</v>
       </c>
       <c r="G52" s="3">
-        <v>4649500</v>
+        <v>4822400</v>
       </c>
       <c r="H52" s="3">
-        <v>4606900</v>
+        <v>4744400</v>
       </c>
       <c r="I52" s="3">
-        <v>1714500</v>
+        <v>4700900</v>
       </c>
       <c r="J52" s="3">
+        <v>1749500</v>
+      </c>
+      <c r="K52" s="3">
         <v>4210700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4125300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4122900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1297500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3828800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3852800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3282900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1444000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3282800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3215000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2575400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1012100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2275000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2065600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2072100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1957600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1128300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1064000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>773500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>287400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>544500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>588900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>726800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>453800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>847100</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>26950200</v>
+        <v>25847600</v>
       </c>
       <c r="E54" s="3">
-        <v>25687400</v>
+        <v>27500200</v>
       </c>
       <c r="F54" s="3">
-        <v>23704800</v>
+        <v>26211700</v>
       </c>
       <c r="G54" s="3">
-        <v>23197900</v>
+        <v>24188600</v>
       </c>
       <c r="H54" s="3">
-        <v>24625800</v>
+        <v>23671300</v>
       </c>
       <c r="I54" s="3">
-        <v>23868700</v>
+        <v>25128500</v>
       </c>
       <c r="J54" s="3">
+        <v>24355800</v>
+      </c>
+      <c r="K54" s="3">
         <v>23861300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23380300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21989000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21169100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21008100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>22012900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>20950100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>19748900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>21327700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>21244900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>18718800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>17264900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>16294800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>14178000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>13970100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>12630400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>11195300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>10818400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>10585300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>10541800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>9869200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>9676800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>9328300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>8439600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>7221400</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,436 +5099,449 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>120400</v>
+        <v>111700</v>
       </c>
       <c r="E57" s="3">
+        <v>122900</v>
+      </c>
+      <c r="F57" s="3">
+        <v>124200</v>
+      </c>
+      <c r="G57" s="3">
         <v>121700</v>
       </c>
-      <c r="F57" s="3">
-        <v>119300</v>
-      </c>
-      <c r="G57" s="3">
-        <v>102300</v>
-      </c>
       <c r="H57" s="3">
-        <v>114800</v>
+        <v>104400</v>
       </c>
       <c r="I57" s="3">
-        <v>208200</v>
+        <v>117200</v>
       </c>
       <c r="J57" s="3">
+        <v>212500</v>
+      </c>
+      <c r="K57" s="3">
         <v>119800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>131000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>127700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>135700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>156200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>126500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>149100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>157900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>146900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>125800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>188800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>186700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>187800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>398700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>450600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>174500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>360300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>331200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>339400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>362500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>307000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>281800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>234400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>203000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>110800</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3432400</v>
+        <v>1859100</v>
       </c>
       <c r="E58" s="3">
-        <v>2658200</v>
+        <v>3502400</v>
       </c>
       <c r="F58" s="3">
-        <v>1550300</v>
+        <v>2712500</v>
       </c>
       <c r="G58" s="3">
-        <v>1641600</v>
+        <v>1582000</v>
       </c>
       <c r="H58" s="3">
-        <v>3784600</v>
+        <v>1675100</v>
       </c>
       <c r="I58" s="3">
-        <v>3298700</v>
+        <v>3861800</v>
       </c>
       <c r="J58" s="3">
+        <v>3366000</v>
+      </c>
+      <c r="K58" s="3">
         <v>3515600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3896300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3131600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2666400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2788200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3864800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3038300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2715100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3278400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3232000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3096000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2591200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2385900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2070800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2159500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1983600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1909900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1825900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1365400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>983000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>850800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>798100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>665400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>554900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>437000</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4743700</v>
+        <v>4504100</v>
       </c>
       <c r="E59" s="3">
-        <v>4658900</v>
+        <v>4840500</v>
       </c>
       <c r="F59" s="3">
-        <v>4391300</v>
+        <v>4754000</v>
       </c>
       <c r="G59" s="3">
-        <v>4105700</v>
+        <v>4480900</v>
       </c>
       <c r="H59" s="3">
-        <v>4138800</v>
+        <v>4189500</v>
       </c>
       <c r="I59" s="3">
-        <v>4344600</v>
+        <v>4223300</v>
       </c>
       <c r="J59" s="3">
+        <v>4433300</v>
+      </c>
+      <c r="K59" s="3">
         <v>4243700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3958700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3888400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4156000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4022200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3733400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3862800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3633700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3490100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3302200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3563100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3110800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2755700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2714800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2925100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2940700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2365900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2092900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2295300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2179300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1824600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1916500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2096200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2083000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1540700</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>8296400</v>
+        <v>6474900</v>
       </c>
       <c r="E60" s="3">
-        <v>7438900</v>
+        <v>8465800</v>
       </c>
       <c r="F60" s="3">
-        <v>6060900</v>
+        <v>7590700</v>
       </c>
       <c r="G60" s="3">
-        <v>5849600</v>
+        <v>6184600</v>
       </c>
       <c r="H60" s="3">
-        <v>8038200</v>
+        <v>5968900</v>
       </c>
       <c r="I60" s="3">
-        <v>7851500</v>
+        <v>8202300</v>
       </c>
       <c r="J60" s="3">
+        <v>8011700</v>
+      </c>
+      <c r="K60" s="3">
         <v>7879100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7986000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7147600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6958100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6966500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7724700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7050200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6506700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6915400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6660000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6848000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5888700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5329300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5184200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5535100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5098900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4636100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4250000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4000100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3524800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2982400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2996300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2995900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2788800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2088600</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>59100</v>
+        <v>60300</v>
       </c>
       <c r="E61" s="3">
-        <v>59100</v>
+        <v>60300</v>
       </c>
       <c r="F61" s="3">
-        <v>59100</v>
+        <v>60300</v>
       </c>
       <c r="G61" s="3">
-        <v>546200</v>
+        <v>60300</v>
       </c>
       <c r="H61" s="3">
+        <v>557400</v>
+      </c>
+      <c r="I61" s="3">
+        <v>525900</v>
+      </c>
+      <c r="J61" s="3">
         <v>515300</v>
       </c>
-      <c r="I61" s="3">
-        <v>505000</v>
-      </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>490500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>466500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>438300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>175700</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -5459,106 +5602,112 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>545600</v>
+        <v>372400</v>
       </c>
       <c r="E62" s="3">
-        <v>493300</v>
+        <v>556700</v>
       </c>
       <c r="F62" s="3">
-        <v>460500</v>
+        <v>503400</v>
       </c>
       <c r="G62" s="3">
-        <v>462500</v>
+        <v>469900</v>
       </c>
       <c r="H62" s="3">
-        <v>505300</v>
+        <v>471900</v>
       </c>
       <c r="I62" s="3">
-        <v>470300</v>
+        <v>515600</v>
       </c>
       <c r="J62" s="3">
+        <v>479900</v>
+      </c>
+      <c r="K62" s="3">
         <v>342600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>343700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>350100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>336700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>331200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>284400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>241500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>186100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>154400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>214700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>166100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>129300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>185900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>210400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>168600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>65000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>87600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>84800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>60500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>34400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>17800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>41800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>27800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>57100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>9365700</v>
+        <v>7392000</v>
       </c>
       <c r="E66" s="3">
-        <v>8516100</v>
+        <v>9556900</v>
       </c>
       <c r="F66" s="3">
-        <v>7128500</v>
+        <v>8689900</v>
       </c>
       <c r="G66" s="3">
-        <v>7411000</v>
+        <v>7274000</v>
       </c>
       <c r="H66" s="3">
-        <v>9615800</v>
+        <v>7562300</v>
       </c>
       <c r="I66" s="3">
-        <v>9399000</v>
+        <v>9812100</v>
       </c>
       <c r="J66" s="3">
+        <v>9590800</v>
+      </c>
+      <c r="K66" s="3">
         <v>9304100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9362800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>8502500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>8034800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9098800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9768700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9019800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8316900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8765700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8600700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8843500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7802300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6535300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6393700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>6672100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>6061400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5124400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4561000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4202100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3754700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3188400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3215300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3151400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2885400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2130900</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,19 +6548,22 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E72" s="3">
-        <v>15716500</v>
-      </c>
-      <c r="F72" s="3" t="s">
+      <c r="E72" s="3" t="s">
         <v>37</v>
+      </c>
+      <c r="F72" s="3">
+        <v>16037300</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>37</v>
@@ -6397,11 +6571,11 @@
       <c r="H72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I72" s="3">
-        <v>12759500</v>
-      </c>
-      <c r="J72" s="3" t="s">
+      <c r="I72" s="3" t="s">
         <v>37</v>
+      </c>
+      <c r="J72" s="3">
+        <v>13020000</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>37</v>
@@ -6409,11 +6583,11 @@
       <c r="L72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="N72" s="3">
         <v>10848700</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>37</v>
@@ -6421,11 +6595,11 @@
       <c r="P72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="R72" s="3">
         <v>9102400</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>37</v>
@@ -6433,11 +6607,11 @@
       <c r="T72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="V72" s="3">
         <v>8870600</v>
-      </c>
-      <c r="V72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="W72" s="3" t="s">
         <v>37</v>
@@ -6445,11 +6619,11 @@
       <c r="X72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z72" s="3">
         <v>6566100</v>
-      </c>
-      <c r="Z72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="AA72" s="3" t="s">
         <v>37</v>
@@ -6469,14 +6643,17 @@
       <c r="AF72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH72" s="3">
         <v>5306600</v>
       </c>
-      <c r="AH72" s="3" t="s">
+      <c r="AI72" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>17584400</v>
+        <v>18455700</v>
       </c>
       <c r="E76" s="3">
-        <v>17171300</v>
+        <v>17943300</v>
       </c>
       <c r="F76" s="3">
-        <v>16576300</v>
+        <v>17521800</v>
       </c>
       <c r="G76" s="3">
-        <v>15786800</v>
+        <v>16914600</v>
       </c>
       <c r="H76" s="3">
-        <v>15010000</v>
+        <v>16109000</v>
       </c>
       <c r="I76" s="3">
-        <v>14469700</v>
+        <v>15316400</v>
       </c>
       <c r="J76" s="3">
+        <v>14765000</v>
+      </c>
+      <c r="K76" s="3">
         <v>14557200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14017500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13486500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13134300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11909300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12244200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11930300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11432100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12562000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12644200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9875400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9462600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9759400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7784300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7298000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>6569000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6070900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6257400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6383200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6787100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6680800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6461500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6176800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5554100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5090500</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>1054700</v>
+        <v>952800</v>
       </c>
       <c r="E81" s="3">
-        <v>909400</v>
+        <v>1076200</v>
       </c>
       <c r="F81" s="3">
-        <v>1082700</v>
+        <v>928000</v>
       </c>
       <c r="G81" s="3">
-        <v>1138800</v>
+        <v>1104800</v>
       </c>
       <c r="H81" s="3">
-        <v>933200</v>
+        <v>1162100</v>
       </c>
       <c r="I81" s="3">
-        <v>546100</v>
+        <v>952300</v>
       </c>
       <c r="J81" s="3">
+        <v>557300</v>
+      </c>
+      <c r="K81" s="3">
         <v>925600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>735600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>606700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>784500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>452300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>503500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>617900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>135800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>441800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>668700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>560200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>470200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1960200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>469200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>363900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>246600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>223400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>302200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>107900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>190800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>375100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>441100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>582200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>535600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,106 +7400,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>78500</v>
+        <v>89100</v>
       </c>
       <c r="E83" s="3">
-        <v>91200</v>
+        <v>80100</v>
       </c>
       <c r="F83" s="3">
-        <v>90100</v>
+        <v>93000</v>
       </c>
       <c r="G83" s="3">
-        <v>91400</v>
+        <v>91900</v>
       </c>
       <c r="H83" s="3">
-        <v>149500</v>
+        <v>93200</v>
       </c>
       <c r="I83" s="3">
-        <v>106300</v>
+        <v>152600</v>
       </c>
       <c r="J83" s="3">
+        <v>108400</v>
+      </c>
+      <c r="K83" s="3">
         <v>98600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>84700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>105800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>115200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>114500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>115800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>114100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>134000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>134500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>131500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>108900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>107100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>106000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>98100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>89700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>98200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>79800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>67600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>52600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>40700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>31300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>25300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>21700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>14100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1320400</v>
+        <v>920900</v>
       </c>
       <c r="E89" s="3">
-        <v>1631400</v>
+        <v>1347400</v>
       </c>
       <c r="F89" s="3">
-        <v>1360000</v>
+        <v>1664700</v>
       </c>
       <c r="G89" s="3">
-        <v>1060800</v>
+        <v>1387800</v>
       </c>
       <c r="H89" s="3">
-        <v>829100</v>
+        <v>1082500</v>
       </c>
       <c r="I89" s="3">
-        <v>1244700</v>
+        <v>846000</v>
       </c>
       <c r="J89" s="3">
+        <v>1270100</v>
+      </c>
+      <c r="K89" s="3">
         <v>1034300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>921900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>632800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1153000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>894500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>671300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>771500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1143400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>795900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>703200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1025500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>848500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>593400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>682300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>517400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>862000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>506300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>280900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>273300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>576000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>245700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>344500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>598300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>782200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>542400</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-568400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-603800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-606700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1385700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-803900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1479600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-510800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-709300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-530200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-893200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-739700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-625900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-988600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-45900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-42200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-51700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-34900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-25900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-36300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-50800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-41900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-56500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-73400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-80900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-111200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-96200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-84900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-76000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-64300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-48300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-67700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-24400</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>1776700</v>
+        <v>-2093700</v>
       </c>
       <c r="E94" s="3">
-        <v>-1481700</v>
+        <v>1813000</v>
       </c>
       <c r="F94" s="3">
-        <v>-71300</v>
+        <v>-1512000</v>
       </c>
       <c r="G94" s="3">
-        <v>1601200</v>
+        <v>-72700</v>
       </c>
       <c r="H94" s="3">
-        <v>-2402900</v>
+        <v>1633900</v>
       </c>
       <c r="I94" s="3">
-        <v>533900</v>
+        <v>-2452000</v>
       </c>
       <c r="J94" s="3">
+        <v>544800</v>
+      </c>
+      <c r="K94" s="3">
         <v>136400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-164500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1524100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2144900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>3007600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-788000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-991800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>145500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1105500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2985100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-391000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1069600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1090100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-514900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-724400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1195600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-55800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-555300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-153300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-592900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-140100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-343300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-831600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-670000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-658900</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,106 +8585,110 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-683200</v>
+        <v>-319300</v>
       </c>
       <c r="E96" s="3">
-        <v>-312100</v>
+        <v>-697100</v>
       </c>
       <c r="F96" s="3">
-        <v>-334800</v>
+        <v>-318500</v>
       </c>
       <c r="G96" s="3">
-        <v>-292800</v>
+        <v>-341600</v>
       </c>
       <c r="H96" s="3">
-        <v>-167500</v>
+        <v>-298800</v>
       </c>
       <c r="I96" s="3">
-        <v>-278900</v>
+        <v>-170900</v>
       </c>
       <c r="J96" s="3">
+        <v>-284600</v>
+      </c>
+      <c r="K96" s="3">
         <v>-223500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-195100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-232500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-129600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-146100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-181800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-36300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-119900</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-203000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-164300</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-146200</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1061000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-142200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-93700</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-63200</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-58000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-74700</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-27500</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-45300</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-92700</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-109200</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-145500</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-136100</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-100700</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-99400</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-68400</v>
+        <v>-2244300</v>
       </c>
       <c r="E100" s="3">
-        <v>710000</v>
+        <v>-69800</v>
       </c>
       <c r="F100" s="3">
-        <v>-946900</v>
+        <v>724500</v>
       </c>
       <c r="G100" s="3">
-        <v>-2808100</v>
+        <v>-966200</v>
       </c>
       <c r="H100" s="3">
-        <v>79100</v>
+        <v>-2865400</v>
       </c>
       <c r="I100" s="3">
-        <v>-854200</v>
+        <v>80700</v>
       </c>
       <c r="J100" s="3">
+        <v>-871600</v>
+      </c>
+      <c r="K100" s="3">
         <v>-992700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>116900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>316100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-147900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2117200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>281100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>195600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-887500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-367800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2973500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-219900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>180400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>112800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-188300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>62800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>406100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-127900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-41900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-6900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-171000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-31700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>16300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>17200</v>
       </c>
-      <c r="AH100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-6000</v>
+        <v>1200</v>
       </c>
       <c r="E101" s="3">
-        <v>-24100</v>
+        <v>-6100</v>
       </c>
       <c r="F101" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="G101" s="3">
         <v>600</v>
       </c>
-      <c r="G101" s="3">
-        <v>-6600</v>
-      </c>
       <c r="H101" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="I101" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J101" s="3">
+        <v>7500</v>
+      </c>
+      <c r="K101" s="3">
+        <v>500</v>
+      </c>
+      <c r="L101" s="3">
+        <v>10400</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="O101" s="3">
         <v>2100</v>
       </c>
-      <c r="I101" s="3">
-        <v>7400</v>
-      </c>
-      <c r="J101" s="3">
-        <v>500</v>
-      </c>
-      <c r="K101" s="3">
-        <v>10400</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-11100</v>
-      </c>
-      <c r="N101" s="3">
-        <v>2100</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>5000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-9400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-3700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>26500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>11700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-4100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>5900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>5400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>7600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>11200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>4000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>9900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>3022800</v>
+        <v>-3416000</v>
       </c>
       <c r="E102" s="3">
-        <v>835700</v>
+        <v>3084500</v>
       </c>
       <c r="F102" s="3">
-        <v>342500</v>
+        <v>852700</v>
       </c>
       <c r="G102" s="3">
-        <v>-152700</v>
+        <v>349400</v>
       </c>
       <c r="H102" s="3">
-        <v>-1492600</v>
+        <v>-155800</v>
       </c>
       <c r="I102" s="3">
-        <v>931700</v>
+        <v>-1523100</v>
       </c>
       <c r="J102" s="3">
+        <v>950800</v>
+      </c>
+      <c r="K102" s="3">
         <v>178500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>884700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-578200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1150900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1786900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>160900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-19700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>392000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-681100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>718200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>426300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-44800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-378000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-15500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-146900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>70400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>330100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-305100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>114500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-25400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-61500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-34000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-217600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>139300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-112800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NTES_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NTES_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
   <si>
     <t>NTES</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3593000</v>
+        <v>3736500</v>
       </c>
       <c r="E8" s="3">
-        <v>3785600</v>
+        <v>3507100</v>
       </c>
       <c r="F8" s="3">
-        <v>3826200</v>
+        <v>3718800</v>
       </c>
       <c r="G8" s="3">
-        <v>3844600</v>
+        <v>3827500</v>
       </c>
       <c r="H8" s="3">
-        <v>3385100</v>
+        <v>3737400</v>
       </c>
       <c r="I8" s="3">
-        <v>3531000</v>
+        <v>3310900</v>
       </c>
       <c r="J8" s="3">
+        <v>3646200</v>
+      </c>
+      <c r="K8" s="3">
         <v>3574400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3374800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3219600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3252600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3358200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3154400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2917600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2856000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2750800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2749500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2679700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2691800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2422800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2253600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2207400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2203400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1098200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1841900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2336400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2033500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2167900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1851800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1985100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2024400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1759600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1339600</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1331400</v>
+        <v>1387600</v>
       </c>
       <c r="E9" s="3">
-        <v>1386700</v>
+        <v>1299500</v>
       </c>
       <c r="F9" s="3">
-        <v>1454200</v>
+        <v>1362200</v>
       </c>
       <c r="G9" s="3">
-        <v>1452700</v>
+        <v>1454700</v>
       </c>
       <c r="H9" s="3">
-        <v>1358500</v>
+        <v>1412200</v>
       </c>
       <c r="I9" s="3">
-        <v>1430900</v>
+        <v>1328700</v>
       </c>
       <c r="J9" s="3">
+        <v>1477600</v>
+      </c>
+      <c r="K9" s="3">
         <v>1707200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1475900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1420400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1480100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1578400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1475500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1327000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1317500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1368900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1292700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1236700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1212300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1131300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1041700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1025400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1021300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>92700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>830800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1296900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1179300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1315400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>969100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>985300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>913700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>819600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>564000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2261600</v>
+        <v>2348900</v>
       </c>
       <c r="E10" s="3">
-        <v>2398900</v>
+        <v>2207600</v>
       </c>
       <c r="F10" s="3">
-        <v>2372000</v>
+        <v>2356600</v>
       </c>
       <c r="G10" s="3">
-        <v>2391900</v>
+        <v>2372800</v>
       </c>
       <c r="H10" s="3">
-        <v>2026600</v>
+        <v>2325200</v>
       </c>
       <c r="I10" s="3">
-        <v>2100100</v>
+        <v>1982200</v>
       </c>
       <c r="J10" s="3">
+        <v>2168600</v>
+      </c>
+      <c r="K10" s="3">
         <v>1867200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1898900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1799100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1772400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1779800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1678900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1590600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1538500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1381900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1456800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1443000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1479400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1291500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1211900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1182000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1182200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1005500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1011100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1039500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>854200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>852600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>882700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>999800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1110600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>940000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>775700</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,109 +1152,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>628200</v>
+        <v>630800</v>
       </c>
       <c r="E12" s="3">
-        <v>588600</v>
+        <v>613200</v>
       </c>
       <c r="F12" s="3">
-        <v>631500</v>
+        <v>578200</v>
       </c>
       <c r="G12" s="3">
-        <v>612800</v>
+        <v>631700</v>
       </c>
       <c r="H12" s="3">
-        <v>551100</v>
+        <v>595800</v>
       </c>
       <c r="I12" s="3">
-        <v>528600</v>
+        <v>539000</v>
       </c>
       <c r="J12" s="3">
+        <v>545900</v>
+      </c>
+      <c r="K12" s="3">
         <v>576600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>548400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>497900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>469200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>530100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>534700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>484300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>426000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>421700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>411000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>354900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>338000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>349100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>332900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>297300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>311300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>269400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>300500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>275100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>209300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>184400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>171100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>156000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>137200</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>127600</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>119300</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1341,31 +1358,34 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1442,31 +1462,34 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>74200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>87000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>78700</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>93000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>89300</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>91200</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>157600</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>2607100</v>
+        <v>2717700</v>
       </c>
       <c r="E17" s="3">
-        <v>2710900</v>
+        <v>2544800</v>
       </c>
       <c r="F17" s="3">
-        <v>2857900</v>
+        <v>2663100</v>
       </c>
       <c r="G17" s="3">
-        <v>2779100</v>
+        <v>2858800</v>
       </c>
       <c r="H17" s="3">
-        <v>2530400</v>
+        <v>2701600</v>
       </c>
       <c r="I17" s="3">
-        <v>2513100</v>
+        <v>2474900</v>
       </c>
       <c r="J17" s="3">
+        <v>2595100</v>
+      </c>
+      <c r="K17" s="3">
         <v>2949400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2719700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2531900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2492200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2723300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2617800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2383300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2260800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2331600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2326500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2065200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1984000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1964500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1740100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1638400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1629700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>531600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1487000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2001600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1860400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1956200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1473400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1479700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1316200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1197200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>925700</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>985900</v>
+        <v>1018900</v>
       </c>
       <c r="E18" s="3">
-        <v>1074600</v>
+        <v>962400</v>
       </c>
       <c r="F18" s="3">
-        <v>968300</v>
+        <v>1055700</v>
       </c>
       <c r="G18" s="3">
-        <v>1065500</v>
+        <v>968600</v>
       </c>
       <c r="H18" s="3">
-        <v>854700</v>
+        <v>1035800</v>
       </c>
       <c r="I18" s="3">
-        <v>1017900</v>
+        <v>836000</v>
       </c>
       <c r="J18" s="3">
+        <v>1051100</v>
+      </c>
+      <c r="K18" s="3">
         <v>625000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>655100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>687600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>760400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>634900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>536600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>534200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>595200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>419300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>422900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>614500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>707800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>458300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>513500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>569000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>573700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>566600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>354900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>334800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>173200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>211700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>378400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>505400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>708200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>562300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>414000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1816,233 +1849,240 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>160200</v>
+        <v>144300</v>
       </c>
       <c r="E20" s="3">
-        <v>234800</v>
+        <v>21100</v>
       </c>
       <c r="F20" s="3">
-        <v>123600</v>
+        <v>-28900</v>
       </c>
       <c r="G20" s="3">
-        <v>217600</v>
+        <v>53000</v>
       </c>
       <c r="H20" s="3">
-        <v>396000</v>
+        <v>22000</v>
       </c>
       <c r="I20" s="3">
-        <v>157700</v>
+        <v>-218700</v>
       </c>
       <c r="J20" s="3">
+        <v>18700</v>
+      </c>
+      <c r="K20" s="3">
         <v>48300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>478800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>109100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>274000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>50600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>118200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>210400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-212200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>39200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>227800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>86200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>152700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>140900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>55000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>49800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>68900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>55200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>50200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-17100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>24600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>32300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>43400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>27100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>105700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>54700</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>1235200</v>
+        <v>948800</v>
       </c>
       <c r="E21" s="3">
-        <v>1389500</v>
+        <v>1028200</v>
       </c>
       <c r="F21" s="3">
-        <v>1184900</v>
+        <v>1163300</v>
       </c>
       <c r="G21" s="3">
-        <v>1375000</v>
+        <v>1008600</v>
       </c>
       <c r="H21" s="3">
-        <v>1344000</v>
+        <v>1103200</v>
       </c>
       <c r="I21" s="3">
-        <v>1328200</v>
+        <v>1145800</v>
       </c>
       <c r="J21" s="3">
+        <v>1189900</v>
+      </c>
+      <c r="K21" s="3">
         <v>781800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1232600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>881400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>870100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1024100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>701700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>768200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>919700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>341000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>596700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>973700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>902800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>718200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>762700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>720800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>712200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>734400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>489200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>452600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>208600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>277000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>441900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>574100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>756900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>682100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>481700</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+        <v>124700</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2119,210 +2159,219 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>1146100</v>
+        <v>1139900</v>
       </c>
       <c r="E23" s="3">
-        <v>1309500</v>
+        <v>1118700</v>
       </c>
       <c r="F23" s="3">
-        <v>1091900</v>
+        <v>1286400</v>
       </c>
       <c r="G23" s="3">
-        <v>1283100</v>
+        <v>1092200</v>
       </c>
       <c r="H23" s="3">
-        <v>1250700</v>
+        <v>1247300</v>
       </c>
       <c r="I23" s="3">
-        <v>1175600</v>
+        <v>1223300</v>
       </c>
       <c r="J23" s="3">
+        <v>1214000</v>
+      </c>
+      <c r="K23" s="3">
         <v>673400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1134000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>796800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>764300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>908900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>587200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>652400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>805600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>207100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>462100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>842300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>794000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>611000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>654400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>624000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>623500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>635400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>410100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>385000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>156000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>236300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>410700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>548800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>735300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>668100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>468700</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>183400</v>
+        <v>183800</v>
       </c>
       <c r="E24" s="3">
-        <v>209500</v>
+        <v>179000</v>
       </c>
       <c r="F24" s="3">
+        <v>205800</v>
+      </c>
+      <c r="G24" s="3">
         <v>150700</v>
       </c>
-      <c r="G24" s="3">
-        <v>181900</v>
-      </c>
       <c r="H24" s="3">
-        <v>100400</v>
+        <v>176800</v>
       </c>
       <c r="I24" s="3">
-        <v>229600</v>
+        <v>98200</v>
       </c>
       <c r="J24" s="3">
+        <v>237100</v>
+      </c>
+      <c r="K24" s="3">
         <v>136300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>219200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>175100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>168400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>128700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>114800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>158200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>177300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>76900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>50500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>156900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>170700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>134900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>13500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>104500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>193500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>132800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>118000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>60300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>40600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>43100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>33500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>104400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>140000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>128300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>62100</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>962700</v>
+        <v>956100</v>
       </c>
       <c r="E26" s="3">
-        <v>1100000</v>
+        <v>939700</v>
       </c>
       <c r="F26" s="3">
-        <v>941200</v>
+        <v>1080600</v>
       </c>
       <c r="G26" s="3">
-        <v>1101200</v>
+        <v>941500</v>
       </c>
       <c r="H26" s="3">
-        <v>1150300</v>
+        <v>1070500</v>
       </c>
       <c r="I26" s="3">
-        <v>946000</v>
+        <v>1125100</v>
       </c>
       <c r="J26" s="3">
+        <v>976900</v>
+      </c>
+      <c r="K26" s="3">
         <v>537100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>914800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>621700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>595900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>780200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>472400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>494200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>628300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>130100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>411600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>685400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>623300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>476100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>640900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>519600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>429900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>502600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>292100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>324700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>115500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>193200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>377200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>444400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>595300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>539800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>406500</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>952800</v>
+        <v>932100</v>
       </c>
       <c r="E27" s="3">
-        <v>1076200</v>
+        <v>930100</v>
       </c>
       <c r="F27" s="3">
-        <v>928000</v>
+        <v>1057300</v>
       </c>
       <c r="G27" s="3">
-        <v>1104800</v>
+        <v>928300</v>
       </c>
       <c r="H27" s="3">
-        <v>1162100</v>
+        <v>1074000</v>
       </c>
       <c r="I27" s="3">
-        <v>952300</v>
+        <v>1136600</v>
       </c>
       <c r="J27" s="3">
+        <v>983300</v>
+      </c>
+      <c r="K27" s="3">
         <v>557300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>925600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>648800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>606700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>784500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>452300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>503500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>617900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>135800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>441800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>668700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>560200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>470200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>636600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>512500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>417500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>489400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>288700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>302200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>107900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>190800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>375100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>441100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>582200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>535600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2725,16 +2783,19 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>37</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -2745,8 +2806,8 @@
       <c r="H29" s="3">
         <v>0</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>37</v>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -2755,16 +2816,16 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>86900</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>37</v>
+      <c r="O29" s="3">
+        <v>0</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>37</v>
@@ -2772,14 +2833,14 @@
       <c r="Q29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
-      <c r="S29" s="3" t="s">
+      <c r="R29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
@@ -2788,28 +2849,28 @@
         <v>0</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>1323600</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-43200</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-53600</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-242900</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-65300</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
+      <c r="AD29" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="AE29" s="3">
         <v>0</v>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-160200</v>
+        <v>-144300</v>
       </c>
       <c r="E32" s="3">
-        <v>-234800</v>
+        <v>-21100</v>
       </c>
       <c r="F32" s="3">
-        <v>-123600</v>
+        <v>28900</v>
       </c>
       <c r="G32" s="3">
-        <v>-217600</v>
+        <v>-53000</v>
       </c>
       <c r="H32" s="3">
-        <v>-396000</v>
+        <v>-22000</v>
       </c>
       <c r="I32" s="3">
-        <v>-157700</v>
+        <v>218700</v>
       </c>
       <c r="J32" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="K32" s="3">
         <v>-48300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-478800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-109100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-274000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-50600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-118200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-210400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>212200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-39200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-227800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-86200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-152700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-140900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-55000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-49800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-68900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-55200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-50200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>17100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-24600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-32300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-43400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-27100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-105700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-54700</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>952800</v>
+        <v>932100</v>
       </c>
       <c r="E33" s="3">
-        <v>1076200</v>
+        <v>930100</v>
       </c>
       <c r="F33" s="3">
-        <v>928000</v>
+        <v>1057300</v>
       </c>
       <c r="G33" s="3">
-        <v>1104800</v>
+        <v>928300</v>
       </c>
       <c r="H33" s="3">
-        <v>1162100</v>
+        <v>1074000</v>
       </c>
       <c r="I33" s="3">
-        <v>952300</v>
+        <v>1136600</v>
       </c>
       <c r="J33" s="3">
+        <v>983300</v>
+      </c>
+      <c r="K33" s="3">
         <v>557300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>925600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>735600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>606700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>784500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>452300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>503500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>617900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>135800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>441800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>668700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>560200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>470200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1960200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>469200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>363900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>246600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>223400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>302200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>107900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>190800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>375100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>441100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>582200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>535600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>952800</v>
+        <v>932100</v>
       </c>
       <c r="E35" s="3">
-        <v>1076200</v>
+        <v>930100</v>
       </c>
       <c r="F35" s="3">
-        <v>928000</v>
+        <v>1057300</v>
       </c>
       <c r="G35" s="3">
-        <v>1104800</v>
+        <v>928300</v>
       </c>
       <c r="H35" s="3">
-        <v>1162100</v>
+        <v>1074000</v>
       </c>
       <c r="I35" s="3">
-        <v>952300</v>
+        <v>1136600</v>
       </c>
       <c r="J35" s="3">
+        <v>983300</v>
+      </c>
+      <c r="K35" s="3">
         <v>557300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>925600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>735600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>606700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>784500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>452300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>503500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>617900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>135800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>441800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>668700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>560200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>470200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1960200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>469200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>363900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>246600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>223400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>302200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>107900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>190800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>375100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>441100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>582200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>535600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3612,397 +3698,407 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>2676100</v>
+        <v>2877500</v>
       </c>
       <c r="E41" s="3">
-        <v>6065900</v>
+        <v>2612200</v>
       </c>
       <c r="F41" s="3">
-        <v>3021000</v>
+        <v>5959000</v>
       </c>
       <c r="G41" s="3">
-        <v>2131100</v>
+        <v>3022000</v>
       </c>
       <c r="H41" s="3">
-        <v>1799800</v>
+        <v>2071700</v>
       </c>
       <c r="I41" s="3">
-        <v>1931500</v>
+        <v>1760300</v>
       </c>
       <c r="J41" s="3">
+        <v>1994500</v>
+      </c>
+      <c r="K41" s="3">
         <v>3508900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2486800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2288500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1360400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1997600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3165200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1412400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1223700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1269100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>952900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1565400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>882300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>499900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>422100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>738300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>631300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>724500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>668700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>441800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>534800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>410200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>382200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>447100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>587600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>791100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>651800</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>14644200</v>
+        <v>14798300</v>
       </c>
       <c r="E42" s="3">
-        <v>12909400</v>
+        <v>14294100</v>
       </c>
       <c r="F42" s="3">
-        <v>14844100</v>
+        <v>12681800</v>
       </c>
       <c r="G42" s="3">
-        <v>13493300</v>
+        <v>14860400</v>
       </c>
       <c r="H42" s="3">
-        <v>13681000</v>
+        <v>13117100</v>
       </c>
       <c r="I42" s="3">
-        <v>15048800</v>
+        <v>13380800</v>
       </c>
       <c r="J42" s="3">
+        <v>15539500</v>
+      </c>
+      <c r="K42" s="3">
         <v>13050600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>13572300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>13218500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>12793000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>11440800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>9817800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>12928100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>12628000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>11741800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>13547400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>12606300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>11025600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>10593800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>9029400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>7748900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>7283200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>6473600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>5270700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>5889700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>5683300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>5987800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>5655100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>5658600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>5370000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>4500100</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>3836200</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>897300</v>
+        <v>880000</v>
       </c>
       <c r="E43" s="3">
-        <v>1095100</v>
+        <v>875900</v>
       </c>
       <c r="F43" s="3">
-        <v>905400</v>
+        <v>1075800</v>
       </c>
       <c r="G43" s="3">
-        <v>915300</v>
+        <v>1304800</v>
       </c>
       <c r="H43" s="3">
-        <v>753300</v>
+        <v>889800</v>
       </c>
       <c r="I43" s="3">
-        <v>858800</v>
+        <v>736700</v>
       </c>
       <c r="J43" s="3">
+        <v>886800</v>
+      </c>
+      <c r="K43" s="3">
         <v>705300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>719500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>724700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>728700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>758900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>770800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>632900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>703900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>637000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>729300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>739500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>719300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>642000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>724700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>686700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>774700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>598200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>639500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>554400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>637900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>537200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>483700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>505200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>546600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>618300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>387100</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>81000</v>
+        <v>87500</v>
       </c>
       <c r="E44" s="3">
-        <v>85100</v>
+        <v>79000</v>
       </c>
       <c r="F44" s="3">
-        <v>98000</v>
+        <v>83600</v>
       </c>
       <c r="G44" s="3">
-        <v>101800</v>
+        <v>98100</v>
       </c>
       <c r="H44" s="3">
-        <v>113800</v>
+        <v>98900</v>
       </c>
       <c r="I44" s="3">
-        <v>123500</v>
+        <v>111300</v>
       </c>
       <c r="J44" s="3">
+        <v>127600</v>
+      </c>
+      <c r="K44" s="3">
         <v>140100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>128900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>117300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>118900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>132900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>147600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>125700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>121800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>86500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>77300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>82300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>88700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>100200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>105700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>606000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>653500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>154800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>880500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>814400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>734800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>812500</v>
-      </c>
-      <c r="AE44" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="AF44" s="3" t="s">
         <v>37</v>
@@ -4010,441 +4106,456 @@
       <c r="AG44" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AH44" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AI44" s="3">
         <v>229500</v>
       </c>
-      <c r="AI44" s="3" t="s">
+      <c r="AJ44" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1178300</v>
+        <v>971000</v>
       </c>
       <c r="E45" s="3">
-        <v>1244100</v>
+        <v>755200</v>
       </c>
       <c r="F45" s="3">
-        <v>1248200</v>
+        <v>799100</v>
       </c>
       <c r="G45" s="3">
-        <v>1342700</v>
+        <v>30400</v>
       </c>
       <c r="H45" s="3">
-        <v>1165300</v>
+        <v>888500</v>
       </c>
       <c r="I45" s="3">
-        <v>1146800</v>
+        <v>738100</v>
       </c>
       <c r="J45" s="3">
+        <v>735300</v>
+      </c>
+      <c r="K45" s="3">
         <v>1148600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1273300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1446800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1440700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1255600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1584900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1384500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1404200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1275600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1457600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1380100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1517400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1268600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2428400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1379700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1603500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2028600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1351100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1249200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1503400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1445900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2209500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1940600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1537400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1120900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>922600</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>19476800</v>
+        <v>20041200</v>
       </c>
       <c r="E46" s="3">
-        <v>21399700</v>
+        <v>19011300</v>
       </c>
       <c r="F46" s="3">
-        <v>20116800</v>
+        <v>21022400</v>
       </c>
       <c r="G46" s="3">
-        <v>17984200</v>
+        <v>20123300</v>
       </c>
       <c r="H46" s="3">
-        <v>17513100</v>
+        <v>17482900</v>
       </c>
       <c r="I46" s="3">
-        <v>19109500</v>
+        <v>17128900</v>
       </c>
       <c r="J46" s="3">
+        <v>19732600</v>
+      </c>
+      <c r="K46" s="3">
         <v>18553400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>18180800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>17795800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>16441700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>15585700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15486300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>16483600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>16081600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>15010100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>16764400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>16373600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>14233300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>13104500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>12710400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>11159600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>10946200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>9979600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>8810600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>8949500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>9094200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>9193700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>8730600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>8551400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>8041600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>7181800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>5797700</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>555500</v>
+        <v>573800</v>
       </c>
       <c r="E47" s="3">
-        <v>148000</v>
+        <v>542200</v>
       </c>
       <c r="F47" s="3">
-        <v>3219000</v>
+        <v>145400</v>
       </c>
       <c r="G47" s="3">
-        <v>313100</v>
+        <v>3220100</v>
       </c>
       <c r="H47" s="3">
-        <v>378100</v>
+        <v>304400</v>
       </c>
       <c r="I47" s="3">
-        <v>385100</v>
+        <v>369800</v>
       </c>
       <c r="J47" s="3">
+        <v>397700</v>
+      </c>
+      <c r="K47" s="3">
         <v>3033600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>618100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>622000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>617700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3393300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>988400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1009300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>938200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2553100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>626300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1005500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>607400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1794500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7700</v>
-      </c>
-      <c r="X47" s="3">
-        <v>7600</v>
       </c>
       <c r="Y47" s="3">
         <v>7600</v>
       </c>
       <c r="Z47" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AA47" s="3">
         <v>776400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>21000</v>
-      </c>
-      <c r="AB47" s="3">
-        <v>21500</v>
       </c>
       <c r="AC47" s="3">
         <v>21500</v>
       </c>
       <c r="AD47" s="3">
+        <v>21500</v>
+      </c>
+      <c r="AE47" s="3">
         <v>413300</v>
-      </c>
-      <c r="AE47" s="3">
-        <v>7400</v>
       </c>
       <c r="AF47" s="3">
         <v>7400</v>
       </c>
       <c r="AG47" s="3">
+        <v>7400</v>
+      </c>
+      <c r="AH47" s="3">
         <v>74200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>366500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1140800</v>
+        <v>1169100</v>
       </c>
       <c r="E48" s="3">
-        <v>1135800</v>
+        <v>1113500</v>
       </c>
       <c r="F48" s="3">
-        <v>1244100</v>
+        <v>1115800</v>
       </c>
       <c r="G48" s="3">
-        <v>1069000</v>
+        <v>1244500</v>
       </c>
       <c r="H48" s="3">
-        <v>1035800</v>
+        <v>1039200</v>
       </c>
       <c r="I48" s="3">
-        <v>933000</v>
+        <v>1013100</v>
       </c>
       <c r="J48" s="3">
+        <v>963400</v>
+      </c>
+      <c r="K48" s="3">
         <v>1019300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>851800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>837200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>806700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>892500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>704600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>667300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>647500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>741700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>654200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>650800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1302800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1353900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1301600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>945300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>944100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>678700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>742600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>699200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>611500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>559400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>498100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>442500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>398600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>351900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>314500</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>599500</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>553500</v>
       </c>
       <c r="F49" s="3">
-        <v>0</v>
+        <v>560700</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
+        <v>1102100</v>
       </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>563200</v>
       </c>
       <c r="I49" s="3">
-        <v>0</v>
+        <v>571900</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>600100</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -4491,38 +4602,41 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-      <c r="Z49" s="3" t="s">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>492700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>84200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>84700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>88000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>88500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>86500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>86900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>85600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>86100</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4674500</v>
+        <v>3808400</v>
       </c>
       <c r="E52" s="3">
-        <v>4816700</v>
+        <v>3802200</v>
       </c>
       <c r="F52" s="3">
-        <v>1631800</v>
+        <v>3966700</v>
       </c>
       <c r="G52" s="3">
-        <v>4822400</v>
+        <v>305300</v>
       </c>
       <c r="H52" s="3">
-        <v>4744400</v>
+        <v>3929800</v>
       </c>
       <c r="I52" s="3">
-        <v>4700900</v>
+        <v>3886300</v>
       </c>
       <c r="J52" s="3">
+        <v>4069300</v>
+      </c>
+      <c r="K52" s="3">
         <v>1749500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4210700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4125300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4122900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1297500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3828800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3852800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3282900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1444000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3282800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3215000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2575400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1012100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2275000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2065600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2072100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1957600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1128300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1064000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>773500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>287400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>544500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>588900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>726800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>453800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>847100</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>25847600</v>
+        <v>26359200</v>
       </c>
       <c r="E54" s="3">
-        <v>27500200</v>
+        <v>25229800</v>
       </c>
       <c r="F54" s="3">
-        <v>26211700</v>
+        <v>27015400</v>
       </c>
       <c r="G54" s="3">
-        <v>24188600</v>
+        <v>26220200</v>
       </c>
       <c r="H54" s="3">
-        <v>23671300</v>
+        <v>23514400</v>
       </c>
       <c r="I54" s="3">
-        <v>25128500</v>
+        <v>23152100</v>
       </c>
       <c r="J54" s="3">
+        <v>25947900</v>
+      </c>
+      <c r="K54" s="3">
         <v>24355800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23861300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23380300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21989000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21169100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21008100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>22012900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>20950100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>19748900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>21327700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>21244900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>18718800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>17264900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>16294800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>14178000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>13970100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>12630400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>11195300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>10818400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>10585300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>10541800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>9869200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>9676800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>9328300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>8439600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>7221400</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,451 +5230,464 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>111700</v>
+        <v>107700</v>
       </c>
       <c r="E57" s="3">
-        <v>122900</v>
+        <v>109000</v>
       </c>
       <c r="F57" s="3">
+        <v>120700</v>
+      </c>
+      <c r="G57" s="3">
         <v>124200</v>
       </c>
-      <c r="G57" s="3">
-        <v>121700</v>
-      </c>
       <c r="H57" s="3">
-        <v>104400</v>
+        <v>118300</v>
       </c>
       <c r="I57" s="3">
-        <v>117200</v>
+        <v>102100</v>
       </c>
       <c r="J57" s="3">
+        <v>121000</v>
+      </c>
+      <c r="K57" s="3">
         <v>212500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>119800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>131000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>127700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>135700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>156200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>126500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>149100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>157900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>146900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>125800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>188800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>186700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>187800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>398700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>450600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>174500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>360300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>331200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>339400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>362500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>307000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>281800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>234400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>203000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>110800</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1859100</v>
+        <v>1510300</v>
       </c>
       <c r="E58" s="3">
-        <v>3502400</v>
+        <v>1814700</v>
       </c>
       <c r="F58" s="3">
-        <v>2712500</v>
+        <v>3440700</v>
       </c>
       <c r="G58" s="3">
-        <v>1582000</v>
+        <v>2750000</v>
       </c>
       <c r="H58" s="3">
-        <v>1675100</v>
+        <v>1537900</v>
       </c>
       <c r="I58" s="3">
-        <v>3861800</v>
+        <v>1638300</v>
       </c>
       <c r="J58" s="3">
+        <v>3987800</v>
+      </c>
+      <c r="K58" s="3">
         <v>3366000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3515600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3896300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3131600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2666400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2788200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3864800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3038300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2715100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3278400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3232000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3096000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2591200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2385900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2070800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2159500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1983600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1909900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1825900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1365400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>983000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>850800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>798100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>665400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>554900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>437000</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4504100</v>
+        <v>2587500</v>
       </c>
       <c r="E59" s="3">
-        <v>4840500</v>
+        <v>2201400</v>
       </c>
       <c r="F59" s="3">
-        <v>4754000</v>
+        <v>2597600</v>
       </c>
       <c r="G59" s="3">
-        <v>4480900</v>
+        <v>3128900</v>
       </c>
       <c r="H59" s="3">
-        <v>4189500</v>
+        <v>2365600</v>
       </c>
       <c r="I59" s="3">
-        <v>4223300</v>
+        <v>2137800</v>
       </c>
       <c r="J59" s="3">
+        <v>2408600</v>
+      </c>
+      <c r="K59" s="3">
         <v>4433300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4243700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3958700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3888400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4156000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4022200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3733400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3862800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3633700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3490100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3302200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3563100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3110800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2755700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2714800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2925100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2940700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2365900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2092900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2295300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2179300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1824600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1916500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2096200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2083000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1540700</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>6474900</v>
+        <v>6516800</v>
       </c>
       <c r="E60" s="3">
-        <v>8465800</v>
+        <v>6320100</v>
       </c>
       <c r="F60" s="3">
-        <v>7590700</v>
+        <v>8316500</v>
       </c>
       <c r="G60" s="3">
-        <v>6184600</v>
+        <v>7593200</v>
       </c>
       <c r="H60" s="3">
-        <v>5968900</v>
+        <v>6012200</v>
       </c>
       <c r="I60" s="3">
-        <v>8202300</v>
+        <v>5838000</v>
       </c>
       <c r="J60" s="3">
+        <v>8469800</v>
+      </c>
+      <c r="K60" s="3">
         <v>8011700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7879100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7986000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7147600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6958100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6966500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7724700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7050200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6506700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6915400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6660000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6848000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5888700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5329300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5184200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5535100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5098900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4636100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4250000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4000100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3524800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2982400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2996300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2995900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2788800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2088600</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>60300</v>
+        <v>61000</v>
       </c>
       <c r="E61" s="3">
-        <v>60300</v>
+        <v>58900</v>
       </c>
       <c r="F61" s="3">
-        <v>60300</v>
+        <v>59300</v>
       </c>
       <c r="G61" s="3">
-        <v>60300</v>
+        <v>138700</v>
       </c>
       <c r="H61" s="3">
-        <v>557400</v>
+        <v>58700</v>
       </c>
       <c r="I61" s="3">
-        <v>525900</v>
+        <v>545200</v>
       </c>
       <c r="J61" s="3">
+        <v>543000</v>
+      </c>
+      <c r="K61" s="3">
         <v>515300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>490500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>466500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>438300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>175700</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -5605,109 +5748,115 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>372400</v>
+        <v>170900</v>
       </c>
       <c r="E62" s="3">
-        <v>556700</v>
+        <v>164100</v>
       </c>
       <c r="F62" s="3">
-        <v>503400</v>
+        <v>172900</v>
       </c>
       <c r="G62" s="3">
-        <v>469900</v>
+        <v>100900</v>
       </c>
       <c r="H62" s="3">
-        <v>471900</v>
+        <v>181900</v>
       </c>
       <c r="I62" s="3">
-        <v>515600</v>
+        <v>156900</v>
       </c>
       <c r="J62" s="3">
+        <v>169600</v>
+      </c>
+      <c r="K62" s="3">
         <v>479900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>342600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>343700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>350100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>336700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>331200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>284400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>241500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>186100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>154400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>214700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>166100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>129300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>185900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>210400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>168600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>65000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>87600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>84800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>60500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>34400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>17800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>41800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>27800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>57100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>7392000</v>
+        <v>7009500</v>
       </c>
       <c r="E66" s="3">
-        <v>9556900</v>
+        <v>6742500</v>
       </c>
       <c r="F66" s="3">
-        <v>8689900</v>
+        <v>8922700</v>
       </c>
       <c r="G66" s="3">
-        <v>7274000</v>
+        <v>8157100</v>
       </c>
       <c r="H66" s="3">
-        <v>7562300</v>
+        <v>6527700</v>
       </c>
       <c r="I66" s="3">
-        <v>9812100</v>
+        <v>6844700</v>
       </c>
       <c r="J66" s="3">
+        <v>9545200</v>
+      </c>
+      <c r="K66" s="3">
         <v>9590800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9304100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9362800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>8502500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8034800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9098800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9768700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9019800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8316900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8765700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8600700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>8843500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7802300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6535300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>6393700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>6672100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6061400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5124400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4561000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4202100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3754700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3188400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3215300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3151400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2885400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2130900</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,8 +6722,11 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6562,11 +6736,11 @@
       <c r="E72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F72" s="3">
-        <v>16037300</v>
-      </c>
-      <c r="G72" s="3" t="s">
+      <c r="F72" s="3" t="s">
         <v>37</v>
+      </c>
+      <c r="G72" s="3">
+        <v>16042500</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>37</v>
@@ -6574,11 +6748,11 @@
       <c r="I72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K72" s="3">
         <v>13020000</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>37</v>
@@ -6586,11 +6760,11 @@
       <c r="M72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O72" s="3">
         <v>10848700</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="P72" s="3" t="s">
         <v>37</v>
@@ -6598,11 +6772,11 @@
       <c r="Q72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="R72" s="3">
+      <c r="R72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="S72" s="3">
         <v>9102400</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>37</v>
@@ -6610,11 +6784,11 @@
       <c r="U72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="V72" s="3">
+      <c r="V72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="W72" s="3">
         <v>8870600</v>
-      </c>
-      <c r="W72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="X72" s="3" t="s">
         <v>37</v>
@@ -6622,11 +6796,11 @@
       <c r="Y72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="Z72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA72" s="3">
         <v>6566100</v>
-      </c>
-      <c r="AA72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="AB72" s="3" t="s">
         <v>37</v>
@@ -6646,14 +6820,17 @@
       <c r="AG72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AH72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AI72" s="3">
         <v>5306600</v>
       </c>
-      <c r="AI72" s="3" t="s">
+      <c r="AJ72" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>18455700</v>
+        <v>18839600</v>
       </c>
       <c r="E76" s="3">
-        <v>17943300</v>
+        <v>18014500</v>
       </c>
       <c r="F76" s="3">
-        <v>17521800</v>
+        <v>17627000</v>
       </c>
       <c r="G76" s="3">
-        <v>16914600</v>
+        <v>17527500</v>
       </c>
       <c r="H76" s="3">
-        <v>16109000</v>
+        <v>16443100</v>
       </c>
       <c r="I76" s="3">
-        <v>15316400</v>
+        <v>15755700</v>
       </c>
       <c r="J76" s="3">
+        <v>15815800</v>
+      </c>
+      <c r="K76" s="3">
         <v>14765000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14557200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14017500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13486500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13134300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11909300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12244200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11930300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11432100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12562000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12644200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9875400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9462600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9759400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7784300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7298000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6569000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6070900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6257400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6383200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6787100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6680800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6461500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6176800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5554100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5090500</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>952800</v>
+        <v>932100</v>
       </c>
       <c r="E81" s="3">
-        <v>1076200</v>
+        <v>930100</v>
       </c>
       <c r="F81" s="3">
-        <v>928000</v>
+        <v>1057300</v>
       </c>
       <c r="G81" s="3">
-        <v>1104800</v>
+        <v>928300</v>
       </c>
       <c r="H81" s="3">
-        <v>1162100</v>
+        <v>1074000</v>
       </c>
       <c r="I81" s="3">
-        <v>952300</v>
+        <v>1136600</v>
       </c>
       <c r="J81" s="3">
+        <v>983300</v>
+      </c>
+      <c r="K81" s="3">
         <v>557300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>925600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>735600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>606700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>784500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>452300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>503500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>617900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>135800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>441800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>668700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>560200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>470200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1960200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>469200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>363900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>246600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>223400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>302200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>107900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>190800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>375100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>441100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>582200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>535600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,109 +7599,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>89100</v>
+        <v>89300</v>
       </c>
       <c r="E83" s="3">
-        <v>80100</v>
+        <v>91200</v>
       </c>
       <c r="F83" s="3">
-        <v>93000</v>
+        <v>157600</v>
       </c>
       <c r="G83" s="3">
-        <v>91900</v>
+        <v>98200</v>
       </c>
       <c r="H83" s="3">
-        <v>93200</v>
+        <v>100300</v>
       </c>
       <c r="I83" s="3">
-        <v>152600</v>
+        <v>90900</v>
       </c>
       <c r="J83" s="3">
+        <v>120900</v>
+      </c>
+      <c r="K83" s="3">
         <v>108400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>98600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>84700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>105800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>115200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>114500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>115800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>114100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>134000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>134500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>131500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>108900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>107100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>106000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>98100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>89700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>98200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>79800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>67600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>52600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>40700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>31300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>25300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>21700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>14100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>920900</v>
+        <v>1507700</v>
       </c>
       <c r="E89" s="3">
-        <v>1347400</v>
+        <v>898800</v>
       </c>
       <c r="F89" s="3">
-        <v>1664700</v>
+        <v>1323600</v>
       </c>
       <c r="G89" s="3">
-        <v>1387800</v>
+        <v>1665300</v>
       </c>
       <c r="H89" s="3">
-        <v>1082500</v>
+        <v>1349100</v>
       </c>
       <c r="I89" s="3">
-        <v>846000</v>
+        <v>1058800</v>
       </c>
       <c r="J89" s="3">
+        <v>873600</v>
+      </c>
+      <c r="K89" s="3">
         <v>1270100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1034300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>921900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>632800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1153000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>894500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>671300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>771500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1143400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>795900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>703200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1025500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>848500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>593400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>682300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>517400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>862000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>506300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>280900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>273300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>576000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>245700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>344500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>598300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>782200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>542400</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-568400</v>
+        <v>-54100</v>
       </c>
       <c r="E91" s="3">
-        <v>-603800</v>
+        <v>-23200</v>
       </c>
       <c r="F91" s="3">
-        <v>-606700</v>
+        <v>-57500</v>
       </c>
       <c r="G91" s="3">
-        <v>-1385700</v>
+        <v>-68400</v>
       </c>
       <c r="H91" s="3">
-        <v>-803900</v>
+        <v>-88100</v>
       </c>
       <c r="I91" s="3">
-        <v>-1479600</v>
+        <v>-71800</v>
       </c>
       <c r="J91" s="3">
+        <v>-95100</v>
+      </c>
+      <c r="K91" s="3">
         <v>-510800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-709300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-530200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-893200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-739700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-625900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-988600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-45900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-42200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-51700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-34900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-25900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-36300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-50800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-41900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-56500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-73400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-80900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-111200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-96200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-84900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-76000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-64300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-48300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-67700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-24400</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-2093700</v>
+        <v>-102800</v>
       </c>
       <c r="E94" s="3">
-        <v>1813000</v>
+        <v>-2043700</v>
       </c>
       <c r="F94" s="3">
-        <v>-1512000</v>
+        <v>1781000</v>
       </c>
       <c r="G94" s="3">
-        <v>-72700</v>
+        <v>-1512500</v>
       </c>
       <c r="H94" s="3">
-        <v>1633900</v>
+        <v>-70700</v>
       </c>
       <c r="I94" s="3">
-        <v>-2452000</v>
+        <v>1598000</v>
       </c>
       <c r="J94" s="3">
+        <v>-2531900</v>
+      </c>
+      <c r="K94" s="3">
         <v>544800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>136400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-164500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1524100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2144900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>3007600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-788000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-991800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>145500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1105500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2985100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-391000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1069600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1090100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-514900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-724400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1195600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-55800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-555300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-153300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-592900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-140100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-343300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-831600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-670000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-658900</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,109 +8819,113 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-319300</v>
+        <v>281300</v>
       </c>
       <c r="E96" s="3">
-        <v>-697100</v>
+        <v>311700</v>
       </c>
       <c r="F96" s="3">
-        <v>-318500</v>
+        <v>684900</v>
       </c>
       <c r="G96" s="3">
-        <v>-341600</v>
+        <v>318600</v>
       </c>
       <c r="H96" s="3">
-        <v>-298800</v>
+        <v>332100</v>
       </c>
       <c r="I96" s="3">
-        <v>-170900</v>
+        <v>292200</v>
       </c>
       <c r="J96" s="3">
+        <v>176500</v>
+      </c>
+      <c r="K96" s="3">
         <v>-284600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-223500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-195100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-232500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-129600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-146100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-181800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-36300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-119900</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-203000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-164300</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-146200</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-1061000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-142200</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-93700</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-63200</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-58000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-74700</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-27500</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-45300</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-92700</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-109200</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-145500</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-136100</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-100700</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-99400</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9233,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2244300</v>
+        <v>-1205900</v>
       </c>
       <c r="E100" s="3">
-        <v>-69800</v>
+        <v>-2190600</v>
       </c>
       <c r="F100" s="3">
-        <v>724500</v>
+        <v>-68600</v>
       </c>
       <c r="G100" s="3">
-        <v>-966200</v>
+        <v>724800</v>
       </c>
       <c r="H100" s="3">
-        <v>-2865400</v>
+        <v>-939300</v>
       </c>
       <c r="I100" s="3">
-        <v>80700</v>
+        <v>-2802600</v>
       </c>
       <c r="J100" s="3">
+        <v>83300</v>
+      </c>
+      <c r="K100" s="3">
         <v>-871600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-992700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>116900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>316100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-147900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2117200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>281100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>195600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-887500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-367800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2973500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-219900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>180400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>112800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-188300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>62800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>406100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-127900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-41900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-6900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-171000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-31700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>16300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>17200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="E101" s="3">
-        <v>-6100</v>
+        <v>-6600</v>
       </c>
       <c r="F101" s="3">
-        <v>-24600</v>
+        <v>2300</v>
       </c>
       <c r="G101" s="3">
-        <v>600</v>
+        <v>7700</v>
       </c>
       <c r="H101" s="3">
-        <v>-6700</v>
+        <v>500</v>
       </c>
       <c r="I101" s="3">
-        <v>2200</v>
+        <v>11200</v>
       </c>
       <c r="J101" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="K101" s="3">
         <v>7500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>10400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-11100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>5000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-9400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-3700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>26500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>11700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-4100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>5900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>5400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>7600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>11200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>4000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>9900</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-3416000</v>
+        <v>189300</v>
       </c>
       <c r="E102" s="3">
-        <v>3084500</v>
+        <v>-3334300</v>
       </c>
       <c r="F102" s="3">
-        <v>852700</v>
+        <v>3030100</v>
       </c>
       <c r="G102" s="3">
-        <v>349400</v>
+        <v>853000</v>
       </c>
       <c r="H102" s="3">
-        <v>-155800</v>
+        <v>339700</v>
       </c>
       <c r="I102" s="3">
-        <v>-1523100</v>
+        <v>-152400</v>
       </c>
       <c r="J102" s="3">
+        <v>-1572800</v>
+      </c>
+      <c r="K102" s="3">
         <v>950800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>178500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>884700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-578200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1150900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1786900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>160900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-19700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>392000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-681100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>718200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>426300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-44800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-378000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-15500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-146900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>70400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>330100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-305100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>114500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-25400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-61500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-34000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-217600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>139300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-112800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NTES_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NTES_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
   <si>
     <t>NTES</t>
   </si>
@@ -656,467 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3664500</v>
+      </c>
+      <c r="E8" s="3">
         <v>3736500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3507100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3718800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3827500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3737400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3310900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3646200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3574400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3374800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3219600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3252600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3358200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3154400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2917600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2856000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2750800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2749500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2679700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2691800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2422800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2253600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2207400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2203400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1098200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1841900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2336400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2033500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2167900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1851800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1985100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2024400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1759600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1339600</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1435200</v>
+      </c>
+      <c r="E9" s="3">
         <v>1387600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1299500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1362200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1454700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1412200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1328700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1477600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1707200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1475900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1420400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1480100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1578400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1475500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1327000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1317500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1368900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1292700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1236700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1212300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1131300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1041700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1025400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1021300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>92700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>830800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1296900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1179300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1315400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>969100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>985300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>913700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>819600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>564000</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2229400</v>
+      </c>
+      <c r="E10" s="3">
         <v>2348900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2207600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2356600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2372800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2325200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1982200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2168600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1867200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1898900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1799100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1772400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1779800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1678900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1590600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1538500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1381900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1456800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1443000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1479400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1291500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1211900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1182000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1182200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1005500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1011100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1039500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>854200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>852600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>882700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>999800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1110600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>940000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>775700</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,112 +1165,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>612400</v>
+      </c>
+      <c r="E12" s="3">
         <v>630800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>613200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>578200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>631700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>595800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>539000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>545900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>576600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>548400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>497900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>469200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>530100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>534700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>484300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>426000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>421700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>411000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>354900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>338000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>349100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>332900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>297300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>311300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>269400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>300500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>275100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>209300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>184400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>171100</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>156000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>137200</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>127600</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>119300</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1361,13 +1377,16 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>37</v>
+      <c r="D14" s="3">
+        <v>69300</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>37</v>
@@ -1387,8 +1406,8 @@
       <c r="J14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1465,35 +1484,38 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>95600</v>
+      </c>
+      <c r="E15" s="3">
         <v>74200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>87000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>78700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>93000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>89300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>91200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>157600</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1569,8 +1591,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1629,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2593000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2717700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2544800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2663100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2858800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2701600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2474900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2595100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2949400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2719700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2531900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2492200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2723300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2617800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2383300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2260800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2331600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2326500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2065200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1984000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1964500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1740100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1638400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1629700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>531600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1487000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2001600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1860400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1956200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1473400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1479700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1316200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1197200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>925700</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1071600</v>
+      </c>
+      <c r="E18" s="3">
         <v>1018900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>962400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1055700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>968600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1035800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>836000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1051100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>625000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>655100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>687600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>760400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>634900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>536600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>534200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>595200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>419300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>422900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>614500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>707800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>458300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>513500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>569000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>573700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>566600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>354900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>334800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>173200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>211700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>378400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>505400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>708200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>562300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>414000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1850,216 +1882,223 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-248600</v>
+      </c>
+      <c r="E20" s="3">
         <v>144300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>21100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-28900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>53000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>22000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-218700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>18700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>48300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>478800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>109100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>274000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>50600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>118200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>210400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-212200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>39200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>227800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>86200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>152700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>140900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>55000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>49800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>68900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>55200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>50200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-17100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>24600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>32300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>43400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>27100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>105700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>54700</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1415700</v>
+      </c>
+      <c r="E21" s="3">
         <v>948800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1028200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1163300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1008600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1103200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1145800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1189900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>781800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1232600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>881400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>870100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1024100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>701700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>768200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>919700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>341000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>596700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>973700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>902800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>718200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>762700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>720800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>712200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>734400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>489200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>452600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>208600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>277000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>441900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>574100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>756900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>682100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>481700</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -2072,11 +2111,11 @@
       <c r="F22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H22" s="3">
         <v>124700</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>37</v>
@@ -2084,8 +2123,8 @@
       <c r="J22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2162,216 +2201,225 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1411700</v>
+      </c>
+      <c r="E23" s="3">
         <v>1139900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1118700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1286400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1092200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1247300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1223300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1214000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>673400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1134000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>796800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>764300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>908900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>587200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>652400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>805600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>207100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>462100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>842300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>794000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>611000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>654400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>624000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>623500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>635400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>410100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>385000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>156000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>236300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>410700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>548800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>735300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>668100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>468700</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>189800</v>
+      </c>
+      <c r="E24" s="3">
         <v>183800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>179000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>205800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>150700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>176800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>98200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>237100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>136300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>219200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>175100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>168400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>128700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>114800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>158200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>177300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>76900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>50500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>156900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>170700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>134900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>13500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>104500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>193500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>132800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>118000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>60300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>40600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>43100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>33500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>104400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>140000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>128300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>62100</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2474,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1221900</v>
+      </c>
+      <c r="E26" s="3">
         <v>956100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>939700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1080600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>941500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1070500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1125100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>976900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>537100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>914800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>621700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>595900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>780200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>472400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>494200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>628300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>130100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>411600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>685400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>623300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>476100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>640900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>519600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>429900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>502600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>292100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>324700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>115500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>193200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>377200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>444400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>595300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>539800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>406500</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1201000</v>
+      </c>
+      <c r="E27" s="3">
         <v>932100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>930100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1057300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>928300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1074000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1136600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>983300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>557300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>925600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>648800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>606700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>784500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>452300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>503500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>617900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>135800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>441800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>668700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>560200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>470200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>636600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>512500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>417500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>489400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>288700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>302200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>107900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>190800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>375100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>441100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>582200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>535600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2819,16 +2879,16 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>86900</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>37</v>
+      <c r="P29" s="3">
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>37</v>
@@ -2836,14 +2896,14 @@
       <c r="R29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3" t="s">
+      <c r="S29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -2852,28 +2912,28 @@
         <v>0</v>
       </c>
       <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>1323600</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-43200</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-53600</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-242900</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-65300</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
+      <c r="AE29" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="AF29" s="3">
         <v>0</v>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3098,216 +3164,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>248600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-144300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-21100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>28900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-53000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-22000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>218700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-18700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-48300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-478800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-109100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-274000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-50600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-118200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-210400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>212200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-39200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-227800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-86200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-152700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-140900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-55000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-49800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-68900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-55200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-50200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>17100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-24600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-32300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-43400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-27100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-105700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-54700</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>1201000</v>
+      </c>
+      <c r="E33" s="3">
         <v>932100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>930100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1057300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>928300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1074000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1136600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>983300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>557300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>925600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>735600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>606700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>784500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>452300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>503500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>617900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>135800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>441800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>668700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>560200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>470200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1960200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>469200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>363900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>246600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>223400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>302200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>107900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>190800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>375100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>441100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>582200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>535600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3410,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>1201000</v>
+      </c>
+      <c r="E35" s="3">
         <v>932100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>930100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1057300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>928300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1074000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1136600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>983300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>557300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>925600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>735600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>606700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>784500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>452300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>503500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>617900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>135800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>441800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>668700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>560200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>470200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1960200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>469200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>363900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>246600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>223400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>302200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>107900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>190800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>375100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>441100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>582200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>535600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3699,409 +3784,419 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>7039700</v>
+      </c>
+      <c r="E41" s="3">
         <v>2877500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2612200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5959000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3022000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2071700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1760300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1994500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3508900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2486800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2288500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1360400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1997600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3165200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1412400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1223700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1269100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>952900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1565400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>882300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>499900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>422100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>738300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>631300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>724500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>668700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>441800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>534800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>410200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>382200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>447100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>587600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>791100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>651800</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>11809300</v>
+      </c>
+      <c r="E42" s="3">
         <v>14798300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>14294100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>12681800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>14860400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>13117100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>13380800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>15539500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>13050600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>13572300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>13218500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>12793000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>11440800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>9817800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>12928100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>12628000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>11741800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>13547400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>12606300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>11025600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>10593800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>9029400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>7748900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>7283200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>6473600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>5270700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>5889700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>5683300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>5987800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>5655100</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>5658600</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>5370000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>4500100</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>3836200</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>776700</v>
+      </c>
+      <c r="E43" s="3">
         <v>880000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>875900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1075800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1304800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>889800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>736700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>886800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>705300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>719500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>724700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>728700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>758900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>770800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>632900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>703900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>637000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>729300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>739500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>719300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>642000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>724700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>686700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>774700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>598200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>639500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>554400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>637900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>537200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>483700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>505200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>546600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>618300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>387100</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>78300</v>
+      </c>
+      <c r="E44" s="3">
         <v>87500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>79000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>83600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>98100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>98900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>111300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>127600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>140100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>128900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>117300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>118900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>132900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>147600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>125700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>121800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>86500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>77300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>82300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>88700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>100200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>105700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>606000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>653500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>154800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>880500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>814400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>734800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>812500</v>
-      </c>
-      <c r="AF44" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="AG44" s="3" t="s">
         <v>37</v>
@@ -4109,457 +4204,472 @@
       <c r="AH44" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AI44" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ44" s="3">
         <v>229500</v>
       </c>
-      <c r="AJ44" s="3" t="s">
+      <c r="AK44" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>879100</v>
+      </c>
+      <c r="E45" s="3">
         <v>971000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>755200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>799100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>30400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>888500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>738100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>735300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1148600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1273300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1446800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1440700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1255600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1584900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1384500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1404200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1275600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1457600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1380100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1517400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1268600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2428400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1379700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1603500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2028600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1351100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1249200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1503400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1445900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2209500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1940600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1537400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1120900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>922600</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>21006000</v>
+      </c>
+      <c r="E46" s="3">
         <v>20041200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>19011300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>21022400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>20123300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>17482900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>17128900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>19732600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>18553400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>18180800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>17795800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>16441700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15585700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15486300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>16483600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>16081600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>15010100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>16764400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>16373600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>14233300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>13104500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>12710400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>11159600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>10946200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>9979600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>8810600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>8949500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>9094200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>9193700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>8730600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>8551400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>8041600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>7181800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>5797700</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>414400</v>
+      </c>
+      <c r="E47" s="3">
         <v>573800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>542200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>145400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3220100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>304400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>369800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>397700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3033600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>618100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>622000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>617700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3393300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>988400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1009300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>938200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2553100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>626300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1005500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>607400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1794500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>7700</v>
-      </c>
-      <c r="Y47" s="3">
-        <v>7600</v>
       </c>
       <c r="Z47" s="3">
         <v>7600</v>
       </c>
       <c r="AA47" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AB47" s="3">
         <v>776400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>21000</v>
-      </c>
-      <c r="AC47" s="3">
-        <v>21500</v>
       </c>
       <c r="AD47" s="3">
         <v>21500</v>
       </c>
       <c r="AE47" s="3">
+        <v>21500</v>
+      </c>
+      <c r="AF47" s="3">
         <v>413300</v>
-      </c>
-      <c r="AF47" s="3">
-        <v>7400</v>
       </c>
       <c r="AG47" s="3">
         <v>7400</v>
       </c>
       <c r="AH47" s="3">
+        <v>7400</v>
+      </c>
+      <c r="AI47" s="3">
         <v>74200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>366500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1167300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1169100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1113500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1115800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1244500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1039200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1013100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>963400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1019300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>851800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>837200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>806700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>892500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>704600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>667300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>647500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>741700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>654200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>650800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1302800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1353900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1301600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>945300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>944100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>678700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>742600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>699200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>611500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>559400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>498100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>442500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>398600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>351900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>314500</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>571600</v>
+      </c>
+      <c r="E49" s="3">
         <v>599500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>553500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>560700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1102100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>563200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>571900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>600100</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
@@ -4605,38 +4715,41 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-      <c r="AA49" s="3" t="s">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>492700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>84200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>84700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>88000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>88500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>86500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>86900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>85600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>86100</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +4959,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3539600</v>
+      </c>
+      <c r="E52" s="3">
         <v>3808400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3802200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3966700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>305300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3929800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3886300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4069300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1749500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4210700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4125300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4122900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1297500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3828800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3852800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3282900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1444000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3282800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3215000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2575400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1012100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2275000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2065600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2072100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1957600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1128300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1064000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>773500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>287400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>544500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>588900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>726800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>453800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>847100</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>26851500</v>
+      </c>
+      <c r="E54" s="3">
         <v>26359200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>25229800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>27015400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>26220200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>23514400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>23152100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>25947900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>24355800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23861300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>23380300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21989000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21169100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>21008100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>22012900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>20950100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>19748900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>21327700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>21244900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>18718800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>17264900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>16294800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>14178000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>13970100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>12630400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>11195300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>10818400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>10585300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>10541800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>9869200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>9676800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>9328300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>8439600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>7221400</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,466 +5360,479 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>98700</v>
+      </c>
+      <c r="E57" s="3">
         <v>107700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>109000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>120700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>124200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>118300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>102100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>121000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>212500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>119800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>131000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>127700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>135700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>156200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>126500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>149100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>157900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>146900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>125800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>188800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>186700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>187800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>398700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>450600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>174500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>360300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>331200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>339400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>362500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>307000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>281800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>234400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>203000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>110800</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1617300</v>
+      </c>
+      <c r="E58" s="3">
         <v>1510300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1814700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3440700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2750000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1537900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1638300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3987800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3366000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3515600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3896300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3131600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2666400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2788200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3864800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3038300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2715100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3278400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3232000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3096000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2591200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2385900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2070800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2159500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1983600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1909900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1825900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1365400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>983000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>850800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>798100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>665400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>554900</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>437000</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2474100</v>
+      </c>
+      <c r="E59" s="3">
         <v>2587500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2201400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2597600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3128900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2365600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2137800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2408600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4433300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4243700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3958700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3888400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4156000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4022200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3733400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3862800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3633700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3490100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3302200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3563100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3110800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2755700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2714800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2925100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2940700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2365900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2092900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2295300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2179300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1824600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1916500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2096200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2083000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1540700</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6804600</v>
+      </c>
+      <c r="E60" s="3">
         <v>6516800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6320100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8316500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7593200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6012200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5838000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8469800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8011700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7879100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7986000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7147600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6958100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6966500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7724700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7050200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6506700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6915400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6660000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6848000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5888700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5329300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5184200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5535100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5098900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4636100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4250000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4000100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3524800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2982400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2996300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2995900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2788800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2088600</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>58600</v>
+      </c>
+      <c r="E61" s="3">
         <v>61000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>58900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>59300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>138700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>58700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>545200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>543000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>515300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>490500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>466500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>438300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>175700</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -5751,112 +5893,118 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>168300</v>
+      </c>
+      <c r="E62" s="3">
         <v>170900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>164100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>172900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>100900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>181900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>156900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>169600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>479900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>342600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>343700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>350100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>336700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>331200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>284400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>241500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>186100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>154400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>214700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>166100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>129300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>185900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>210400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>168600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>65000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>87600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>84800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>60500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>34400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>17800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>41800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>27800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>57100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7329300</v>
+      </c>
+      <c r="E66" s="3">
         <v>7009500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6742500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8922700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8157100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6527700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6844700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9545200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9590800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9304100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9362800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8502500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8034800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9098800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9768700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9019800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8316900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8765700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>8600700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8843500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7802300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>6535300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>6393700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6672100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6061400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5124400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4561000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4202100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3754700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3188400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3215300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3151400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2885400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2130900</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,8 +6895,11 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6739,11 +6912,11 @@
       <c r="F72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H72" s="3">
         <v>16042500</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>37</v>
@@ -6751,11 +6924,11 @@
       <c r="J72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L72" s="3">
         <v>13020000</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>37</v>
@@ -6763,11 +6936,11 @@
       <c r="N72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="P72" s="3">
         <v>10848700</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>37</v>
@@ -6775,11 +6948,11 @@
       <c r="R72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="T72" s="3">
         <v>9102400</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>37</v>
@@ -6787,11 +6960,11 @@
       <c r="V72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="W72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="X72" s="3">
         <v>8870600</v>
-      </c>
-      <c r="X72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="Y72" s="3" t="s">
         <v>37</v>
@@ -6799,11 +6972,11 @@
       <c r="Z72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB72" s="3">
         <v>6566100</v>
-      </c>
-      <c r="AB72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="AC72" s="3" t="s">
         <v>37</v>
@@ -6823,14 +6996,17 @@
       <c r="AH72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AI72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ72" s="3">
         <v>5306600</v>
       </c>
-      <c r="AJ72" s="3" t="s">
+      <c r="AK72" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>19000400</v>
+      </c>
+      <c r="E76" s="3">
         <v>18839600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18014500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>17627000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17527500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16443100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>15755700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>15815800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14765000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14557200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14017500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13486500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13134300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11909300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12244200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11930300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11432100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12562000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>12644200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9875400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9462600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>9759400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7784300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7298000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6569000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6070900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6257400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6383200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6787100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6680800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6461500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6176800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5554100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>5090500</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>1201000</v>
+      </c>
+      <c r="E81" s="3">
         <v>932100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>930100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1057300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>928300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1074000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1136600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>983300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>557300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>925600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>735600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>606700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>784500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>452300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>503500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>617900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>135800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>441800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>668700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>560200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>470200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1960200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>469200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>363900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>246600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>223400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>302200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>107900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>190800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>375100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>441100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>582200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>535600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,112 +7797,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>78700</v>
+      </c>
+      <c r="E83" s="3">
         <v>89300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>91200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>157600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>98200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>100300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>90900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>120900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>108400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>98600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>84700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>105800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>115200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>114500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>115800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>114100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>134000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>134500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>131500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>108900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>107100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>106000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>98100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>89700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>98200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>79800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>67600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>52600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>40700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>31300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>25300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>21700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>14100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1782700</v>
+      </c>
+      <c r="E89" s="3">
         <v>1507700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>898800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1323600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1665300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1349100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1058800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>873600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1270100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1034300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>921900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>632800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1153000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>894500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>671300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>771500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1143400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>795900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>703200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1025500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>848500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>593400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>682300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>517400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>862000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>506300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>280900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>273300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>576000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>245700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>344500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>598300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>782200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>542400</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8585,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-42700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-54100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-23200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-57500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-68400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-88100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-71800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-95100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-510800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-709300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-530200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-893200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-739700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-625900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-988600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-45900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-42200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-51700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-34900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-25900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-36300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-50800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-41900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-56500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-73400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-80900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-111200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-96200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-84900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-76000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-64300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-48300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-67700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-24400</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8904,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>2826200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-102800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2043700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1781000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1512500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-70700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1598000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2531900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>544800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>136400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-164500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1524100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2144900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>3007600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-788000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-991800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>145500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1105500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2985100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-391000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1069600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1090100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-514900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-724400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1195600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-55800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-555300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-153300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-592900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-140100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-343300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-831600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-670000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-658900</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,112 +9052,116 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>271600</v>
+      </c>
+      <c r="E96" s="3">
         <v>281300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>311700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>684900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>318600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>332100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>292200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>176500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-284600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-223500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-195100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-232500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-129600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-146100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-181800</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-36300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-119900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-203000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-164300</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-146200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-1061000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-142200</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-93700</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-63200</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-58000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-74700</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-27500</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-45300</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-92700</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-109200</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-145500</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-136100</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-100700</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-99400</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,316 +9478,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-337400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1205900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2190600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-68600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>724800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-939300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2802600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>83300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-871600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-992700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>116900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>316100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-147900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2117200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>281100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>195600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-887500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-367800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2973500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-219900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>180400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>112800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-188300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>62800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>406100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-127900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-41900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-6900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-171000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-31700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>16300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>17200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="E101" s="3">
         <v>600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-6600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>7700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>11200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>7500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>10400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-11100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-3600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>5000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-9400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-3700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>26500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>11700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-4100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>5900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>5400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>7600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>11200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>4000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>9900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4287000</v>
+      </c>
+      <c r="E102" s="3">
         <v>189300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3334300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3030100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>853000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>339700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-152400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1572800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>950800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>178500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>884700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-578200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1150900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1786900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>160900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-19700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>392000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-681100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>718200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>426300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-44800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-378000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-15500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-146900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>70400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>330100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-305100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>114500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-25400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-61500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-34000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-217600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>139300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-112800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NTES_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NTES_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>NTES</t>
   </si>
@@ -656,479 +656,492 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3972800</v>
+      </c>
+      <c r="E8" s="3">
         <v>3664500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3736500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3507100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3718800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3827500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3737400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3310900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3646200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3574400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3374800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3219600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3252600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3358200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3154400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2917600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2856000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2750800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2749500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2679700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2691800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2422800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2253600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2207400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2203400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1098200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1841900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2336400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2033500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2167900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1851800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1985100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2024400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1759600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1339600</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1426200</v>
+      </c>
+      <c r="E9" s="3">
         <v>1435200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1387600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1299500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1362200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1454700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1412200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1328700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1477600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1707200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1475900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1420400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1480100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1578400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1475500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1327000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1317500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1368900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1292700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1236700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1212300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1131300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1041700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1025400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1021300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>92700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>830800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1296900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1179300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1315400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>969100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>985300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>913700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>819600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>564000</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2546600</v>
+      </c>
+      <c r="E10" s="3">
         <v>2229400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2348900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2207600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2356600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2372800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2325200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1982200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2168600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1867200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1898900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1799100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1772400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1779800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1678900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1590600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1538500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1381900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1456800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1443000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1479400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1291500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1211900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1182000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1182200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1005500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1011100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1039500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>854200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>852600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>882700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>999800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1110600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>940000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>775700</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,115 +1179,119 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>604500</v>
+      </c>
+      <c r="E12" s="3">
         <v>612400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>630800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>613200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>578200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>631700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>595800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>539000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>545900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>576600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>548400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>497900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>469200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>530100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>534700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>484300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>426000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>421700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>411000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>354900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>338000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>349100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>332900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>297300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>311300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>269400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>300500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>275100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>209300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>184400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>171100</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>156000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>137200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>127600</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>119300</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1380,13 +1397,16 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>69300</v>
+      <c r="D14" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>37</v>
@@ -1409,8 +1429,8 @@
       <c r="K14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1487,38 +1507,41 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>66300</v>
+      </c>
+      <c r="E15" s="3">
         <v>95600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>74200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>87000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>78700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>93000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>89300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>91200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>157600</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1594,8 +1617,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2533900</v>
+      </c>
+      <c r="E17" s="3">
         <v>2593000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2717700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2544800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2663100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2858800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2701600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2474900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2595100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2949400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2719700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2531900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2492200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2723300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2617800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2383300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2260800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2331600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2326500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2065200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1984000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1964500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1740100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1638400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1629700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>531600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1487000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2001600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1860400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1956200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1473400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1479700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1316200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1197200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>925700</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1438900</v>
+      </c>
+      <c r="E18" s="3">
         <v>1071600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1018900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>962400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1055700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>968600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1035800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>836000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1051100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>625000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>655100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>687600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>760400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>634900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>536600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>534200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>595200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>419300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>422900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>614500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>707800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>458300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>513500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>569000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>573700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>566600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>354900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>334800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>173200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>211700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>378400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>505400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>708200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>562300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>414000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1883,230 +1916,237 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-35400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-248600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>144300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>21100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-28900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>53000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>22000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-218700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>18700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>48300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>478800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>109100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>274000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>50600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>118200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>210400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-212200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>39200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>227800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>86200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>152700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>140900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>55000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>49800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>68900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>55200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>50200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-17100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>24600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>32300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>43400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>27100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>105700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>54700</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1540600</v>
+      </c>
+      <c r="E21" s="3">
         <v>1415700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>948800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1028200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1163300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1008600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1103200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1145800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1189900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>781800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1232600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>881400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>870100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1024100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>701700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>768200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>919700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>341000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>596700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>973700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>902800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>718200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>762700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>720800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>712200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>734400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>489200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>452600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>208600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>277000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>441900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>574100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>756900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>682100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>481700</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>37</v>
+      <c r="E22" s="3">
+        <v>81900</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>37</v>
@@ -2114,11 +2154,11 @@
       <c r="G22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I22" s="3">
         <v>124700</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>37</v>
@@ -2126,8 +2166,8 @@
       <c r="K22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2204,222 +2244,231 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1716000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1411700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1139900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1118700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1286400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1092200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1247300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1223300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1214000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>673400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1134000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>796800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>764300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>908900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>587200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>652400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>805600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>207100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>462100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>842300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>794000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>611000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>654400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>624000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>623500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>635400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>410100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>385000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>156000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>236300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>410700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>548800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>735300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>668100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>468700</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>262500</v>
+      </c>
+      <c r="E24" s="3">
         <v>189800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>183800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>179000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>205800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>150700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>176800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>98200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>237100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>136300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>219200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>175100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>168400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>128700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>114800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>158200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>177300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>76900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>50500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>156900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>170700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>134900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>13500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>104500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>193500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>132800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>118000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>60300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>40600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>43100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>33500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>104400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>140000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>128300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>62100</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2525,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1453400</v>
+      </c>
+      <c r="E26" s="3">
         <v>1221900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>956100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>939700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1080600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>941500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1070500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1125100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>976900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>537100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>914800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>621700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>595900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>780200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>472400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>494200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>628300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>130100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>411600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>685400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>623300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>476100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>640900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>519600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>429900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>502600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>292100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>324700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>115500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>193200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>377200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>444400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>595300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>539800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>406500</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1419600</v>
+      </c>
+      <c r="E27" s="3">
         <v>1201000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>932100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>930100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1057300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>928300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1074000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1136600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>983300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>557300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>925600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>648800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>606700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>784500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>452300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>503500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>617900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>135800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>441800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>668700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>560200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>470200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>636600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>512500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>417500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>489400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>288700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>302200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>107900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>190800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>375100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>441100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>582200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>535600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2882,16 +2943,16 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>86900</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>37</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>37</v>
@@ -2899,14 +2960,14 @@
       <c r="S29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
-      <c r="U29" s="3" t="s">
+      <c r="T29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -2915,28 +2976,28 @@
         <v>0</v>
       </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>1323600</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-43200</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-53600</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-242900</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-65300</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
+      <c r="AF29" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="AG29" s="3">
         <v>0</v>
@@ -2953,8 +3014,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3167,222 +3234,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E32" s="3">
         <v>248600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-144300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-21100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>28900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-53000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-22000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>218700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-18700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-48300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-478800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-109100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-274000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-50600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-118200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-210400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>212200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-39200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-227800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-86200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-152700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-140900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-55000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-49800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-68900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-55200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-50200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>17100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-24600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-32300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-43400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-27100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-105700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-54700</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>1419600</v>
+      </c>
+      <c r="E33" s="3">
         <v>1201000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>932100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>930100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1057300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>928300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1074000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1136600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>983300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>557300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>925600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>735600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>606700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>784500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>452300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>503500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>617900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>135800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>441800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>668700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>560200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>470200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1960200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>469200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>363900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>246600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>223400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>302200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>107900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>190800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>375100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>441100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>582200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>535600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3488,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>1419600</v>
+      </c>
+      <c r="E35" s="3">
         <v>1201000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>932100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>930100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1057300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>928300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1074000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1136600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>983300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>557300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>925600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>735600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>606700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>784500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>452300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>503500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>617900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>135800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>441800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>668700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>560200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>470200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1960200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>469200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>363900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>246600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>223400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>302200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>107900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>190800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>375100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>441100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>582200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>535600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3785,421 +3871,431 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>5753300</v>
+      </c>
+      <c r="E41" s="3">
         <v>7039700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2877500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2612200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5959000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3022000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2071700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1760300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1994500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3508900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2486800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2288500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1360400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1997600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3165200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1412400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1223700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1269100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>952900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1565400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>882300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>499900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>422100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>738300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>631300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>724500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>668700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>441800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>534800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>410200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>382200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>447100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>587600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>791100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>651800</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>11809300</v>
+        <v>13555600</v>
       </c>
       <c r="E42" s="3">
+        <v>11821900</v>
+      </c>
+      <c r="F42" s="3">
         <v>14798300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>14294100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>12681800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>14860400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>13117100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>13380800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>15539500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>13050600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>13572300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>13218500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>12793000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>11440800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>9817800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>12928100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>12628000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>11741800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>13547400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>12606300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>11025600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>10593800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>9029400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>7748900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>7283200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>6473600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>5270700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>5889700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>5683300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>5987800</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>5655100</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>5658600</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>5370000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>4500100</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>3836200</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>776700</v>
+        <v>929100</v>
       </c>
       <c r="E43" s="3">
+        <v>1117700</v>
+      </c>
+      <c r="F43" s="3">
         <v>880000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>875900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1075800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1304800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>889800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>736700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>886800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>705300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>719500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>724700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>728700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>758900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>770800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>632900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>703900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>637000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>729300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>739500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>719300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>642000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>724700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>686700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>774700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>598200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>639500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>554400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>637900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>537200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>483700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>505200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>546600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>618300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>387100</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>71400</v>
+      </c>
+      <c r="E44" s="3">
         <v>78300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>87500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>79000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>83600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>98100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>98900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>111300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>127600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>140100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>128900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>117300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>118900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>132900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>147600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>125700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>121800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>86500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>77300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>82300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>88700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>100200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>105700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>606000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>653500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>154800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>880500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>814400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>734800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>812500</v>
-      </c>
-      <c r="AG44" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="AH44" s="3" t="s">
         <v>37</v>
@@ -4207,472 +4303,487 @@
       <c r="AI44" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AJ44" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AK44" s="3">
         <v>229500</v>
       </c>
-      <c r="AK44" s="3" t="s">
+      <c r="AL44" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>879100</v>
+        <v>917000</v>
       </c>
       <c r="E45" s="3">
+        <v>30800</v>
+      </c>
+      <c r="F45" s="3">
         <v>971000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>755200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>799100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>30400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>888500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>738100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>735300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1148600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1273300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1446800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1440700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1255600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1584900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1384500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1404200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1275600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1457600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1380100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1517400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1268600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2428400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1379700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1603500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2028600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1351100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1249200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1503400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1445900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2209500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1940600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1537400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1120900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>922600</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>21728200</v>
+      </c>
+      <c r="E46" s="3">
         <v>21006000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>20041200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>19011300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>21022400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>20123300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>17482900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>17128900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>19732600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>18553400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>18180800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>17795800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>16441700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15585700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>15486300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>16483600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>16081600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>15010100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>16764400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>16373600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>14233300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>13104500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>12710400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>11159600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>10946200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>9979600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>8810600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>8949500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>9094200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>9193700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>8730600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>8551400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>8041600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>7181800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>5797700</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>414400</v>
+        <v>416900</v>
       </c>
       <c r="E47" s="3">
+        <v>3182800</v>
+      </c>
+      <c r="F47" s="3">
         <v>573800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>542200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>145400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3220100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>304400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>369800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>397700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3033600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>618100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>622000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>617700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3393300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>988400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1009300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>938200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2553100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>626300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1005500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>607400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1794500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>7700</v>
-      </c>
-      <c r="Z47" s="3">
-        <v>7600</v>
       </c>
       <c r="AA47" s="3">
         <v>7600</v>
       </c>
       <c r="AB47" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AC47" s="3">
         <v>776400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>21000</v>
-      </c>
-      <c r="AD47" s="3">
-        <v>21500</v>
       </c>
       <c r="AE47" s="3">
         <v>21500</v>
       </c>
       <c r="AF47" s="3">
+        <v>21500</v>
+      </c>
+      <c r="AG47" s="3">
         <v>413300</v>
-      </c>
-      <c r="AG47" s="3">
-        <v>7400</v>
       </c>
       <c r="AH47" s="3">
         <v>7400</v>
       </c>
       <c r="AI47" s="3">
+        <v>7400</v>
+      </c>
+      <c r="AJ47" s="3">
         <v>74200</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>366500</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1167300</v>
+        <v>1165100</v>
       </c>
       <c r="E48" s="3">
+        <v>1241400</v>
+      </c>
+      <c r="F48" s="3">
         <v>1169100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1113500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1115800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1244500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1039200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1013100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>963400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1019300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>851800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>837200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>806700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>892500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>704600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>667300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>647500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>741700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>654200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>650800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1302800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1353900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1301600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>945300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>944100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>678700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>742600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>699200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>611500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>559400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>498100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>442500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>398600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>351900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>314500</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>571600</v>
+        <v>570700</v>
       </c>
       <c r="E49" s="3">
+        <v>1019400</v>
+      </c>
+      <c r="F49" s="3">
         <v>599500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>553500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>560700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1102100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>563200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>571900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>600100</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
         <v>0</v>
       </c>
@@ -4718,38 +4829,41 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-      <c r="AB49" s="3" t="s">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>492700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>84200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>84700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>88000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>88500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>86500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>86900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>85600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>86100</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,115 +5079,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3539600</v>
+        <v>3622000</v>
       </c>
       <c r="E52" s="3">
+        <v>247000</v>
+      </c>
+      <c r="F52" s="3">
         <v>3808400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3802200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3966700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>305300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3929800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3886300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4069300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1749500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4210700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4125300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4122900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1297500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3828800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3852800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3282900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1444000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3282800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3215000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2575400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1012100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2275000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2065600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2072100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1957600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1128300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1064000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>773500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>287400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>544500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>588900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>726800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>453800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>847100</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>27679800</v>
+      </c>
+      <c r="E54" s="3">
         <v>26851500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>26359200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>25229800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>27015400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>26220200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>23514400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>23152100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>25947900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>24355800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>23861300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>23380300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21989000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>21169100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>21008100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>22012900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>20950100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>19748900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>21327700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>21244900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>18718800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>17264900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>16294800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>14178000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>13970100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>12630400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>11195300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>10818400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>10585300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>10541800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>9869200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>9676800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>9328300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>8439600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>7221400</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,481 +5491,494 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>77900</v>
+      </c>
+      <c r="E57" s="3">
         <v>98700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>107700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>109000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>120700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>124200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>118300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>102100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>121000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>212500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>119800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>131000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>127700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>135700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>156200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>126500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>149100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>157900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>146900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>125800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>188800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>186700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>187800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>398700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>450600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>174500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>360300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>331200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>339400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>362500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>307000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>281800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>234400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>203000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>110800</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1617300</v>
+        <v>1353800</v>
       </c>
       <c r="E58" s="3">
+        <v>1640800</v>
+      </c>
+      <c r="F58" s="3">
         <v>1510300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1814700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3440700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2750000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1537900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1638300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3987800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3366000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3515600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3896300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3131600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2666400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2788200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3864800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3038300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2715100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3278400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3232000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3096000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2591200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2385900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2070800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2159500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1983600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1909900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1825900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1365400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>983000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>850800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>798100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>665400</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>554900</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>437000</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2474100</v>
+        <v>3074000</v>
       </c>
       <c r="E59" s="3">
+        <v>3413900</v>
+      </c>
+      <c r="F59" s="3">
         <v>2587500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2201400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2597600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3128900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2365600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2137800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2408600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4433300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4243700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3958700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3888400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4156000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4022200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3733400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3862800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3633700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3490100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3302200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3563100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3110800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2755700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2714800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2925100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2940700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2365900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2092900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2295300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2179300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1824600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1916500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2096200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2083000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1540700</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6771600</v>
+      </c>
+      <c r="E60" s="3">
         <v>6804600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6516800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6320100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8316500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7593200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6012200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5838000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8469800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8011700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7879100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7986000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7147600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6958100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6966500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7724700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7050200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6506700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6915400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6660000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6848000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5888700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5329300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5184200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5535100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5098900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4636100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4250000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4000100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3524800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2982400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2996300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2995900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2788800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2088600</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>58600</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>115200</v>
+      </c>
+      <c r="F61" s="3">
         <v>61000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>58900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>59300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>138700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>58700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>545200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>543000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>515300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>490500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>466500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>438300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>175700</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -5896,115 +6039,121 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>168300</v>
+        <v>162500</v>
       </c>
       <c r="E62" s="3">
+        <v>111800</v>
+      </c>
+      <c r="F62" s="3">
         <v>170900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>164100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>172900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>100900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>181900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>156900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>169600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>479900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>342600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>343700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>350100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>336700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>331200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>284400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>241500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>186100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>154400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>214700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>166100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>129300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>185900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>210400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>168600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>65000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>87600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>84800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>60500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>34400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>17800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>41800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>27800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>57100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7302300</v>
+      </c>
+      <c r="E66" s="3">
         <v>7329300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7009500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6742500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8922700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>8157100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6527700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6844700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9545200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9590800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9304100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9362800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8502500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8034800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9098800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9768700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>9019800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8316900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>8765700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8600700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8843500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>7802300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>6535300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6393700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6672100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6061400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5124400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4561000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4202100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3754700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3188400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3215300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3151400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2885400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2130900</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,16 +7069,19 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>37</v>
+      <c r="E72" s="3">
+        <v>18123900</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>37</v>
@@ -6915,11 +7089,11 @@
       <c r="G72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I72" s="3">
         <v>16042500</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>37</v>
@@ -6927,11 +7101,11 @@
       <c r="K72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M72" s="3">
         <v>13020000</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>37</v>
@@ -6939,11 +7113,11 @@
       <c r="O72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="P72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q72" s="3">
         <v>10848700</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="R72" s="3" t="s">
         <v>37</v>
@@ -6951,11 +7125,11 @@
       <c r="S72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="T72" s="3">
+      <c r="T72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="U72" s="3">
         <v>9102400</v>
-      </c>
-      <c r="U72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>37</v>
@@ -6963,11 +7137,11 @@
       <c r="W72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="X72" s="3">
+      <c r="X72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y72" s="3">
         <v>8870600</v>
-      </c>
-      <c r="Y72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="Z72" s="3" t="s">
         <v>37</v>
@@ -6975,11 +7149,11 @@
       <c r="AA72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AB72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC72" s="3">
         <v>6566100</v>
-      </c>
-      <c r="AC72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="AD72" s="3" t="s">
         <v>37</v>
@@ -6999,14 +7173,17 @@
       <c r="AI72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AJ72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AK72" s="3">
         <v>5306600</v>
       </c>
-      <c r="AK72" s="3" t="s">
+      <c r="AL72" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>19821400</v>
+      </c>
+      <c r="E76" s="3">
         <v>19000400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18839600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18014500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17627000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>17527500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16443100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>15755700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15815800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14765000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14557200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14017500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13486500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13134300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11909300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12244200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11930300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11432100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>12562000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>12644200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9875400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>9462600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>9759400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7784300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7298000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6569000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6070900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6257400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6383200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6787100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6680800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6461500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>6176800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>5554100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>5090500</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>1419600</v>
+      </c>
+      <c r="E81" s="3">
         <v>1201000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>932100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>930100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1057300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>928300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1074000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1136600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>983300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>557300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>925600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>735600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>606700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>784500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>452300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>503500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>617900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>135800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>441800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>668700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>560200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>470200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1960200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>469200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>363900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>246600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>223400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>302200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>107900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>190800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>375100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>441100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>582200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>535600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,8 +7996,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7807,106 +8006,109 @@
         <v>78700</v>
       </c>
       <c r="E83" s="3">
+        <v>78700</v>
+      </c>
+      <c r="F83" s="3">
         <v>89300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>91200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>157600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>98200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>100300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>90900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>120900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>108400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>98600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>84700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>105800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>115200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>114500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>115800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>114100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>134000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>134500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>131500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>108900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>107100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>106000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>98100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>89700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>98200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>79800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>67600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>52600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>40700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>31300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>25300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>21700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>14100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1668400</v>
+      </c>
+      <c r="E89" s="3">
         <v>1782700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1507700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>898800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1323600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1665300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1349100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1058800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>873600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1270100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1034300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>921900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>632800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1153000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>894500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>671300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>771500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1143400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>795900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>703200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1025500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>848500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>593400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>682300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>517400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>862000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>506300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>280900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>273300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>576000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>245700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>344500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>598300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>782200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>542400</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,115 +8806,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-62600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-42700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-54100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-23200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-57500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-68400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-88100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-71800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-95100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-510800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-709300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-530200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-893200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-739700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-625900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-988600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-45900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-42200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-51700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-34900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-25900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-36300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-50800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-41900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-56500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-73400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-80900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-111200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-96200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-84900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-76000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-64300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-48300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-67700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-24400</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,115 +9134,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1769600</v>
+      </c>
+      <c r="E94" s="3">
         <v>2826200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-102800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2043700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1781000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1512500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-70700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1598000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2531900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>544800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>136400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-164500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1524100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2144900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>3007600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-788000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-991800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>145500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1105500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2985100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-391000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1069600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1090100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-514900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-724400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1195600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-55800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-555300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-153300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-592900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-140100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-343300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-831600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-670000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-658900</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,115 +9286,119 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>769600</v>
+      </c>
+      <c r="E96" s="3">
         <v>271600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>281300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>311700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>684900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>318600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>332100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>292200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>176500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-284600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-223500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-195100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-232500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-129600</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-146100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-181800</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-36300</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-119900</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-203000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-164300</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-146200</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1061000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-142200</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-93700</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-63200</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-58000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-74700</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-27500</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-45300</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-92700</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-109200</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-145500</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-136100</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-100700</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-99400</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,325 +9724,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1142200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-337400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1205900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2190600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-68600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>724800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-939300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2802600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>83300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-871600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-992700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>116900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>316100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-147900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2117200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>281100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>195600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-887500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-367800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2973500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-219900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>180400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>112800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-188300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>62800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>406100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-127900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-41900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-6900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-171000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-31700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>16300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>17200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-24600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-6600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>7700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>11200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>7500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>10400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-11100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-3600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>5000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-9400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-3700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>26500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>11700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>5900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>5400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>7600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>11200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-5100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>4000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>9900</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1251200</v>
+      </c>
+      <c r="E102" s="3">
         <v>4287000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>189300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3334300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3030100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>853000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>339700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-152400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1572800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>950800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>178500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>884700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-578200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1150900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1786900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>160900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-19700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>392000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-681100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>718200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>426300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-44800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-378000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-15500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-146900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>70400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>330100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-305100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>114500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-25400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-61500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-34000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-217600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>139300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-112800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NTES_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NTES_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>NTES</t>
   </si>
@@ -656,492 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3893400</v>
+      </c>
+      <c r="E8" s="3">
         <v>3972800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3664500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3736500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3507100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3718800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3827500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3737400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3310900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3646200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3574400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3374800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3219600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3252600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3358200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3154400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2917600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2856000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2750800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2749500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2679700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2691800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2422800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2253600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2207400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2203400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1098200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1841900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2336400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2033500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2167900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1851800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1985100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2024400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1759600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1339600</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1373500</v>
+      </c>
+      <c r="E9" s="3">
         <v>1426200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1435200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1387600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1299500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1362200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1454700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1412200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1328700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1477600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1707200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1475900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1420400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1480100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1578400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1475500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1327000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1317500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1368900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1292700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1236700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1212300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1131300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1041700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1025400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1021300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>92700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>830800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1296900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1179300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1315400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>969100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>985300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>913700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>819600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>564000</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2520000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2546600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2229400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2348900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2207600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2356600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2372800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2325200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1982200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2168600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1867200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1898900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1799100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1772400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1779800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1678900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1590600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1538500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1381900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1456800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1443000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1479400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1291500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1211900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1182000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1182200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1005500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1011100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1039500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>854200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>852600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>882700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>999800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1110600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>940000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>775700</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,118 +1193,122 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>608100</v>
+      </c>
+      <c r="E12" s="3">
         <v>604500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>612400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>630800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>613200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>578200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>631700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>595800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>539000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>545900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>576600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>548400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>497900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>469200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>530100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>534700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>484300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>426000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>421700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>411000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>354900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>338000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>349100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>332900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>297300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>311300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>269400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>300500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>275100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>209300</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>184400</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>171100</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>156000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>137200</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>127600</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>119300</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1400,8 +1417,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1432,8 +1452,8 @@
       <c r="L14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1510,41 +1530,44 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>59800</v>
+      </c>
+      <c r="E15" s="3">
         <v>66300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>95600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>74200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>87000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>78700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>93000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>89300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>91200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>157600</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1620,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2628600</v>
+      </c>
+      <c r="E17" s="3">
         <v>2533900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2593000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2717700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2544800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2663100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2858800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2701600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2474900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2595100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2949400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2719700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2531900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2492200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2723300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2617800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2383300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2260800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2331600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2326500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2065200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1984000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1964500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1740100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1638400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1629700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>531600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1487000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2001600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1860400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1956200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1473400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1479700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1316200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1197200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>925700</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1264800</v>
+      </c>
+      <c r="E18" s="3">
         <v>1438900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1071600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1018900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>962400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1055700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>968600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1035800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>836000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1051100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>625000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>655100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>687600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>760400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>634900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>536600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>534200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>595200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>419300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>422900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>614500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>707800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>458300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>513500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>569000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>573700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>566600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>354900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>334800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>173200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>211700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>378400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>505400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>708200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>562300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>414000</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1917,239 +1950,246 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-42700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-35400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-248600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>144300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>21100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-28900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>53000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>22000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-218700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>18700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>48300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>478800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>109100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>274000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>50600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>118200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>210400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-212200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>39200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>227800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>86200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>152700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>140900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>55000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>49800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>68900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>55200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>50200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-17100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>24600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>32300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>43400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>27100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>105700</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>54700</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1367400</v>
+      </c>
+      <c r="E21" s="3">
         <v>1540600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1415700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>948800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1028200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1163300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1008600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1103200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1145800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1189900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>781800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1232600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>881400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>870100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1024100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>701700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>768200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>919700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>341000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>596700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>973700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>902800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>718200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>762700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>720800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>712200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>734400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>489200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>452600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>208600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>277000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>441900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>574100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>756900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>682100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>481700</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="3">
         <v>81900</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>37</v>
@@ -2157,11 +2197,11 @@
       <c r="H22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J22" s="3">
         <v>124700</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>37</v>
@@ -2169,8 +2209,8 @@
       <c r="L22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2247,228 +2287,237 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1486500</v>
+      </c>
+      <c r="E23" s="3">
         <v>1716000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1411700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1139900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1118700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1286400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1092200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1247300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1223300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1214000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>673400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1134000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>796800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>764300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>908900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>587200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>652400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>805600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>207100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>462100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>842300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>794000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>611000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>654400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>624000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>623500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>635400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>410100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>385000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>156000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>236300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>410700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>548800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>735300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>668100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>468700</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>217900</v>
+      </c>
+      <c r="E24" s="3">
         <v>262500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>189800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>183800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>179000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>205800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>150700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>176800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>98200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>237100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>136300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>219200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>175100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>168400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>128700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>114800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>158200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>177300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>76900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>50500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>156900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>170700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>134900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>13500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>104500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>193500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>132800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>118000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>60300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>40600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>43100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>33500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>104400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>140000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>128300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>62100</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1268700</v>
+      </c>
+      <c r="E26" s="3">
         <v>1453400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1221900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>956100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>939700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1080600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>941500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1070500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1125100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>976900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>537100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>914800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>621700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>595900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>780200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>472400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>494200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>628300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>130100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>411600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>685400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>623300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>476100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>640900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>519600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>429900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>502600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>292100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>324700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>115500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>193200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>377200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>444400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>595300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>539800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>406500</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1200600</v>
+      </c>
+      <c r="E27" s="3">
         <v>1419600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1201000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>932100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>930100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1057300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>928300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1074000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1136600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>983300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>557300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>925600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>648800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>606700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>784500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>452300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>503500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>617900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>135800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>441800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>668700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>560200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>470200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>636600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>512500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>417500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>489400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>288700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>302200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>107900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>190800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>375100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>441100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>582200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>535600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2946,16 +3007,16 @@
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>86900</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>37</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>37</v>
@@ -2963,14 +3024,14 @@
       <c r="T29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3" t="s">
+      <c r="U29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="X29" s="3">
         <v>0</v>
@@ -2979,28 +3040,28 @@
         <v>0</v>
       </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>1323600</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-43200</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-53600</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-242900</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-65300</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
+      <c r="AG29" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="AH29" s="3">
         <v>0</v>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3237,228 +3304,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>42700</v>
+      </c>
+      <c r="E32" s="3">
         <v>35400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>248600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-144300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-21100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>28900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-53000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-22000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>218700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-18700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-48300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-478800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-109100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-274000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-50600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-118200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-210400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>212200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-39200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-227800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-86200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-152700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-140900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-55000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-49800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-68900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-55200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-50200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>17100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-24600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-32300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-43400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-27100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-105700</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-54700</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>1200600</v>
+      </c>
+      <c r="E33" s="3">
         <v>1419600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1201000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>932100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>930100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1057300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>928300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1074000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1136600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>983300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>557300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>925600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>735600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>606700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>784500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>452300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>503500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>617900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>135800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>441800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>668700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>560200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>470200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1960200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>469200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>363900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>246600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>223400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>302200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>107900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>190800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>375100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>441100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>582200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>535600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>1200600</v>
+      </c>
+      <c r="E35" s="3">
         <v>1419600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1201000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>932100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>930100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1057300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>928300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1074000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1136600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>983300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>557300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>925600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>735600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>606700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>784500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>452300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>503500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>617900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>135800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>441800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>668700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>560200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>470200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1960200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>469200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>363900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>246600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>223400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>302200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>107900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>190800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>375100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>441100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>582200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>535600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3872,433 +3958,443 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>7598000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5753300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7039700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2877500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2612200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5959000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3022000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2071700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1760300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1994500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3508900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2486800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2288500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1360400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1997600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3165200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1412400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1223700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1269100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>952900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1565400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>882300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>499900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>422100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>738300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>631300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>724500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>668700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>441800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>534800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>410200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>382200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>447100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>587600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>791100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>651800</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>12878400</v>
+      </c>
+      <c r="E42" s="3">
         <v>13555600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>11821900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>14798300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>14294100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>12681800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>14860400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>13117100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>13380800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>15539500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>13050600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>13572300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>13218500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>12793000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>11440800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>9817800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>12928100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>12628000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>11741800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>13547400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>12606300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>11025600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>10593800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>9029400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>7748900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>7283200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>6473600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>5270700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>5889700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>5683300</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>5987800</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>5655100</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>5658600</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>5370000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>4500100</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>3836200</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>806300</v>
+      </c>
+      <c r="E43" s="3">
         <v>929100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1117700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>880000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>875900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1075800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1304800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>889800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>736700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>886800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>705300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>719500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>724700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>728700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>758900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>770800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>632900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>703900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>637000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>729300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>739500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>719300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>642000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>724700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>686700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>774700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>598200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>639500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>554400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>637900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>537200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>483700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>505200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>546600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>618300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>387100</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>82600</v>
+      </c>
+      <c r="E44" s="3">
         <v>71400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>78300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>87500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>79000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>83600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>98100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>98900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>111300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>127600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>140100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>128900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>117300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>118900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>132900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>147600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>125700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>121800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>86500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>77300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>82300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>88700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>100200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>105700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>606000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>653500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>154800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>880500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>814400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>734800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>812500</v>
-      </c>
-      <c r="AH44" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="AI44" s="3" t="s">
         <v>37</v>
@@ -4306,487 +4402,502 @@
       <c r="AJ44" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AK44" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AL44" s="3">
         <v>229500</v>
       </c>
-      <c r="AL44" s="3" t="s">
+      <c r="AM44" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>860200</v>
+      </c>
+      <c r="E45" s="3">
         <v>917000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>30800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>971000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>755200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>799100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>30400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>888500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>738100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>735300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1148600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1273300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1446800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1440700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1255600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1584900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1384500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1404200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1275600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1457600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1380100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1517400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1268600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2428400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1379700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1603500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2028600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1351100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1249200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1503400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1445900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2209500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1940600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1537400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1120900</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>922600</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>22746300</v>
+      </c>
+      <c r="E46" s="3">
         <v>21728200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>21006000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>20041200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>19011300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>21022400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>20123300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>17482900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>17128900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>19732600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>18553400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>18180800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>17795800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>16441700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>15585700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>15486300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>16483600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>16081600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>15010100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>16764400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>16373600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>14233300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>13104500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>12710400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>11159600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>10946200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>9979600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>8810600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>8949500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>9094200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>9193700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>8730600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>8551400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>8041600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>7181800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>5797700</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>409700</v>
+      </c>
+      <c r="E47" s="3">
         <v>416900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3182800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>573800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>542200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>145400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3220100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>304400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>369800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>397700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3033600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>618100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>622000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>617700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3393300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>988400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1009300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>938200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2553100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>626300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1005500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>607400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1794500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>7700</v>
-      </c>
-      <c r="AA47" s="3">
-        <v>7600</v>
       </c>
       <c r="AB47" s="3">
         <v>7600</v>
       </c>
       <c r="AC47" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AD47" s="3">
         <v>776400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>21000</v>
-      </c>
-      <c r="AE47" s="3">
-        <v>21500</v>
       </c>
       <c r="AF47" s="3">
         <v>21500</v>
       </c>
       <c r="AG47" s="3">
+        <v>21500</v>
+      </c>
+      <c r="AH47" s="3">
         <v>413300</v>
-      </c>
-      <c r="AH47" s="3">
-        <v>7400</v>
       </c>
       <c r="AI47" s="3">
         <v>7400</v>
       </c>
       <c r="AJ47" s="3">
+        <v>7400</v>
+      </c>
+      <c r="AK47" s="3">
         <v>74200</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>366500</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1179100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1165100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1241400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1169100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1113500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1115800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1244500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1039200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1013100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>963400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1019300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>851800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>837200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>806700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>892500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>704600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>667300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>647500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>741700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>654200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>650800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1302800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1353900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1301600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>945300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>944100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>678700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>742600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>699200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>611500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>559400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>498100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>442500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>398600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>351900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>314500</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>573900</v>
+      </c>
+      <c r="E49" s="3">
         <v>570700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1019400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>599500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>553500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>560700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1102100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>563200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>571900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>600100</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
       <c r="N49" s="3">
         <v>0</v>
       </c>
@@ -4832,38 +4943,41 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-      <c r="AC49" s="3" t="s">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>492700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>84200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>84700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>88000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>88500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>86500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>86900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>85600</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>86100</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,118 +5199,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3889700</v>
+      </c>
+      <c r="E52" s="3">
         <v>3622000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>247000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3808400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3802200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3966700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>305300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3929800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3886300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4069300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1749500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4210700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4125300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4122900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1297500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3828800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3852800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3282900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1444000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3282800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3215000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2575400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1012100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2275000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2065600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2072100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1957600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1128300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1064000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>773500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>287400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>544500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>588900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>726800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>453800</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>847100</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>29104500</v>
+      </c>
+      <c r="E54" s="3">
         <v>27679800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>26851500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>26359200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>25229800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>27015400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>26220200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>23514400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23152100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>25947900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>24355800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>23861300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>23380300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>21989000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>21169100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>21008100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>22012900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>20950100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>19748900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>21327700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>21244900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>18718800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>17264900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>16294800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>14178000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>13970100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>12630400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>11195300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>10818400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>10585300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>10541800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>9869200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>9676800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>9328300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>8439600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>7221400</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,448 +5622,461 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>97100</v>
+      </c>
+      <c r="E57" s="3">
         <v>77900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>98700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>107700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>109000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>120700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>124200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>118300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>102100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>121000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>212500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>119800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>131000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>127700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>135700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>156200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>126500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>149100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>157900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>146900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>125800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>188800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>186700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>187800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>398700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>450600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>174500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>360300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>331200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>339400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>362500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>307000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>281800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>234400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>203000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>110800</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1574100</v>
+      </c>
+      <c r="E58" s="3">
         <v>1353800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1640800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1510300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1814700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3440700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2750000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1537900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1638300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3987800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3366000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3515600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3896300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3131600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2666400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2788200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3864800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3038300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2715100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3278400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3232000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3096000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2591200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2385900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2070800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2159500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1983600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1909900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1825900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1365400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>983000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>850800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>798100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>665400</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>554900</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>437000</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2898300</v>
+      </c>
+      <c r="E59" s="3">
         <v>3074000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3413900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2587500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2201400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2597600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3128900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2365600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2137800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2408600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4433300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4243700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3958700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3888400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4156000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4022200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3733400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3862800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3633700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3490100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3302200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3563100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3110800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2755700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2714800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2925100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2940700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2365900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2092900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2295300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2179300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1824600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1916500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2096200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2083000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1540700</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7042600</v>
+      </c>
+      <c r="E60" s="3">
         <v>6771600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6804600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6516800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6320100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8316500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7593200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6012200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5838000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8469800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8011700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7879100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7986000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7147600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6958100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6966500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7724700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7050200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6506700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6915400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6660000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6848000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5888700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5329300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5184200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5535100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5098900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4636100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4250000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4000100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3524800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2982400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2996300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2995900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2788800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2088600</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5941,47 +6084,47 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>115200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>61000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>58900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>59300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>138700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>58700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>545200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>543000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>515300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>490500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>466500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>438300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>175700</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -6042,118 +6185,124 @@
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>170000</v>
+      </c>
+      <c r="E62" s="3">
         <v>162500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>111800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>170900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>164100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>172900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>100900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>181900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>156900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>169600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>479900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>342600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>343700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>350100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>336700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>331200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>284400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>241500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>186100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>154400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>214700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>166100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>129300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>185900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>210400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>168600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>65000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>87600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>84800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>60500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>34400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>17800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>41800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>27800</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>57100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7593000</v>
+      </c>
+      <c r="E66" s="3">
         <v>7302300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7329300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7009500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6742500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>8922700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>8157100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6527700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6844700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9545200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9590800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9304100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9362800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8502500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8034800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9098800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>9768700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9019800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>8316900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8765700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8600700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>8843500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>7802300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6535300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6393700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6672100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6061400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5124400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4561000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4202100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3754700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3188400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3215300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>3151400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2885400</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>2130900</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,19 +7243,22 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E72" s="3">
+      <c r="E72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F72" s="3">
         <v>18123900</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>37</v>
@@ -7092,11 +7266,11 @@
       <c r="H72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J72" s="3">
         <v>16042500</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>37</v>
@@ -7104,11 +7278,11 @@
       <c r="L72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="N72" s="3">
         <v>13020000</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>37</v>
@@ -7116,11 +7290,11 @@
       <c r="P72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="R72" s="3">
         <v>10848700</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>37</v>
@@ -7128,11 +7302,11 @@
       <c r="T72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="V72" s="3">
         <v>9102400</v>
-      </c>
-      <c r="V72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="W72" s="3" t="s">
         <v>37</v>
@@ -7140,11 +7314,11 @@
       <c r="X72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z72" s="3">
         <v>8870600</v>
-      </c>
-      <c r="Z72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="AA72" s="3" t="s">
         <v>37</v>
@@ -7152,11 +7326,11 @@
       <c r="AB72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD72" s="3">
         <v>6566100</v>
-      </c>
-      <c r="AD72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="AE72" s="3" t="s">
         <v>37</v>
@@ -7176,14 +7350,17 @@
       <c r="AJ72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AK72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AL72" s="3">
         <v>5306600</v>
       </c>
-      <c r="AL72" s="3" t="s">
+      <c r="AM72" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20881000</v>
+      </c>
+      <c r="E76" s="3">
         <v>19821400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>19000400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18839600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>18014500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>17627000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>17527500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16443100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15755700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15815800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14765000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14557200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14017500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13486500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13134300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11909300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12244200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11930300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11432100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>12562000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>12644200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>9875400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>9462600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>9759400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7784300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7298000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6569000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6070900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6257400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6383200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6787100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6680800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>6461500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>6176800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>5554100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>5090500</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>1200600</v>
+      </c>
+      <c r="E81" s="3">
         <v>1419600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1201000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>932100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>930100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1057300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>928300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1074000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1136600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>983300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>557300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>925600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>735600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>606700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>784500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>452300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>503500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>617900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>135800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>441800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>668700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>560200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>470200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1960200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>469200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>363900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>246600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>223400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>302200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>107900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>190800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>375100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>441100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>582200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>535600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,118 +8195,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>78700</v>
+        <v>87000</v>
       </c>
       <c r="E83" s="3">
         <v>78700</v>
       </c>
       <c r="F83" s="3">
+        <v>78700</v>
+      </c>
+      <c r="G83" s="3">
         <v>89300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>91200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>157600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>98200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>100300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>90900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>120900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>108400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>98600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>84700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>105800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>115200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>114500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>115800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>114100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>134000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>134500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>131500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>108900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>107100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>106000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>98100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>89700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>98200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>79800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>67600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>52600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>40700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>31300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>25300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>21700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>14100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1516200</v>
+      </c>
+      <c r="E89" s="3">
         <v>1668400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1782700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1507700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>898800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1323600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1665300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1349100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1058800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>873600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1270100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1034300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>921900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>632800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1153000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>894500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>671300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>771500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1143400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>795900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>703200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1025500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>848500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>593400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>682300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>517400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>862000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>506300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>280900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>273300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>576000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>245700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>344500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>598300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>782200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>542400</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,118 +9027,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-26500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-62600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-42700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-54100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-23200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-57500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-68400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-88100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-71800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-95100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-510800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-709300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-530200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-893200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-739700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-625900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-988600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-45900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-42200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-51700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-34900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-25900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-36300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-50800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-41900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-56500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-73400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-80900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-111200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-96200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-84900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-76000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-64300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-48300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-67700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-24400</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>543400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1769600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>2826200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-102800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2043700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>1781000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1512500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-70700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1598000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2531900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>544800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>136400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-164500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1524100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2144900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>3007600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-788000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-991800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>145500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1105500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2985100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-391000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1069600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1090100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-514900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-724400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1195600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-55800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-555300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-153300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-592900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-140100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-343300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-831600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-670000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-658900</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,118 +9520,122 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>430200</v>
+      </c>
+      <c r="E96" s="3">
         <v>769600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>271600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>281300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>311700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>684900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>318600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>332100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>292200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>176500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-284600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-223500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-195100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-232500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-129600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-146100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-181800</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-36300</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-119900</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-203000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-164300</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-146200</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-1061000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-142200</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-93700</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-63200</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-58000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-74700</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-27500</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-45300</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-92700</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-109200</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-145500</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-136100</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-100700</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-99400</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,334 +9970,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-272400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1142200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-337400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1205900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2190600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-68600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>724800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-939300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2802600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>83300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-871600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-992700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>116900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>316100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-147900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2117200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>281100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>195600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-887500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-367800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2973500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-219900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>180400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>112800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-188300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>62800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>406100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-127900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-41900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-6900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-171000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-31700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>16300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>17200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-6000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-24600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-6600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>7700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>11200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>7500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>10400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-11100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-3600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>5000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-9400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-3700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>26500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>11700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>5900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>5400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>7600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>11200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-5100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>4000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-600</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>9900</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1782800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1251200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4287000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>189300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3334300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3030100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>853000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>339700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-152400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1572800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>950800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>178500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>884700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-578200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1150900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1786900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>160900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-19700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>392000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-681100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>718200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>426300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-44800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-378000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-15500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-146900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>70400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>330100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-305100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>114500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-25400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-61500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-34000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-217600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>139300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-112800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NTES_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NTES_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
   <si>
     <t>NTES</t>
   </si>
@@ -656,518 +656,543 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4435200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3938400</v>
+      </c>
+      <c r="F8" s="3">
         <v>3983400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>3893400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>3972800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>3664500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>3736500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>3507100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>3718800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>3827500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>3737400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>3310900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>3646200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>3574400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>3374800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>3219600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>3252600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>3358200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>3154400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>2917600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>2856000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>2750800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>2749500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>2679700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>2691800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>2422800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>2253600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>2207400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>2203400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>1098200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>1841900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>2336400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>2033500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>2167900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>1851800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>1985100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>2024400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>1759600</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>1339600</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1359100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1408900</v>
+      </c>
+      <c r="F9" s="3">
         <v>1430100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1373500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1426200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>1435200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1387600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1299500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1362200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1454700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1412200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1328700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>1477600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>1707200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1475900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1420400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1480100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>1578400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1475500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>1327000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1317500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>1368900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>1292700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>1236700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>1212300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>1131300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>1041700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>1025400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>1021300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>92700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>830800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>1296900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>1179300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>1315400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>969100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>985300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>913700</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>819600</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AP9" s="3">
         <v>564000</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3076100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2529500</v>
+      </c>
+      <c r="F10" s="3">
         <v>2553300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>2520000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>2546600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>2229400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>2348900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>2207600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>2356600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>2372800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>2325200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>1982200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>2168600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1867200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1898900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1799100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1772400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1779800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>1678900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>1590600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>1538500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>1381900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>1456800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>1443000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>1479400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>1291500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>1211900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>1182000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>1182200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>1005500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>1011100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>1039500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>854200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>852600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>882700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>999800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>1110600</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>940000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AP10" s="3">
         <v>775700</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,124 +1233,132 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>649800</v>
+      </c>
+      <c r="E12" s="3">
+        <v>634000</v>
+      </c>
+      <c r="F12" s="3">
         <v>638000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>608100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>604500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>612400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>630800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>613200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>578200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>631700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>595800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>539000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>545900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>576600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>548400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>497900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>469200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>530100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>534700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>484300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>426000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>421700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>411000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>354900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>338000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>349100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>332900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>297300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>311300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>269400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>300500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>275100</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AJ12" s="3">
         <v>209300</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>184400</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>171100</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AM12" s="3">
         <v>156000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AN12" s="3">
         <v>137200</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AO12" s="3">
         <v>127600</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AP12" s="3">
         <v>119300</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1440,8 +1473,14 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1478,11 +1517,11 @@
       <c r="N14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1556,50 +1595,56 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>62400</v>
+      </c>
+      <c r="E15" s="3">
+        <v>103000</v>
+      </c>
+      <c r="F15" s="3">
         <v>86800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>59800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>66300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>95600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>74200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>87000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>78700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>93000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>89300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>91200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>157600</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1672,8 +1717,14 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1762,254 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2600200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2749000</v>
+      </c>
+      <c r="F17" s="3">
         <v>2857800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2628600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2533900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>2593000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2717700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>2544800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2663100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>2858800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2701600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2474900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>2595100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>2949400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>2719700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2531900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>2492200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>2723300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>2617800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>2383300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2260800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>2331600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>2326500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>2065200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>1984000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>1964500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>1740100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>1638400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>1629700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>531600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>1487000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>2001600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>1860400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>1956200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>1473400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>1479700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>1316200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>1197200</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>925700</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1835000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1189400</v>
+      </c>
+      <c r="F18" s="3">
         <v>1125600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>1264800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>1438900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>1071600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>1018900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>962400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>1055700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>968600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>1035800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>836000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>1051100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>625000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>655100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>687600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>760400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>634900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>536600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>534200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>595200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>419300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>422900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>614500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>707800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>458300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>513500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>569000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>573700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>566600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>354900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>334800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>173200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>211700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>378400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>505400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>708200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>562300</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>414000</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1985,281 +2050,295 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E20" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F20" s="3">
         <v>31000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-42700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-35400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-248600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>144300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>21100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-28900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>53000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>22000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-218700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>18700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>48300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>478800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>109100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>3900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>274000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>50600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>118200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>210400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-212200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>39200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>227800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>86200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>152700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>140900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>55000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>49800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>68900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>55200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>50200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>-17100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>24600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>32300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>43400</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>27100</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>105700</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AP20" s="3">
         <v>54700</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1870900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1287800</v>
+      </c>
+      <c r="F21" s="3">
         <v>1181400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>1367400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>1540600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>1415700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>948800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>1028200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>1163300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>1008600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>1103200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>1145800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1189900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>781800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>1232600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>881400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>870100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>1024100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>701700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>768200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>919700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>341000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>596700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>973700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>902800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>718200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>762700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>720800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>712200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>734400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>489200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>452600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>208600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>277000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>441900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>574100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>756900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>682100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>481700</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>37</v>
+      <c r="E22" s="3">
+        <v>47800</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G22" s="3">
-        <v>81900</v>
+      <c r="G22" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>37</v>
+      <c r="I22" s="3">
+        <v>81900</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K22" s="3">
-        <v>124700</v>
+      <c r="K22" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>37</v>
+      <c r="M22" s="3">
+        <v>124700</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2333,240 +2412,258 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1938300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1089500</v>
+      </c>
+      <c r="F23" s="3">
         <v>1420000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>1486500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>1716000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>1411700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>1139900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>1118700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>1286400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>1092200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>1247300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1223300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>1214000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>673400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>1134000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>796800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>764300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>908900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>587200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>652400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>805600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>207100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>462100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>842300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>794000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>611000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>654400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>624000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>623500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>635400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>410100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>385000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>156000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>236300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>410700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>548800</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>735300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>668100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>468700</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>365900</v>
+      </c>
+      <c r="E24" s="3">
+        <v>178800</v>
+      </c>
+      <c r="F24" s="3">
         <v>184900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>217900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>262500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>189800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>183800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>179000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>205800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>150700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>176800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>98200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>237100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>136300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>219200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>175100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>168400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>128700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>114800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>158200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>177300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>76900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>50500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>156900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>170700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>134900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>13500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>104500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>193500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>132800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>118000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>60300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>40600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>43100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>33500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>104400</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>140000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>128300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>62100</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2681,240 +2778,258 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1572400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>910700</v>
+      </c>
+      <c r="F26" s="3">
         <v>1235100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>1268700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>1453400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>1221900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>956100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>939700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>1080600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>941500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>1070500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1125100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>976900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>537100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>914800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>621700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>595900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>780200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>472400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>494200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>628300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>130100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>411600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>685400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>623300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>476100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>640900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>519600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>429900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>502600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>292100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>324700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>115500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>193200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>377200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>444400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>595300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>539800</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>406500</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1547600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>892400</v>
+      </c>
+      <c r="F27" s="3">
         <v>1210200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>1200600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>1419600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>1201000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>932100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>930100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>1057300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>928300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1074000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1136600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>983300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>557300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>925600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>648800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>606700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>784500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>452300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>503500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>617900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>135800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>441800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>668700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>560200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>470200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>636600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>512500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>417500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>489400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>288700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>302200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>107900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>190800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>375100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>441100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>582200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>535600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3029,8 +3144,14 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3074,25 +3195,25 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>86900</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>37</v>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>37</v>
@@ -3100,39 +3221,39 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="AA29" s="3">
         <v>0</v>
       </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>1323600</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AE29" s="3">
         <v>-43200</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AF29" s="3">
         <v>-53600</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AG29" s="3">
         <v>-242900</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AH29" s="3">
         <v>-65300</v>
       </c>
-      <c r="AG29" s="3" t="s">
+      <c r="AI29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AH29" s="3" t="s">
+      <c r="AJ29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ29" s="3">
-        <v>0</v>
-      </c>
       <c r="AK29" s="3">
         <v>0</v>
       </c>
@@ -3145,8 +3266,14 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3261,8 +3388,14 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3377,240 +3510,258 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F32" s="3">
         <v>-31000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>42700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>35400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>248600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-144300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-21100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>28900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-53000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-22000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>218700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-18700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-48300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-478800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-109100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-3900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-274000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-50600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-118200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-210400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>212200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-39200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-227800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-86200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-152700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-140900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-55000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-49800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-68900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-55200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-50200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>17100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-24600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-32300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>-43400</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>-27100</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>-105700</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AP32" s="3">
         <v>-54700</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>1547600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>892400</v>
+      </c>
+      <c r="F33" s="3">
         <v>1210200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>1200600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>1419600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>1201000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>932100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>930100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>1057300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>928300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>1074000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1136600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>983300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>557300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>925600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>735600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>606700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>784500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>452300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>503500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>617900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>135800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>441800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>668700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>560200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>470200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>1960200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>469200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>363900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>246600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>223400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>302200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>107900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>190800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>375100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>441100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>582200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>535600</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3725,245 +3876,263 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>1547600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>892400</v>
+      </c>
+      <c r="F35" s="3">
         <v>1210200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>1200600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>1419600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>1201000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>932100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>930100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>1057300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>928300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>1074000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1136600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>983300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>557300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>925600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>735600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>606700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>784500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>452300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>503500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>617900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>135800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>441800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>668700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>560200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>470200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>1960200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>469200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>363900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>246600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>223400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>302200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>107900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>190800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>375100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>441100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>582200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>535600</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -4004,8 +4173,10 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -4046,978 +4217,1028 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>7367300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>6743700</v>
+      </c>
+      <c r="F41" s="3">
         <v>4400300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>7598000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>5753300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>7039700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2877500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2612200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>5959000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3022000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2071700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1760300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1994500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>3508900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>2486800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>2288500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>1360400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1997600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>3165200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1412400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1223700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1269100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>952900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>1565400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>882300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>499900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>422100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>738300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>631300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>724500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>668700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>441800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>534800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>410200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>382200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>447100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>587600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>791100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>651800</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>17410700</v>
+      </c>
+      <c r="E42" s="3">
+        <v>16738000</v>
+      </c>
+      <c r="F42" s="3">
         <v>16542100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>12878400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>13555600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>11821900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>14798300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>14294100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>12681800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>14860400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>13117100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>13380800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>15539500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>13050600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>13572300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>13218500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>12793000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>11440800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>9817800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>12928100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>12628000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>11741800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>13547400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>12606300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>11025600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>10593800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>9029400</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>7748900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>7283200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>6473600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>5270700</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>5889700</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AJ42" s="3">
         <v>5683300</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AK42" s="3">
         <v>5987800</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AL42" s="3">
         <v>5655100</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AM42" s="3">
         <v>5658600</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AN42" s="3">
         <v>5370000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AO42" s="3">
         <v>4500100</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AP42" s="3">
         <v>3836200</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>941400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1029200</v>
+      </c>
+      <c r="F43" s="3">
         <v>837500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>806300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>929100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1117700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>880000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>875900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1075800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1304800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>889800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>736700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>886800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>705300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>719500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>724700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>728700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>758900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>770800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>632900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>703900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>637000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>729300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>739500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>719300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>642000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>724700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>686700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>774700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>598200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>639500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>554400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>637900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>537200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>483700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>505200</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>546600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>618300</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AP43" s="3">
         <v>387100</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>79200</v>
+      </c>
+      <c r="E44" s="3">
+        <v>98500</v>
+      </c>
+      <c r="F44" s="3">
         <v>89500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>82600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>71400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>78300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>87500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>79000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>83600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>98100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>98900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>111300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>127600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>140100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>128900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>117300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>118900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>132900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>147600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>125700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>121800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>86500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>77300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>82300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>88700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>100200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>105700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>606000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>653500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>154800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>880500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>814400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>734800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>812500</v>
-      </c>
-      <c r="AJ44" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AK44" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="AL44" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AM44" s="3">
-        <v>229500</v>
+      <c r="AM44" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="AN44" s="3" t="s">
         <v>37</v>
       </c>
+      <c r="AO44" s="3">
+        <v>229500</v>
+      </c>
+      <c r="AP44" s="3" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>900800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>35200</v>
+      </c>
+      <c r="F45" s="3">
         <v>964000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>860200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>917000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>30800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>971000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>755200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>799100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>30400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>888500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>738100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>735300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1148600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1273300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1446800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1440700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>1255600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>1584900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>1384500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1404200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>1275600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>1457600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>1380100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>1517400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>1268600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>2428400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>1379700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>1603500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>2028600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>1351100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>1249200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>1503400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>1445900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>2209500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>1940600</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>1537400</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>1120900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>922600</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>27352100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>25822900</v>
+      </c>
+      <c r="F46" s="3">
         <v>24049000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>22746300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>21728200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>21006000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>20041200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>19011300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>21022400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>20123300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>17482900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>17128900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>19732600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>18553400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>18180800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>17795800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>16441700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>15585700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>15486300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>16483600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>16081600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>15010100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>16764400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>16373600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>14233300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>13104500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>12710400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>11159600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>10946200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>9979600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>8810600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>8949500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>9094200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>9193700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>8730600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>8551400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>8041600</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>7181800</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>5797700</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>441500</v>
+      </c>
+      <c r="E47" s="3">
+        <v>3067900</v>
+      </c>
+      <c r="F47" s="3">
         <v>399600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>409700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>416900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>3182800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>573800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>542200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>145400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>3220100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>304400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>369800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>397700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>3033600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>618100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>622000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>617700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>3393300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>988400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>1009300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>938200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>2553100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>626300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>1005500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>607400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>1794500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>7700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>7600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>7600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>776400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>21000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>21500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>21500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AK47" s="3">
         <v>413300</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AL47" s="3">
         <v>7400</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AM47" s="3">
         <v>7400</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AN47" s="3">
         <v>74200</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AO47" s="3">
         <v>366500</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AP47" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1205000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1250400</v>
+      </c>
+      <c r="F48" s="3">
         <v>1196400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1179100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1165100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1241400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1169100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1113500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1115800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1244500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1039200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1013100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>963400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1019300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>851800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>837200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>806700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>892500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>704600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>667300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>647500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>741700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>654200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>650800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>1302800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>1353900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>1301600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>945300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>944100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>678700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>742600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>699200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>611500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>559400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>498100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>442500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>398600</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>351900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>314500</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>582100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>979400</v>
+      </c>
+      <c r="F49" s="3">
         <v>572900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>573900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>570700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1019400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>599500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>553500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>560700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1102100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>563200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>571900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>600100</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
-      <c r="P49" s="3">
-        <v>0</v>
-      </c>
       <c r="Q49" s="3">
         <v>0</v>
       </c>
@@ -5060,38 +5281,44 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-      <c r="AE49" s="3" t="s">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>492700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>84200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>84700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>88000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>88500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>86500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>86900</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>85600</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AP49" s="3">
         <v>86100</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5433,14 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,124 +5555,136 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3548100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>128400</v>
+      </c>
+      <c r="F52" s="3">
         <v>3543400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>3889700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>3622000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>247000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>3808400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>3802200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>3966700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>305300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>3929800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>3886300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>4069300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1749500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>4210700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>4125300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>4122900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>1297500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>3828800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>3852800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>3282900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>1444000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>3282800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>3215000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>2575400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>1012100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>2275000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>2065600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>2072100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>1957600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>1128300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>1064000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>773500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>287400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>544500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>588900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>726800</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>453800</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>847100</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5799,136 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>33548400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>31656000</v>
+      </c>
+      <c r="F54" s="3">
         <v>30128200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>29104500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>27679800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>26851500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>26359200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>25229800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>27015400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>26220200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>23514400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>23152100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>25947900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>24355800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>23861300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>23380300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>21989000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>21169100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>21008100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>22012900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>20950100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>19748900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>21327700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>21244900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>18718800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>17264900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>16294800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>14178000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>13970100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>12630400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>11195300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>10818400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>10585300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>10541800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>9869200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>9676800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>9328300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>8439600</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>7221400</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5969,10 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,472 +6013,498 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>113200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>92000</v>
+      </c>
+      <c r="F57" s="3">
         <v>100900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>97100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>77900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>98700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>107700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>109000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>120700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>124200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>118300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>102100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>121000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>212500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>119800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>131000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>127700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>135700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>156200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>126500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>149100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>157900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>146900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>125800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>188800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>186700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>187800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>398700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>450600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>174500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>360300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>331200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>339400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>362500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>307000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>281800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>234400</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>203000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>110800</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1588300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>929000</v>
+      </c>
+      <c r="F58" s="3">
         <v>1032400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1574100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1353800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1640800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1510300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1814700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>3440700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2750000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1537900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1638300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>3987800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>3366000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>3515600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>3896300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>3131600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>2666400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>2788200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>3864800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>3038300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>2715100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>3278400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>3232000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>3096000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>2591200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>2385900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>2070800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>2159500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>1983600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>1909900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>1825900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>1365400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>983000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>850800</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>798100</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AN58" s="3">
         <v>665400</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AO58" s="3">
         <v>554900</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AP58" s="3">
         <v>437000</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3998200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>4704000</v>
+      </c>
+      <c r="F59" s="3">
         <v>3341100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2898300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>3074000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>3413900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2587500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2201400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2597600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>3128900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2365600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>2137800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2408600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>4433300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>4243700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>3958700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>3888400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>4156000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>4022200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>3733400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>3862800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>3633700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>3490100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>3302200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>3563100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>3110800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>2755700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>2714800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>2925100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>2940700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>2365900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>2092900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>2295300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>2179300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>1824600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>1916500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>2096200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>2083000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>1540700</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8327400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>7487300</v>
+      </c>
+      <c r="F60" s="3">
         <v>7035700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>7042600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>6771600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>6804600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>6516800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>6320100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>8316500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>7593200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>6012200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>5838000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>8469800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>8011700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>7879100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>7986000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>7147600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>6958100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>6966500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>7724700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>7050200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>6506700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>6915400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>6660000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>6848000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>5888700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>5329300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>5184200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>5535100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>5098900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>4636100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>4250000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>4000100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>3524800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>2982400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>2996300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>2995900</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>2788800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>2088600</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -6227,56 +6512,56 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>33200</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>115200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>61000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>58900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>59300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>138700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>58700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>545200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>543000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>515300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>490500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>466500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>438300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>175700</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -6334,124 +6619,136 @@
       <c r="AN61" s="3">
         <v>0</v>
       </c>
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>199800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>153400</v>
+      </c>
+      <c r="F62" s="3">
         <v>176400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>170000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>162500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>111800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>170900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>164100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>172900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>100900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>181900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>156900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>169600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>479900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>342600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>343700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>350100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>336700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>331200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>284400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>241500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>186100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>154400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>214700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>166100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>129300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>185900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>210400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>168600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>65000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>87600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>84800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>60500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>34400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>17800</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>41800</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>27800</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>57100</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6863,14 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6682,8 +6985,14 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +7107,136 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8995800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>8050900</v>
+      </c>
+      <c r="F66" s="3">
         <v>7522900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>7593000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>7302300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>7329300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>7009500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>6742500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>8922700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>8157100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>6527700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>6844700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>9545200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>9590800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>9304100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>9362800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>8502500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>8034800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>9098800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>9768700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>9019800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>8316900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>8765700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>8600700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>8843500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>7802300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>6535300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>6393700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>6672100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>6061400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>5124400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>4561000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>4202100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>3754700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>3188400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>3215300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>3151400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>2885400</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>2130900</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7277,10 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7395,14 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7517,14 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7639,14 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,100 +7761,106 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>37</v>
+      <c r="E72" s="3">
+        <v>21762000</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G72" s="3">
-        <v>18123900</v>
+      <c r="G72" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>37</v>
+      <c r="I72" s="3">
+        <v>18123900</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K72" s="3">
-        <v>16042500</v>
+      <c r="K72" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>37</v>
+      <c r="M72" s="3">
+        <v>16042500</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O72" s="3">
-        <v>13020000</v>
+      <c r="O72" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="P72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>37</v>
+      <c r="Q72" s="3">
+        <v>13020000</v>
       </c>
       <c r="R72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="S72" s="3">
-        <v>10848700</v>
+      <c r="S72" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>37</v>
+      <c r="U72" s="3">
+        <v>10848700</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="W72" s="3">
-        <v>9102400</v>
+      <c r="W72" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="X72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>37</v>
+      <c r="Y72" s="3">
+        <v>9102400</v>
       </c>
       <c r="Z72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AA72" s="3">
-        <v>8870600</v>
+      <c r="AA72" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="AB72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>37</v>
+      <c r="AC72" s="3">
+        <v>8870600</v>
       </c>
       <c r="AD72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AE72" s="3">
-        <v>6566100</v>
+      <c r="AE72" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="AF72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>37</v>
+      <c r="AG72" s="3">
+        <v>6566100</v>
       </c>
       <c r="AH72" s="3" t="s">
         <v>37</v>
@@ -7530,14 +7877,20 @@
       <c r="AL72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AM72" s="3">
-        <v>5306600</v>
+      <c r="AM72" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="AN72" s="3" t="s">
         <v>37</v>
       </c>
+      <c r="AO72" s="3">
+        <v>5306600</v>
+      </c>
+      <c r="AP72" s="3" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +8005,14 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +8127,14 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8249,136 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>23881800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>22917800</v>
+      </c>
+      <c r="F76" s="3">
         <v>21948600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>20881000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>19821400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>19000400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>18839600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>18014500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>17627000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>17527500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>16443100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>15755700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>15815800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>14765000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>14557200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>14017500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>13486500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>13134300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>11909300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>12244200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>11930300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>11432100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>12562000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>12644200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>9875400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>9462600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>9759400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>7784300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>7298000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>6569000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>6070900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>6257400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>6383200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>6787100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>6680800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>6461500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>6176800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>5554100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>5090500</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,245 +8493,263 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>1547600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>892400</v>
+      </c>
+      <c r="F81" s="3">
         <v>1210200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>1200600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>1419600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>1201000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>932100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>930100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>1057300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>928300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>1074000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1136600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>983300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>557300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>925600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>735600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>606700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>784500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>452300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>503500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>617900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>135800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>441800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>668700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>560200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>470200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>1960200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>469200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>363900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>246600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>223400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>302200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>107900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>190800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>375100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>441100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>582200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>535600</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>398500</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,124 +8790,132 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>66300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>80100</v>
+      </c>
+      <c r="F83" s="3">
         <v>74200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>87000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>78700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>78700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>89300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>91200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>157600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>98200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>100300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>90900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>120900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>108400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>98600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>84700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>105800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>115200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>114500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>115800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>114100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>134000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>134500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>131500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>108900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>107100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>106000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>98100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>89700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>98200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>79800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>67600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>52600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>40700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>31300</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>25300</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>21700</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>14100</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AP83" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +9030,14 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +9152,14 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9274,14 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9396,14 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9518,136 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1991100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>2119300</v>
+      </c>
+      <c r="F89" s="3">
         <v>1818700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1516200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>1668400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>1782700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>1507700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>898800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1323600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>1665300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1349100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1058800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>873600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>1270100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>1034300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>921900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>632800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>1153000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>894500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>671300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>771500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>1143400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>795900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>703200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>1025500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>848500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>593400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>682300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>517400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>862000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>506300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>280900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>273300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>576000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>245700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>344500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>598300</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>782200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>542400</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,124 +9688,132 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-45300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-19700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-39800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-26500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-62600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-42700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-54100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-23200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-57500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-68400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-88100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-71800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-95100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-510800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-709300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-530200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-893200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-739700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-625900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-988600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-45900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-42200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-51700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-34900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-25900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-36300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-50800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-41900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-56500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-73400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-80900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-111200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-96200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-84900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-76000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-64300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-48300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-67700</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AP91" s="3">
         <v>-24400</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9928,14 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,124 +10050,136 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1125700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>55400</v>
+      </c>
+      <c r="F94" s="3">
         <v>-3458300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>543400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-1769600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>2826200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-102800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-2043700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>1781000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-1512500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-70700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>1598000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-2531900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>544800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>136400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-164500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-1524100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-2144900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>3007600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-788000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-991800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>145500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-1105500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-2985100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-391000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-1069600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-1090100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-514900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-724400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-1195600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-55800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-555300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-153300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-592900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-140100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-343300</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-831600</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-670000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>-658900</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,124 +10220,132 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>747600</v>
+      </c>
+      <c r="E96" s="3">
+        <v>368200</v>
+      </c>
+      <c r="F96" s="3">
         <v>362900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>430200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>769600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>271600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>281300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>311700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>684900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>318600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>332100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>292200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>176500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-284600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-223500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-195100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-232500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-129600</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-146100</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-181800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-36300</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-119900</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-203000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-164300</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-146200</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-1061000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-142200</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-93700</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-63200</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-58000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-74700</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AI96" s="3">
         <v>-27500</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AJ96" s="3">
         <v>-45300</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AK96" s="3">
         <v>-92700</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AL96" s="3">
         <v>-109200</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AM96" s="3">
         <v>-145500</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AN96" s="3">
         <v>-136100</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AO96" s="3">
         <v>-100700</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AP96" s="3">
         <v>-99400</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10460,14 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10582,14 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,352 +10704,376 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-260600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-504500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-897800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-272400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-1142200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-337400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-1205900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-2190600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-68600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>724800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-939300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-2802600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>83300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-871600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-992700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>116900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>316100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-147900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-2117200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>281100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>195600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-887500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-367800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>2973500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-219900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>180400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>112800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-188300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>62800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>406100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-127900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-41900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-6900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-171000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-31700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>16300</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>17200</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E101" s="3">
+        <v>15600</v>
+      </c>
+      <c r="F101" s="3">
         <v>-9700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>1100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-6000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-24600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-6600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>2300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>7700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>11200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-3300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>7500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>10400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-2900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-11100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>2100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-3600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>5000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-9400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>26500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>11700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>5900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>5400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>7600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>11200</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>-5100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>4000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>-3500</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AN101" s="3">
         <v>-600</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AO101" s="3">
         <v>9900</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AP101" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>555300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>1645100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-2554000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>1782800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1251200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>4287000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>189300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-3334300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>3030100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>853000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>339700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-152400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-1572800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>950800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>178500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>884700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-578200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-1150900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>1786900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>160900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-19700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>392000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-681100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>718200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>426300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-44800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-378000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-15500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-146900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>70400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>330100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-305100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>114500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-25400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>-61500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>-34000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>-217600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>139300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>-112800</v>
       </c>
     </row>
